--- a/backend/templates/template_site.xlsx
+++ b/backend/templates/template_site.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sites" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hướng dẫn" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Lookups" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="Sites" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Hướng dẫn" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="_Lookups" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sites'!$A$1:$Y$1</definedName>
@@ -27756,67 +27756,67 @@
   </sheetData>
   <autoFilter ref="A1:Y1"/>
   <dataValidations count="20">
-    <dataValidation sqref="A2:A1001" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
+    <dataValidation sqref="A2:A1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"MB,MT,MN"</formula1>
     </dataValidation>
-    <dataValidation sqref="B2:B1001" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
+    <dataValidation sqref="B2:B1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>'_Lookups'!$A$2:$A$35</formula1>
     </dataValidation>
-    <dataValidation sqref="C2:C1001" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
+    <dataValidation sqref="C2:C1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>'_Lookups'!$B$2:$B$2995</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:F1001" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
+    <dataValidation sqref="F2:F1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"VIP,VVIP"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H1001" showErrorMessage="1" showInputMessage="1" allowBlank="1" errorTitle="Latitude không hợp lệ" error="Latitude phải trong khoảng 8.33–23.39" type="decimal" operator="between">
+    <dataValidation sqref="H2:H1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Latitude không hợp lệ" error="Latitude phải trong khoảng 8.33–23.39" type="decimal" operator="between">
       <formula1>8.33</formula1>
       <formula2>23.39</formula2>
     </dataValidation>
-    <dataValidation sqref="I2:I1001" showErrorMessage="1" showInputMessage="1" allowBlank="1" errorTitle="Longitude không hợp lệ" error="Longitude phải trong khoảng 102.14–109.47" type="decimal" operator="between">
+    <dataValidation sqref="I2:I1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Longitude không hợp lệ" error="Longitude phải trong khoảng 102.14–109.47" type="decimal" operator="between">
       <formula1>102.14</formula1>
       <formula2>109.47</formula2>
     </dataValidation>
-    <dataValidation sqref="J2:J1001" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
+    <dataValidation sqref="J2:J1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"x,"</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K1001" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
+    <dataValidation sqref="K2:K1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"x,"</formula1>
     </dataValidation>
-    <dataValidation sqref="L2:L1001" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
+    <dataValidation sqref="L2:L1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"x,"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M1001" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
+    <dataValidation sqref="M2:M1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"x,"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N1001" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
+    <dataValidation sqref="N2:N1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"x,"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O1001" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
+    <dataValidation sqref="O2:O1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"x,"</formula1>
     </dataValidation>
-    <dataValidation sqref="P2:P1001" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
+    <dataValidation sqref="P2:P1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"x,"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q2:Q1001" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
+    <dataValidation sqref="Q2:Q1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"x,"</formula1>
     </dataValidation>
-    <dataValidation sqref="R2:R1001" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
+    <dataValidation sqref="R2:R1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>'_Lookups'!$C$2:$C$6</formula1>
     </dataValidation>
-    <dataValidation sqref="S2:S1001" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
+    <dataValidation sqref="S2:S1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"VNPT HOST,MBF HOST"</formula1>
     </dataValidation>
-    <dataValidation sqref="T2:T1001" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
+    <dataValidation sqref="T2:T1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"VNPT HOST,MBF HOST"</formula1>
     </dataValidation>
-    <dataValidation sqref="U2:U1001" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
+    <dataValidation sqref="U2:U1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"VNPT HOST,MBF HOST"</formula1>
     </dataValidation>
-    <dataValidation sqref="V2:V1001" showErrorMessage="1" showInputMessage="1" allowBlank="1" errorTitle="Độ cao không hợp lệ" error="Phải là số dương (m)" type="decimal" operator="between">
+    <dataValidation sqref="V2:V1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Độ cao không hợp lệ" error="Phải là số dương (m)" type="decimal" operator="between">
       <formula1>0</formula1>
       <formula2>999</formula2>
     </dataValidation>
-    <dataValidation sqref="W2:W1001" showErrorMessage="1" showInputMessage="1" allowBlank="1" errorTitle="Độ cao không hợp lệ" error="Phải là số dương (m)" type="decimal" operator="between">
+    <dataValidation sqref="W2:W1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Độ cao không hợp lệ" error="Phải là số dương (m)" type="decimal" operator="between">
       <formula1>0</formula1>
       <formula2>999</formula2>
     </dataValidation>
@@ -28567,11 +28567,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A19:C19"/>
     <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A9:C9"/>
     <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A28:C28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/templates/template_site.xlsx
+++ b/backend/templates/template_site.xlsx
@@ -27755,7 +27755,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:Y1"/>
-  <dataValidations count="20">
+  <dataValidations count="18">
     <dataValidation sqref="A2:A1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"MB,MT,MN"</formula1>
     </dataValidation>
@@ -27812,14 +27812,6 @@
     <dataValidation sqref="U2:U1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"VNPT HOST,MBF HOST"</formula1>
     </dataValidation>
-    <dataValidation sqref="V2:V1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Độ cao không hợp lệ" error="Phải là số dương (m)" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>999</formula2>
-    </dataValidation>
-    <dataValidation sqref="W2:W1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Độ cao không hợp lệ" error="Phải là số dương (m)" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>999</formula2>
-    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -28505,7 +28497,7 @@
       </c>
       <c r="B51" s="13" t="inlineStr">
         <is>
-          <t>Độ cao đỉnh cột anten tới mặt đất (m) – bắt buộc</t>
+          <t>Độ cao đỉnh cột anten tới mặt đất – bắt buộc (số hoặc chuỗi, vd: 35 hoặc IBC)</t>
         </is>
       </c>
       <c r="C51" s="15" t="inlineStr">
@@ -28522,7 +28514,7 @@
       </c>
       <c r="B52" s="13" t="inlineStr">
         <is>
-          <t>Độ cao cột anten – đỉnh đến chân cột (m)</t>
+          <t>Độ cao cột anten – đỉnh đến chân cột (số hoặc chuỗi, vd: 30 hoặc IBC)</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">

--- a/backend/templates/template_site.xlsx
+++ b/backend/templates/template_site.xlsx
@@ -27823,7 +27823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -28108,90 +28108,78 @@
       </c>
       <c r="C26" s="9" t="inlineStr"/>
     </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>Tinh / Phuong xa để trống</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>→ Tự động điền theo 6 ký tự đầu của Site name (khớp cột ky_tu_1_6 trong danh mục Tỉnh/Xã/Phường). Ví dụ: HNIHKM0001 → HNIHKM</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>Tinh / Phuong xa đã có giá trị</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>→ Giữ nguyên giá trị đã nhập, KHÔNG tự động điền</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>Không tìm thấy mã 6 ký tự</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>→ Tinh / Phuong xa để trống (không phải lỗi – các cột này KHÔNG bắt buộc)</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>MÔ TẢ CÁC CỘT</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="11" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>Tên cột</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>Mô tả / Hướng dẫn</t>
         </is>
       </c>
-      <c r="C29" s="11" t="inlineStr">
+      <c r="C32" s="11" t="inlineStr">
         <is>
           <t>Bắt buộc</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>Mien</t>
-        </is>
-      </c>
-      <c r="B30" s="13" t="inlineStr">
-        <is>
-          <t>Miền: MB / MT / MN</t>
-        </is>
-      </c>
-      <c r="C30" s="14" t="inlineStr">
-        <is>
-          <t>Tùy chọn</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="12" t="inlineStr">
-        <is>
-          <t>Tinh</t>
-        </is>
-      </c>
-      <c r="B31" s="13" t="inlineStr">
-        <is>
-          <t>Tỉnh / Thành phố – chọn từ danh sách</t>
-        </is>
-      </c>
-      <c r="C31" s="14" t="inlineStr">
-        <is>
-          <t>Tùy chọn</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="12" t="inlineStr">
-        <is>
-          <t>Phuong xa</t>
-        </is>
-      </c>
-      <c r="B32" s="13" t="inlineStr">
-        <is>
-          <t>Phường / Xã – chọn từ danh sách</t>
-        </is>
-      </c>
-      <c r="C32" s="14" t="inlineStr">
-        <is>
-          <t>Tùy chọn</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>Site name (cu)</t>
+          <t>Mien</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>Tên site cũ – điền khi đổi tên site</t>
+          <t>Miền: MB / MT / MN</t>
         </is>
       </c>
       <c r="C33" s="14" t="inlineStr">
@@ -28201,31 +28189,31 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
-        <is>
-          <t>Site name</t>
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Tinh</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>Tên site hiện tại – bắt buộc, phải là duy nhất</t>
-        </is>
-      </c>
-      <c r="C34" s="15" t="inlineStr">
-        <is>
-          <t>✔ Bắt buộc</t>
+          <t>Tỉnh / Thành phố – chọn từ danh sách. KHÔNG bắt buộc – để trống thì hệ thống tự điền theo 6 ký tự đầu của Site name (khớp cột ky_tu_1_6 trong danh mục Tỉnh/Xã/Phường); đã nhập thì giữ nguyên</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>Tùy chọn</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>Site VIP</t>
+          <t>Phuong xa</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>Mức độ VIP: VIP hoặc VVIP – để trống nếu không phải</t>
+          <t>Phường / Xã – chọn từ danh sách. KHÔNG bắt buộc – để trống thì hệ thống tự điền theo 6 ký tự đầu của Site name (khớp cột ky_tu_1_6 trong danh mục Tỉnh/Xã/Phường); đã nhập thì giữ nguyên</t>
         </is>
       </c>
       <c r="C35" s="14" t="inlineStr">
@@ -28237,12 +28225,12 @@
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Ma PTM</t>
+          <t>Site name (cu)</t>
         </is>
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>Mã PTM của trạm</t>
+          <t>Tên site cũ – điền khi đổi tên site</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
@@ -28254,12 +28242,12 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>Lat</t>
+          <t>Site name</t>
         </is>
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>Latitude (vĩ độ) – phải trong 8.33–23.39</t>
+          <t>Tên site hiện tại – bắt buộc, phải là duy nhất</t>
         </is>
       </c>
       <c r="C37" s="15" t="inlineStr">
@@ -28269,31 +28257,31 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
-        <is>
-          <t>Long</t>
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Site VIP</t>
         </is>
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>Longitude (kinh độ) – phải trong 102.14–109.47</t>
-        </is>
-      </c>
-      <c r="C38" s="15" t="inlineStr">
-        <is>
-          <t>✔ Bắt buộc</t>
+          <t>Mức độ VIP: VIP hoặc VVIP – để trống nếu không phải</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="inlineStr">
+        <is>
+          <t>Tùy chọn</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>Tram 2G</t>
+          <t>Ma PTM</t>
         </is>
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>x = có trạm 2G, để trống = không</t>
+          <t>Mã PTM của trạm</t>
         </is>
       </c>
       <c r="C39" s="14" t="inlineStr">
@@ -28303,48 +28291,48 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="12" t="inlineStr">
-        <is>
-          <t>Tram 3G</t>
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>Lat</t>
         </is>
       </c>
       <c r="B40" s="13" t="inlineStr">
         <is>
-          <t>x = có trạm 3G, để trống = không</t>
-        </is>
-      </c>
-      <c r="C40" s="14" t="inlineStr">
-        <is>
-          <t>Tùy chọn</t>
+          <t>Latitude (vĩ độ) – phải trong 8.33–23.39</t>
+        </is>
+      </c>
+      <c r="C40" s="15" t="inlineStr">
+        <is>
+          <t>✔ Bắt buộc</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="12" t="inlineStr">
-        <is>
-          <t>Tram 4G</t>
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>Long</t>
         </is>
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>x = có trạm 4G, để trống = không</t>
-        </is>
-      </c>
-      <c r="C41" s="14" t="inlineStr">
-        <is>
-          <t>Tùy chọn</t>
+          <t>Longitude (kinh độ) – phải trong 102.14–109.47</t>
+        </is>
+      </c>
+      <c r="C41" s="15" t="inlineStr">
+        <is>
+          <t>✔ Bắt buộc</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>Tram 5G</t>
+          <t>Tram 2G</t>
         </is>
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>x = có trạm 5G, để trống = không</t>
+          <t>x = có trạm 2G, để trống = không</t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
@@ -28356,12 +28344,12 @@
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t>Repeater</t>
+          <t>Tram 3G</t>
         </is>
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>x = có Repeater, để trống = không</t>
+          <t>x = có trạm 3G, để trống = không</t>
         </is>
       </c>
       <c r="C43" s="14" t="inlineStr">
@@ -28373,12 +28361,12 @@
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>Booster</t>
+          <t>Tram 4G</t>
         </is>
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>x = có Booster, để trống = không</t>
+          <t>x = có trạm 4G, để trống = không</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
@@ -28390,12 +28378,12 @@
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>Node truyen dan only</t>
+          <t>Tram 5G</t>
         </is>
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>x = Node truyền dẫn only, để trống = không</t>
+          <t>x = có trạm 5G, để trống = không</t>
         </is>
       </c>
       <c r="C45" s="14" t="inlineStr">
@@ -28407,12 +28395,12 @@
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>Tram phu song TSCA</t>
+          <t>Repeater</t>
         </is>
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>x = Trạm phủ sóng TSCA, để trống = không</t>
+          <t>x = có Repeater, để trống = không</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
@@ -28424,12 +28412,12 @@
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t>Phan loai tram</t>
+          <t>Booster</t>
         </is>
       </c>
       <c r="B47" s="13" t="inlineStr">
         <is>
-          <t>Phân loại trạm – chọn từ danh sách</t>
+          <t>x = có Booster, để trống = không</t>
         </is>
       </c>
       <c r="C47" s="14" t="inlineStr">
@@ -28441,12 +28429,12 @@
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>MORAN 3G</t>
+          <t>Node truyen dan only</t>
         </is>
       </c>
       <c r="B48" s="13" t="inlineStr">
         <is>
-          <t>MORAN 3G: VNPT HOST hoặc MBF HOST</t>
+          <t>x = Node truyền dẫn only, để trống = không</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
@@ -28458,12 +28446,12 @@
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>MORAN 4G</t>
+          <t>Tram phu song TSCA</t>
         </is>
       </c>
       <c r="B49" s="13" t="inlineStr">
         <is>
-          <t>MORAN 4G: VNPT HOST hoặc MBF HOST</t>
+          <t>x = Trạm phủ sóng TSCA, để trống = không</t>
         </is>
       </c>
       <c r="C49" s="14" t="inlineStr">
@@ -28475,12 +28463,12 @@
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>MORAN 5G</t>
+          <t>Phan loai tram</t>
         </is>
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>MORAN 5G: VNPT HOST hoặc MBF HOST</t>
+          <t>Phân loại trạm – chọn từ danh sách</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
@@ -28490,68 +28478,119 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="10" t="inlineStr">
-        <is>
-          <t>Do cao dinh cot anten</t>
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t>MORAN 3G</t>
         </is>
       </c>
       <c r="B51" s="13" t="inlineStr">
         <is>
-          <t>Độ cao đỉnh cột anten tới mặt đất – bắt buộc (số hoặc chuỗi, vd: 35 hoặc IBC)</t>
-        </is>
-      </c>
-      <c r="C51" s="15" t="inlineStr">
-        <is>
-          <t>✔ Bắt buộc</t>
+          <t>MORAN 3G: VNPT HOST hoặc MBF HOST</t>
+        </is>
+      </c>
+      <c r="C51" s="14" t="inlineStr">
+        <is>
+          <t>Tùy chọn</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
+          <t>MORAN 4G</t>
+        </is>
+      </c>
+      <c r="B52" s="13" t="inlineStr">
+        <is>
+          <t>MORAN 4G: VNPT HOST hoặc MBF HOST</t>
+        </is>
+      </c>
+      <c r="C52" s="14" t="inlineStr">
+        <is>
+          <t>Tùy chọn</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t>MORAN 5G</t>
+        </is>
+      </c>
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>MORAN 5G: VNPT HOST hoặc MBF HOST</t>
+        </is>
+      </c>
+      <c r="C53" s="14" t="inlineStr">
+        <is>
+          <t>Tùy chọn</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>Do cao dinh cot anten</t>
+        </is>
+      </c>
+      <c r="B54" s="13" t="inlineStr">
+        <is>
+          <t>Độ cao đỉnh cột anten tới mặt đất – bắt buộc (số hoặc chuỗi, vd: 35 hoặc IBC)</t>
+        </is>
+      </c>
+      <c r="C54" s="15" t="inlineStr">
+        <is>
+          <t>✔ Bắt buộc</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
           <t>Do cao cot anten</t>
         </is>
       </c>
-      <c r="B52" s="13" t="inlineStr">
+      <c r="B55" s="13" t="inlineStr">
         <is>
           <t>Độ cao cột anten – đỉnh đến chân cột (số hoặc chuỗi, vd: 30 hoặc IBC)</t>
         </is>
       </c>
-      <c r="C52" s="14" t="inlineStr">
+      <c r="C55" s="14" t="inlineStr">
         <is>
           <t>Tùy chọn</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="10" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="10" t="inlineStr">
         <is>
           <t>Dia chi</t>
         </is>
       </c>
-      <c r="B53" s="13" t="inlineStr">
+      <c r="B56" s="13" t="inlineStr">
         <is>
           <t>Địa chỉ chi tiết của trạm – bắt buộc</t>
         </is>
       </c>
-      <c r="C53" s="15" t="inlineStr">
+      <c r="C56" s="15" t="inlineStr">
         <is>
           <t>✔ Bắt buộc</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="12" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="12" t="inlineStr">
         <is>
           <t>Ghi chu</t>
         </is>
       </c>
-      <c r="B54" s="13" t="inlineStr">
+      <c r="B57" s="13" t="inlineStr">
         <is>
           <t>Ghi chú thêm</t>
         </is>
       </c>
-      <c r="C54" s="14" t="inlineStr">
+      <c r="C57" s="14" t="inlineStr">
         <is>
           <t>Tùy chọn</t>
         </is>
@@ -28559,9 +28598,9 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A28:C28"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A31:C31"/>
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="A4:C4"/>
   </mergeCells>

--- a/backend/templates/template_site.xlsx
+++ b/backend/templates/template_site.xlsx
@@ -773,7 +773,7 @@
         <v>35</v>
       </c>
       <c r="W2" s="2" t="n"/>
-      <c r="X2" s="3" t="inlineStr">
+      <c r="X2" s="2" t="inlineStr">
         <is>
           <t>Số 1, Đường ABC, Phường XYZ, Hà Nội</t>
         </is>
@@ -804,7 +804,7 @@
       <c r="U3" s="4" t="n"/>
       <c r="V3" s="3" t="n"/>
       <c r="W3" s="4" t="n"/>
-      <c r="X3" s="3" t="n"/>
+      <c r="X3" s="4" t="n"/>
       <c r="Y3" s="4" t="n"/>
     </row>
     <row r="4">
@@ -831,7 +831,7 @@
       <c r="U4" s="2" t="n"/>
       <c r="V4" s="3" t="n"/>
       <c r="W4" s="2" t="n"/>
-      <c r="X4" s="3" t="n"/>
+      <c r="X4" s="2" t="n"/>
       <c r="Y4" s="2" t="n"/>
     </row>
     <row r="5">
@@ -858,7 +858,7 @@
       <c r="U5" s="4" t="n"/>
       <c r="V5" s="3" t="n"/>
       <c r="W5" s="4" t="n"/>
-      <c r="X5" s="3" t="n"/>
+      <c r="X5" s="4" t="n"/>
       <c r="Y5" s="4" t="n"/>
     </row>
     <row r="6">
@@ -885,7 +885,7 @@
       <c r="U6" s="2" t="n"/>
       <c r="V6" s="3" t="n"/>
       <c r="W6" s="2" t="n"/>
-      <c r="X6" s="3" t="n"/>
+      <c r="X6" s="2" t="n"/>
       <c r="Y6" s="2" t="n"/>
     </row>
     <row r="7">
@@ -912,7 +912,7 @@
       <c r="U7" s="4" t="n"/>
       <c r="V7" s="3" t="n"/>
       <c r="W7" s="4" t="n"/>
-      <c r="X7" s="3" t="n"/>
+      <c r="X7" s="4" t="n"/>
       <c r="Y7" s="4" t="n"/>
     </row>
     <row r="8">
@@ -939,7 +939,7 @@
       <c r="U8" s="2" t="n"/>
       <c r="V8" s="3" t="n"/>
       <c r="W8" s="2" t="n"/>
-      <c r="X8" s="3" t="n"/>
+      <c r="X8" s="2" t="n"/>
       <c r="Y8" s="2" t="n"/>
     </row>
     <row r="9">
@@ -966,7 +966,7 @@
       <c r="U9" s="4" t="n"/>
       <c r="V9" s="3" t="n"/>
       <c r="W9" s="4" t="n"/>
-      <c r="X9" s="3" t="n"/>
+      <c r="X9" s="4" t="n"/>
       <c r="Y9" s="4" t="n"/>
     </row>
     <row r="10">
@@ -993,7 +993,7 @@
       <c r="U10" s="2" t="n"/>
       <c r="V10" s="3" t="n"/>
       <c r="W10" s="2" t="n"/>
-      <c r="X10" s="3" t="n"/>
+      <c r="X10" s="2" t="n"/>
       <c r="Y10" s="2" t="n"/>
     </row>
     <row r="11">
@@ -1020,7 +1020,7 @@
       <c r="U11" s="4" t="n"/>
       <c r="V11" s="3" t="n"/>
       <c r="W11" s="4" t="n"/>
-      <c r="X11" s="3" t="n"/>
+      <c r="X11" s="4" t="n"/>
       <c r="Y11" s="4" t="n"/>
     </row>
     <row r="12">
@@ -1047,7 +1047,7 @@
       <c r="U12" s="2" t="n"/>
       <c r="V12" s="3" t="n"/>
       <c r="W12" s="2" t="n"/>
-      <c r="X12" s="3" t="n"/>
+      <c r="X12" s="2" t="n"/>
       <c r="Y12" s="2" t="n"/>
     </row>
     <row r="13">
@@ -1074,7 +1074,7 @@
       <c r="U13" s="4" t="n"/>
       <c r="V13" s="3" t="n"/>
       <c r="W13" s="4" t="n"/>
-      <c r="X13" s="3" t="n"/>
+      <c r="X13" s="4" t="n"/>
       <c r="Y13" s="4" t="n"/>
     </row>
     <row r="14">
@@ -1101,7 +1101,7 @@
       <c r="U14" s="2" t="n"/>
       <c r="V14" s="3" t="n"/>
       <c r="W14" s="2" t="n"/>
-      <c r="X14" s="3" t="n"/>
+      <c r="X14" s="2" t="n"/>
       <c r="Y14" s="2" t="n"/>
     </row>
     <row r="15">
@@ -1128,7 +1128,7 @@
       <c r="U15" s="4" t="n"/>
       <c r="V15" s="3" t="n"/>
       <c r="W15" s="4" t="n"/>
-      <c r="X15" s="3" t="n"/>
+      <c r="X15" s="4" t="n"/>
       <c r="Y15" s="4" t="n"/>
     </row>
     <row r="16">
@@ -1155,7 +1155,7 @@
       <c r="U16" s="2" t="n"/>
       <c r="V16" s="3" t="n"/>
       <c r="W16" s="2" t="n"/>
-      <c r="X16" s="3" t="n"/>
+      <c r="X16" s="2" t="n"/>
       <c r="Y16" s="2" t="n"/>
     </row>
     <row r="17">
@@ -1182,7 +1182,7 @@
       <c r="U17" s="4" t="n"/>
       <c r="V17" s="3" t="n"/>
       <c r="W17" s="4" t="n"/>
-      <c r="X17" s="3" t="n"/>
+      <c r="X17" s="4" t="n"/>
       <c r="Y17" s="4" t="n"/>
     </row>
     <row r="18">
@@ -1209,7 +1209,7 @@
       <c r="U18" s="2" t="n"/>
       <c r="V18" s="3" t="n"/>
       <c r="W18" s="2" t="n"/>
-      <c r="X18" s="3" t="n"/>
+      <c r="X18" s="2" t="n"/>
       <c r="Y18" s="2" t="n"/>
     </row>
     <row r="19">
@@ -1236,7 +1236,7 @@
       <c r="U19" s="4" t="n"/>
       <c r="V19" s="3" t="n"/>
       <c r="W19" s="4" t="n"/>
-      <c r="X19" s="3" t="n"/>
+      <c r="X19" s="4" t="n"/>
       <c r="Y19" s="4" t="n"/>
     </row>
     <row r="20">
@@ -1263,7 +1263,7 @@
       <c r="U20" s="2" t="n"/>
       <c r="V20" s="3" t="n"/>
       <c r="W20" s="2" t="n"/>
-      <c r="X20" s="3" t="n"/>
+      <c r="X20" s="2" t="n"/>
       <c r="Y20" s="2" t="n"/>
     </row>
     <row r="21">
@@ -1290,7 +1290,7 @@
       <c r="U21" s="4" t="n"/>
       <c r="V21" s="3" t="n"/>
       <c r="W21" s="4" t="n"/>
-      <c r="X21" s="3" t="n"/>
+      <c r="X21" s="4" t="n"/>
       <c r="Y21" s="4" t="n"/>
     </row>
     <row r="22">
@@ -1317,7 +1317,7 @@
       <c r="U22" s="2" t="n"/>
       <c r="V22" s="3" t="n"/>
       <c r="W22" s="2" t="n"/>
-      <c r="X22" s="3" t="n"/>
+      <c r="X22" s="2" t="n"/>
       <c r="Y22" s="2" t="n"/>
     </row>
     <row r="23">
@@ -1344,7 +1344,7 @@
       <c r="U23" s="4" t="n"/>
       <c r="V23" s="3" t="n"/>
       <c r="W23" s="4" t="n"/>
-      <c r="X23" s="3" t="n"/>
+      <c r="X23" s="4" t="n"/>
       <c r="Y23" s="4" t="n"/>
     </row>
     <row r="24">
@@ -1371,7 +1371,7 @@
       <c r="U24" s="2" t="n"/>
       <c r="V24" s="3" t="n"/>
       <c r="W24" s="2" t="n"/>
-      <c r="X24" s="3" t="n"/>
+      <c r="X24" s="2" t="n"/>
       <c r="Y24" s="2" t="n"/>
     </row>
     <row r="25">
@@ -1398,7 +1398,7 @@
       <c r="U25" s="4" t="n"/>
       <c r="V25" s="3" t="n"/>
       <c r="W25" s="4" t="n"/>
-      <c r="X25" s="3" t="n"/>
+      <c r="X25" s="4" t="n"/>
       <c r="Y25" s="4" t="n"/>
     </row>
     <row r="26">
@@ -1425,7 +1425,7 @@
       <c r="U26" s="2" t="n"/>
       <c r="V26" s="3" t="n"/>
       <c r="W26" s="2" t="n"/>
-      <c r="X26" s="3" t="n"/>
+      <c r="X26" s="2" t="n"/>
       <c r="Y26" s="2" t="n"/>
     </row>
     <row r="27">
@@ -1452,7 +1452,7 @@
       <c r="U27" s="4" t="n"/>
       <c r="V27" s="3" t="n"/>
       <c r="W27" s="4" t="n"/>
-      <c r="X27" s="3" t="n"/>
+      <c r="X27" s="4" t="n"/>
       <c r="Y27" s="4" t="n"/>
     </row>
     <row r="28">
@@ -1479,7 +1479,7 @@
       <c r="U28" s="2" t="n"/>
       <c r="V28" s="3" t="n"/>
       <c r="W28" s="2" t="n"/>
-      <c r="X28" s="3" t="n"/>
+      <c r="X28" s="2" t="n"/>
       <c r="Y28" s="2" t="n"/>
     </row>
     <row r="29">
@@ -1506,7 +1506,7 @@
       <c r="U29" s="4" t="n"/>
       <c r="V29" s="3" t="n"/>
       <c r="W29" s="4" t="n"/>
-      <c r="X29" s="3" t="n"/>
+      <c r="X29" s="4" t="n"/>
       <c r="Y29" s="4" t="n"/>
     </row>
     <row r="30">
@@ -1533,7 +1533,7 @@
       <c r="U30" s="2" t="n"/>
       <c r="V30" s="3" t="n"/>
       <c r="W30" s="2" t="n"/>
-      <c r="X30" s="3" t="n"/>
+      <c r="X30" s="2" t="n"/>
       <c r="Y30" s="2" t="n"/>
     </row>
     <row r="31">
@@ -1560,7 +1560,7 @@
       <c r="U31" s="4" t="n"/>
       <c r="V31" s="3" t="n"/>
       <c r="W31" s="4" t="n"/>
-      <c r="X31" s="3" t="n"/>
+      <c r="X31" s="4" t="n"/>
       <c r="Y31" s="4" t="n"/>
     </row>
     <row r="32">
@@ -1587,7 +1587,7 @@
       <c r="U32" s="2" t="n"/>
       <c r="V32" s="3" t="n"/>
       <c r="W32" s="2" t="n"/>
-      <c r="X32" s="3" t="n"/>
+      <c r="X32" s="2" t="n"/>
       <c r="Y32" s="2" t="n"/>
     </row>
     <row r="33">
@@ -1614,7 +1614,7 @@
       <c r="U33" s="4" t="n"/>
       <c r="V33" s="3" t="n"/>
       <c r="W33" s="4" t="n"/>
-      <c r="X33" s="3" t="n"/>
+      <c r="X33" s="4" t="n"/>
       <c r="Y33" s="4" t="n"/>
     </row>
     <row r="34">
@@ -1641,7 +1641,7 @@
       <c r="U34" s="2" t="n"/>
       <c r="V34" s="3" t="n"/>
       <c r="W34" s="2" t="n"/>
-      <c r="X34" s="3" t="n"/>
+      <c r="X34" s="2" t="n"/>
       <c r="Y34" s="2" t="n"/>
     </row>
     <row r="35">
@@ -1668,7 +1668,7 @@
       <c r="U35" s="4" t="n"/>
       <c r="V35" s="3" t="n"/>
       <c r="W35" s="4" t="n"/>
-      <c r="X35" s="3" t="n"/>
+      <c r="X35" s="4" t="n"/>
       <c r="Y35" s="4" t="n"/>
     </row>
     <row r="36">
@@ -1695,7 +1695,7 @@
       <c r="U36" s="2" t="n"/>
       <c r="V36" s="3" t="n"/>
       <c r="W36" s="2" t="n"/>
-      <c r="X36" s="3" t="n"/>
+      <c r="X36" s="2" t="n"/>
       <c r="Y36" s="2" t="n"/>
     </row>
     <row r="37">
@@ -1722,7 +1722,7 @@
       <c r="U37" s="4" t="n"/>
       <c r="V37" s="3" t="n"/>
       <c r="W37" s="4" t="n"/>
-      <c r="X37" s="3" t="n"/>
+      <c r="X37" s="4" t="n"/>
       <c r="Y37" s="4" t="n"/>
     </row>
     <row r="38">
@@ -1749,7 +1749,7 @@
       <c r="U38" s="2" t="n"/>
       <c r="V38" s="3" t="n"/>
       <c r="W38" s="2" t="n"/>
-      <c r="X38" s="3" t="n"/>
+      <c r="X38" s="2" t="n"/>
       <c r="Y38" s="2" t="n"/>
     </row>
     <row r="39">
@@ -1776,7 +1776,7 @@
       <c r="U39" s="4" t="n"/>
       <c r="V39" s="3" t="n"/>
       <c r="W39" s="4" t="n"/>
-      <c r="X39" s="3" t="n"/>
+      <c r="X39" s="4" t="n"/>
       <c r="Y39" s="4" t="n"/>
     </row>
     <row r="40">
@@ -1803,7 +1803,7 @@
       <c r="U40" s="2" t="n"/>
       <c r="V40" s="3" t="n"/>
       <c r="W40" s="2" t="n"/>
-      <c r="X40" s="3" t="n"/>
+      <c r="X40" s="2" t="n"/>
       <c r="Y40" s="2" t="n"/>
     </row>
     <row r="41">
@@ -1830,7 +1830,7 @@
       <c r="U41" s="4" t="n"/>
       <c r="V41" s="3" t="n"/>
       <c r="W41" s="4" t="n"/>
-      <c r="X41" s="3" t="n"/>
+      <c r="X41" s="4" t="n"/>
       <c r="Y41" s="4" t="n"/>
     </row>
     <row r="42">
@@ -1857,7 +1857,7 @@
       <c r="U42" s="2" t="n"/>
       <c r="V42" s="3" t="n"/>
       <c r="W42" s="2" t="n"/>
-      <c r="X42" s="3" t="n"/>
+      <c r="X42" s="2" t="n"/>
       <c r="Y42" s="2" t="n"/>
     </row>
     <row r="43">
@@ -1884,7 +1884,7 @@
       <c r="U43" s="4" t="n"/>
       <c r="V43" s="3" t="n"/>
       <c r="W43" s="4" t="n"/>
-      <c r="X43" s="3" t="n"/>
+      <c r="X43" s="4" t="n"/>
       <c r="Y43" s="4" t="n"/>
     </row>
     <row r="44">
@@ -1911,7 +1911,7 @@
       <c r="U44" s="2" t="n"/>
       <c r="V44" s="3" t="n"/>
       <c r="W44" s="2" t="n"/>
-      <c r="X44" s="3" t="n"/>
+      <c r="X44" s="2" t="n"/>
       <c r="Y44" s="2" t="n"/>
     </row>
     <row r="45">
@@ -1938,7 +1938,7 @@
       <c r="U45" s="4" t="n"/>
       <c r="V45" s="3" t="n"/>
       <c r="W45" s="4" t="n"/>
-      <c r="X45" s="3" t="n"/>
+      <c r="X45" s="4" t="n"/>
       <c r="Y45" s="4" t="n"/>
     </row>
     <row r="46">
@@ -1965,7 +1965,7 @@
       <c r="U46" s="2" t="n"/>
       <c r="V46" s="3" t="n"/>
       <c r="W46" s="2" t="n"/>
-      <c r="X46" s="3" t="n"/>
+      <c r="X46" s="2" t="n"/>
       <c r="Y46" s="2" t="n"/>
     </row>
     <row r="47">
@@ -1992,7 +1992,7 @@
       <c r="U47" s="4" t="n"/>
       <c r="V47" s="3" t="n"/>
       <c r="W47" s="4" t="n"/>
-      <c r="X47" s="3" t="n"/>
+      <c r="X47" s="4" t="n"/>
       <c r="Y47" s="4" t="n"/>
     </row>
     <row r="48">
@@ -2019,7 +2019,7 @@
       <c r="U48" s="2" t="n"/>
       <c r="V48" s="3" t="n"/>
       <c r="W48" s="2" t="n"/>
-      <c r="X48" s="3" t="n"/>
+      <c r="X48" s="2" t="n"/>
       <c r="Y48" s="2" t="n"/>
     </row>
     <row r="49">
@@ -2046,7 +2046,7 @@
       <c r="U49" s="4" t="n"/>
       <c r="V49" s="3" t="n"/>
       <c r="W49" s="4" t="n"/>
-      <c r="X49" s="3" t="n"/>
+      <c r="X49" s="4" t="n"/>
       <c r="Y49" s="4" t="n"/>
     </row>
     <row r="50">
@@ -2073,7 +2073,7 @@
       <c r="U50" s="2" t="n"/>
       <c r="V50" s="3" t="n"/>
       <c r="W50" s="2" t="n"/>
-      <c r="X50" s="3" t="n"/>
+      <c r="X50" s="2" t="n"/>
       <c r="Y50" s="2" t="n"/>
     </row>
     <row r="51">
@@ -2100,7 +2100,7 @@
       <c r="U51" s="4" t="n"/>
       <c r="V51" s="3" t="n"/>
       <c r="W51" s="4" t="n"/>
-      <c r="X51" s="3" t="n"/>
+      <c r="X51" s="4" t="n"/>
       <c r="Y51" s="4" t="n"/>
     </row>
     <row r="52">
@@ -2127,7 +2127,7 @@
       <c r="U52" s="2" t="n"/>
       <c r="V52" s="3" t="n"/>
       <c r="W52" s="2" t="n"/>
-      <c r="X52" s="3" t="n"/>
+      <c r="X52" s="2" t="n"/>
       <c r="Y52" s="2" t="n"/>
     </row>
     <row r="53">
@@ -2154,7 +2154,7 @@
       <c r="U53" s="4" t="n"/>
       <c r="V53" s="3" t="n"/>
       <c r="W53" s="4" t="n"/>
-      <c r="X53" s="3" t="n"/>
+      <c r="X53" s="4" t="n"/>
       <c r="Y53" s="4" t="n"/>
     </row>
     <row r="54">
@@ -2181,7 +2181,7 @@
       <c r="U54" s="2" t="n"/>
       <c r="V54" s="3" t="n"/>
       <c r="W54" s="2" t="n"/>
-      <c r="X54" s="3" t="n"/>
+      <c r="X54" s="2" t="n"/>
       <c r="Y54" s="2" t="n"/>
     </row>
     <row r="55">
@@ -2208,7 +2208,7 @@
       <c r="U55" s="4" t="n"/>
       <c r="V55" s="3" t="n"/>
       <c r="W55" s="4" t="n"/>
-      <c r="X55" s="3" t="n"/>
+      <c r="X55" s="4" t="n"/>
       <c r="Y55" s="4" t="n"/>
     </row>
     <row r="56">
@@ -2235,7 +2235,7 @@
       <c r="U56" s="2" t="n"/>
       <c r="V56" s="3" t="n"/>
       <c r="W56" s="2" t="n"/>
-      <c r="X56" s="3" t="n"/>
+      <c r="X56" s="2" t="n"/>
       <c r="Y56" s="2" t="n"/>
     </row>
     <row r="57">
@@ -2262,7 +2262,7 @@
       <c r="U57" s="4" t="n"/>
       <c r="V57" s="3" t="n"/>
       <c r="W57" s="4" t="n"/>
-      <c r="X57" s="3" t="n"/>
+      <c r="X57" s="4" t="n"/>
       <c r="Y57" s="4" t="n"/>
     </row>
     <row r="58">
@@ -2289,7 +2289,7 @@
       <c r="U58" s="2" t="n"/>
       <c r="V58" s="3" t="n"/>
       <c r="W58" s="2" t="n"/>
-      <c r="X58" s="3" t="n"/>
+      <c r="X58" s="2" t="n"/>
       <c r="Y58" s="2" t="n"/>
     </row>
     <row r="59">
@@ -2316,7 +2316,7 @@
       <c r="U59" s="4" t="n"/>
       <c r="V59" s="3" t="n"/>
       <c r="W59" s="4" t="n"/>
-      <c r="X59" s="3" t="n"/>
+      <c r="X59" s="4" t="n"/>
       <c r="Y59" s="4" t="n"/>
     </row>
     <row r="60">
@@ -2343,7 +2343,7 @@
       <c r="U60" s="2" t="n"/>
       <c r="V60" s="3" t="n"/>
       <c r="W60" s="2" t="n"/>
-      <c r="X60" s="3" t="n"/>
+      <c r="X60" s="2" t="n"/>
       <c r="Y60" s="2" t="n"/>
     </row>
     <row r="61">
@@ -2370,7 +2370,7 @@
       <c r="U61" s="4" t="n"/>
       <c r="V61" s="3" t="n"/>
       <c r="W61" s="4" t="n"/>
-      <c r="X61" s="3" t="n"/>
+      <c r="X61" s="4" t="n"/>
       <c r="Y61" s="4" t="n"/>
     </row>
     <row r="62">
@@ -2397,7 +2397,7 @@
       <c r="U62" s="2" t="n"/>
       <c r="V62" s="3" t="n"/>
       <c r="W62" s="2" t="n"/>
-      <c r="X62" s="3" t="n"/>
+      <c r="X62" s="2" t="n"/>
       <c r="Y62" s="2" t="n"/>
     </row>
     <row r="63">
@@ -2424,7 +2424,7 @@
       <c r="U63" s="4" t="n"/>
       <c r="V63" s="3" t="n"/>
       <c r="W63" s="4" t="n"/>
-      <c r="X63" s="3" t="n"/>
+      <c r="X63" s="4" t="n"/>
       <c r="Y63" s="4" t="n"/>
     </row>
     <row r="64">
@@ -2451,7 +2451,7 @@
       <c r="U64" s="2" t="n"/>
       <c r="V64" s="3" t="n"/>
       <c r="W64" s="2" t="n"/>
-      <c r="X64" s="3" t="n"/>
+      <c r="X64" s="2" t="n"/>
       <c r="Y64" s="2" t="n"/>
     </row>
     <row r="65">
@@ -2478,7 +2478,7 @@
       <c r="U65" s="4" t="n"/>
       <c r="V65" s="3" t="n"/>
       <c r="W65" s="4" t="n"/>
-      <c r="X65" s="3" t="n"/>
+      <c r="X65" s="4" t="n"/>
       <c r="Y65" s="4" t="n"/>
     </row>
     <row r="66">
@@ -2505,7 +2505,7 @@
       <c r="U66" s="2" t="n"/>
       <c r="V66" s="3" t="n"/>
       <c r="W66" s="2" t="n"/>
-      <c r="X66" s="3" t="n"/>
+      <c r="X66" s="2" t="n"/>
       <c r="Y66" s="2" t="n"/>
     </row>
     <row r="67">
@@ -2532,7 +2532,7 @@
       <c r="U67" s="4" t="n"/>
       <c r="V67" s="3" t="n"/>
       <c r="W67" s="4" t="n"/>
-      <c r="X67" s="3" t="n"/>
+      <c r="X67" s="4" t="n"/>
       <c r="Y67" s="4" t="n"/>
     </row>
     <row r="68">
@@ -2559,7 +2559,7 @@
       <c r="U68" s="2" t="n"/>
       <c r="V68" s="3" t="n"/>
       <c r="W68" s="2" t="n"/>
-      <c r="X68" s="3" t="n"/>
+      <c r="X68" s="2" t="n"/>
       <c r="Y68" s="2" t="n"/>
     </row>
     <row r="69">
@@ -2586,7 +2586,7 @@
       <c r="U69" s="4" t="n"/>
       <c r="V69" s="3" t="n"/>
       <c r="W69" s="4" t="n"/>
-      <c r="X69" s="3" t="n"/>
+      <c r="X69" s="4" t="n"/>
       <c r="Y69" s="4" t="n"/>
     </row>
     <row r="70">
@@ -2613,7 +2613,7 @@
       <c r="U70" s="2" t="n"/>
       <c r="V70" s="3" t="n"/>
       <c r="W70" s="2" t="n"/>
-      <c r="X70" s="3" t="n"/>
+      <c r="X70" s="2" t="n"/>
       <c r="Y70" s="2" t="n"/>
     </row>
     <row r="71">
@@ -2640,7 +2640,7 @@
       <c r="U71" s="4" t="n"/>
       <c r="V71" s="3" t="n"/>
       <c r="W71" s="4" t="n"/>
-      <c r="X71" s="3" t="n"/>
+      <c r="X71" s="4" t="n"/>
       <c r="Y71" s="4" t="n"/>
     </row>
     <row r="72">
@@ -2667,7 +2667,7 @@
       <c r="U72" s="2" t="n"/>
       <c r="V72" s="3" t="n"/>
       <c r="W72" s="2" t="n"/>
-      <c r="X72" s="3" t="n"/>
+      <c r="X72" s="2" t="n"/>
       <c r="Y72" s="2" t="n"/>
     </row>
     <row r="73">
@@ -2694,7 +2694,7 @@
       <c r="U73" s="4" t="n"/>
       <c r="V73" s="3" t="n"/>
       <c r="W73" s="4" t="n"/>
-      <c r="X73" s="3" t="n"/>
+      <c r="X73" s="4" t="n"/>
       <c r="Y73" s="4" t="n"/>
     </row>
     <row r="74">
@@ -2721,7 +2721,7 @@
       <c r="U74" s="2" t="n"/>
       <c r="V74" s="3" t="n"/>
       <c r="W74" s="2" t="n"/>
-      <c r="X74" s="3" t="n"/>
+      <c r="X74" s="2" t="n"/>
       <c r="Y74" s="2" t="n"/>
     </row>
     <row r="75">
@@ -2748,7 +2748,7 @@
       <c r="U75" s="4" t="n"/>
       <c r="V75" s="3" t="n"/>
       <c r="W75" s="4" t="n"/>
-      <c r="X75" s="3" t="n"/>
+      <c r="X75" s="4" t="n"/>
       <c r="Y75" s="4" t="n"/>
     </row>
     <row r="76">
@@ -2775,7 +2775,7 @@
       <c r="U76" s="2" t="n"/>
       <c r="V76" s="3" t="n"/>
       <c r="W76" s="2" t="n"/>
-      <c r="X76" s="3" t="n"/>
+      <c r="X76" s="2" t="n"/>
       <c r="Y76" s="2" t="n"/>
     </row>
     <row r="77">
@@ -2802,7 +2802,7 @@
       <c r="U77" s="4" t="n"/>
       <c r="V77" s="3" t="n"/>
       <c r="W77" s="4" t="n"/>
-      <c r="X77" s="3" t="n"/>
+      <c r="X77" s="4" t="n"/>
       <c r="Y77" s="4" t="n"/>
     </row>
     <row r="78">
@@ -2829,7 +2829,7 @@
       <c r="U78" s="2" t="n"/>
       <c r="V78" s="3" t="n"/>
       <c r="W78" s="2" t="n"/>
-      <c r="X78" s="3" t="n"/>
+      <c r="X78" s="2" t="n"/>
       <c r="Y78" s="2" t="n"/>
     </row>
     <row r="79">
@@ -2856,7 +2856,7 @@
       <c r="U79" s="4" t="n"/>
       <c r="V79" s="3" t="n"/>
       <c r="W79" s="4" t="n"/>
-      <c r="X79" s="3" t="n"/>
+      <c r="X79" s="4" t="n"/>
       <c r="Y79" s="4" t="n"/>
     </row>
     <row r="80">
@@ -2883,7 +2883,7 @@
       <c r="U80" s="2" t="n"/>
       <c r="V80" s="3" t="n"/>
       <c r="W80" s="2" t="n"/>
-      <c r="X80" s="3" t="n"/>
+      <c r="X80" s="2" t="n"/>
       <c r="Y80" s="2" t="n"/>
     </row>
     <row r="81">
@@ -2910,7 +2910,7 @@
       <c r="U81" s="4" t="n"/>
       <c r="V81" s="3" t="n"/>
       <c r="W81" s="4" t="n"/>
-      <c r="X81" s="3" t="n"/>
+      <c r="X81" s="4" t="n"/>
       <c r="Y81" s="4" t="n"/>
     </row>
     <row r="82">
@@ -2937,7 +2937,7 @@
       <c r="U82" s="2" t="n"/>
       <c r="V82" s="3" t="n"/>
       <c r="W82" s="2" t="n"/>
-      <c r="X82" s="3" t="n"/>
+      <c r="X82" s="2" t="n"/>
       <c r="Y82" s="2" t="n"/>
     </row>
     <row r="83">
@@ -2964,7 +2964,7 @@
       <c r="U83" s="4" t="n"/>
       <c r="V83" s="3" t="n"/>
       <c r="W83" s="4" t="n"/>
-      <c r="X83" s="3" t="n"/>
+      <c r="X83" s="4" t="n"/>
       <c r="Y83" s="4" t="n"/>
     </row>
     <row r="84">
@@ -2991,7 +2991,7 @@
       <c r="U84" s="2" t="n"/>
       <c r="V84" s="3" t="n"/>
       <c r="W84" s="2" t="n"/>
-      <c r="X84" s="3" t="n"/>
+      <c r="X84" s="2" t="n"/>
       <c r="Y84" s="2" t="n"/>
     </row>
     <row r="85">
@@ -3018,7 +3018,7 @@
       <c r="U85" s="4" t="n"/>
       <c r="V85" s="3" t="n"/>
       <c r="W85" s="4" t="n"/>
-      <c r="X85" s="3" t="n"/>
+      <c r="X85" s="4" t="n"/>
       <c r="Y85" s="4" t="n"/>
     </row>
     <row r="86">
@@ -3045,7 +3045,7 @@
       <c r="U86" s="2" t="n"/>
       <c r="V86" s="3" t="n"/>
       <c r="W86" s="2" t="n"/>
-      <c r="X86" s="3" t="n"/>
+      <c r="X86" s="2" t="n"/>
       <c r="Y86" s="2" t="n"/>
     </row>
     <row r="87">
@@ -3072,7 +3072,7 @@
       <c r="U87" s="4" t="n"/>
       <c r="V87" s="3" t="n"/>
       <c r="W87" s="4" t="n"/>
-      <c r="X87" s="3" t="n"/>
+      <c r="X87" s="4" t="n"/>
       <c r="Y87" s="4" t="n"/>
     </row>
     <row r="88">
@@ -3099,7 +3099,7 @@
       <c r="U88" s="2" t="n"/>
       <c r="V88" s="3" t="n"/>
       <c r="W88" s="2" t="n"/>
-      <c r="X88" s="3" t="n"/>
+      <c r="X88" s="2" t="n"/>
       <c r="Y88" s="2" t="n"/>
     </row>
     <row r="89">
@@ -3126,7 +3126,7 @@
       <c r="U89" s="4" t="n"/>
       <c r="V89" s="3" t="n"/>
       <c r="W89" s="4" t="n"/>
-      <c r="X89" s="3" t="n"/>
+      <c r="X89" s="4" t="n"/>
       <c r="Y89" s="4" t="n"/>
     </row>
     <row r="90">
@@ -3153,7 +3153,7 @@
       <c r="U90" s="2" t="n"/>
       <c r="V90" s="3" t="n"/>
       <c r="W90" s="2" t="n"/>
-      <c r="X90" s="3" t="n"/>
+      <c r="X90" s="2" t="n"/>
       <c r="Y90" s="2" t="n"/>
     </row>
     <row r="91">
@@ -3180,7 +3180,7 @@
       <c r="U91" s="4" t="n"/>
       <c r="V91" s="3" t="n"/>
       <c r="W91" s="4" t="n"/>
-      <c r="X91" s="3" t="n"/>
+      <c r="X91" s="4" t="n"/>
       <c r="Y91" s="4" t="n"/>
     </row>
     <row r="92">
@@ -3207,7 +3207,7 @@
       <c r="U92" s="2" t="n"/>
       <c r="V92" s="3" t="n"/>
       <c r="W92" s="2" t="n"/>
-      <c r="X92" s="3" t="n"/>
+      <c r="X92" s="2" t="n"/>
       <c r="Y92" s="2" t="n"/>
     </row>
     <row r="93">
@@ -3234,7 +3234,7 @@
       <c r="U93" s="4" t="n"/>
       <c r="V93" s="3" t="n"/>
       <c r="W93" s="4" t="n"/>
-      <c r="X93" s="3" t="n"/>
+      <c r="X93" s="4" t="n"/>
       <c r="Y93" s="4" t="n"/>
     </row>
     <row r="94">
@@ -3261,7 +3261,7 @@
       <c r="U94" s="2" t="n"/>
       <c r="V94" s="3" t="n"/>
       <c r="W94" s="2" t="n"/>
-      <c r="X94" s="3" t="n"/>
+      <c r="X94" s="2" t="n"/>
       <c r="Y94" s="2" t="n"/>
     </row>
     <row r="95">
@@ -3288,7 +3288,7 @@
       <c r="U95" s="4" t="n"/>
       <c r="V95" s="3" t="n"/>
       <c r="W95" s="4" t="n"/>
-      <c r="X95" s="3" t="n"/>
+      <c r="X95" s="4" t="n"/>
       <c r="Y95" s="4" t="n"/>
     </row>
     <row r="96">
@@ -3315,7 +3315,7 @@
       <c r="U96" s="2" t="n"/>
       <c r="V96" s="3" t="n"/>
       <c r="W96" s="2" t="n"/>
-      <c r="X96" s="3" t="n"/>
+      <c r="X96" s="2" t="n"/>
       <c r="Y96" s="2" t="n"/>
     </row>
     <row r="97">
@@ -3342,7 +3342,7 @@
       <c r="U97" s="4" t="n"/>
       <c r="V97" s="3" t="n"/>
       <c r="W97" s="4" t="n"/>
-      <c r="X97" s="3" t="n"/>
+      <c r="X97" s="4" t="n"/>
       <c r="Y97" s="4" t="n"/>
     </row>
     <row r="98">
@@ -3369,7 +3369,7 @@
       <c r="U98" s="2" t="n"/>
       <c r="V98" s="3" t="n"/>
       <c r="W98" s="2" t="n"/>
-      <c r="X98" s="3" t="n"/>
+      <c r="X98" s="2" t="n"/>
       <c r="Y98" s="2" t="n"/>
     </row>
     <row r="99">
@@ -3396,7 +3396,7 @@
       <c r="U99" s="4" t="n"/>
       <c r="V99" s="3" t="n"/>
       <c r="W99" s="4" t="n"/>
-      <c r="X99" s="3" t="n"/>
+      <c r="X99" s="4" t="n"/>
       <c r="Y99" s="4" t="n"/>
     </row>
     <row r="100">
@@ -3423,7 +3423,7 @@
       <c r="U100" s="2" t="n"/>
       <c r="V100" s="3" t="n"/>
       <c r="W100" s="2" t="n"/>
-      <c r="X100" s="3" t="n"/>
+      <c r="X100" s="2" t="n"/>
       <c r="Y100" s="2" t="n"/>
     </row>
     <row r="101">
@@ -3450,7 +3450,7 @@
       <c r="U101" s="4" t="n"/>
       <c r="V101" s="3" t="n"/>
       <c r="W101" s="4" t="n"/>
-      <c r="X101" s="3" t="n"/>
+      <c r="X101" s="4" t="n"/>
       <c r="Y101" s="4" t="n"/>
     </row>
     <row r="102">
@@ -3477,7 +3477,7 @@
       <c r="U102" s="2" t="n"/>
       <c r="V102" s="3" t="n"/>
       <c r="W102" s="2" t="n"/>
-      <c r="X102" s="3" t="n"/>
+      <c r="X102" s="2" t="n"/>
       <c r="Y102" s="2" t="n"/>
     </row>
     <row r="103">
@@ -3504,7 +3504,7 @@
       <c r="U103" s="4" t="n"/>
       <c r="V103" s="3" t="n"/>
       <c r="W103" s="4" t="n"/>
-      <c r="X103" s="3" t="n"/>
+      <c r="X103" s="4" t="n"/>
       <c r="Y103" s="4" t="n"/>
     </row>
     <row r="104">
@@ -3531,7 +3531,7 @@
       <c r="U104" s="2" t="n"/>
       <c r="V104" s="3" t="n"/>
       <c r="W104" s="2" t="n"/>
-      <c r="X104" s="3" t="n"/>
+      <c r="X104" s="2" t="n"/>
       <c r="Y104" s="2" t="n"/>
     </row>
     <row r="105">
@@ -3558,7 +3558,7 @@
       <c r="U105" s="4" t="n"/>
       <c r="V105" s="3" t="n"/>
       <c r="W105" s="4" t="n"/>
-      <c r="X105" s="3" t="n"/>
+      <c r="X105" s="4" t="n"/>
       <c r="Y105" s="4" t="n"/>
     </row>
     <row r="106">
@@ -3585,7 +3585,7 @@
       <c r="U106" s="2" t="n"/>
       <c r="V106" s="3" t="n"/>
       <c r="W106" s="2" t="n"/>
-      <c r="X106" s="3" t="n"/>
+      <c r="X106" s="2" t="n"/>
       <c r="Y106" s="2" t="n"/>
     </row>
     <row r="107">
@@ -3612,7 +3612,7 @@
       <c r="U107" s="4" t="n"/>
       <c r="V107" s="3" t="n"/>
       <c r="W107" s="4" t="n"/>
-      <c r="X107" s="3" t="n"/>
+      <c r="X107" s="4" t="n"/>
       <c r="Y107" s="4" t="n"/>
     </row>
     <row r="108">
@@ -3639,7 +3639,7 @@
       <c r="U108" s="2" t="n"/>
       <c r="V108" s="3" t="n"/>
       <c r="W108" s="2" t="n"/>
-      <c r="X108" s="3" t="n"/>
+      <c r="X108" s="2" t="n"/>
       <c r="Y108" s="2" t="n"/>
     </row>
     <row r="109">
@@ -3666,7 +3666,7 @@
       <c r="U109" s="4" t="n"/>
       <c r="V109" s="3" t="n"/>
       <c r="W109" s="4" t="n"/>
-      <c r="X109" s="3" t="n"/>
+      <c r="X109" s="4" t="n"/>
       <c r="Y109" s="4" t="n"/>
     </row>
     <row r="110">
@@ -3693,7 +3693,7 @@
       <c r="U110" s="2" t="n"/>
       <c r="V110" s="3" t="n"/>
       <c r="W110" s="2" t="n"/>
-      <c r="X110" s="3" t="n"/>
+      <c r="X110" s="2" t="n"/>
       <c r="Y110" s="2" t="n"/>
     </row>
     <row r="111">
@@ -3720,7 +3720,7 @@
       <c r="U111" s="4" t="n"/>
       <c r="V111" s="3" t="n"/>
       <c r="W111" s="4" t="n"/>
-      <c r="X111" s="3" t="n"/>
+      <c r="X111" s="4" t="n"/>
       <c r="Y111" s="4" t="n"/>
     </row>
     <row r="112">
@@ -3747,7 +3747,7 @@
       <c r="U112" s="2" t="n"/>
       <c r="V112" s="3" t="n"/>
       <c r="W112" s="2" t="n"/>
-      <c r="X112" s="3" t="n"/>
+      <c r="X112" s="2" t="n"/>
       <c r="Y112" s="2" t="n"/>
     </row>
     <row r="113">
@@ -3774,7 +3774,7 @@
       <c r="U113" s="4" t="n"/>
       <c r="V113" s="3" t="n"/>
       <c r="W113" s="4" t="n"/>
-      <c r="X113" s="3" t="n"/>
+      <c r="X113" s="4" t="n"/>
       <c r="Y113" s="4" t="n"/>
     </row>
     <row r="114">
@@ -3801,7 +3801,7 @@
       <c r="U114" s="2" t="n"/>
       <c r="V114" s="3" t="n"/>
       <c r="W114" s="2" t="n"/>
-      <c r="X114" s="3" t="n"/>
+      <c r="X114" s="2" t="n"/>
       <c r="Y114" s="2" t="n"/>
     </row>
     <row r="115">
@@ -3828,7 +3828,7 @@
       <c r="U115" s="4" t="n"/>
       <c r="V115" s="3" t="n"/>
       <c r="W115" s="4" t="n"/>
-      <c r="X115" s="3" t="n"/>
+      <c r="X115" s="4" t="n"/>
       <c r="Y115" s="4" t="n"/>
     </row>
     <row r="116">
@@ -3855,7 +3855,7 @@
       <c r="U116" s="2" t="n"/>
       <c r="V116" s="3" t="n"/>
       <c r="W116" s="2" t="n"/>
-      <c r="X116" s="3" t="n"/>
+      <c r="X116" s="2" t="n"/>
       <c r="Y116" s="2" t="n"/>
     </row>
     <row r="117">
@@ -3882,7 +3882,7 @@
       <c r="U117" s="4" t="n"/>
       <c r="V117" s="3" t="n"/>
       <c r="W117" s="4" t="n"/>
-      <c r="X117" s="3" t="n"/>
+      <c r="X117" s="4" t="n"/>
       <c r="Y117" s="4" t="n"/>
     </row>
     <row r="118">
@@ -3909,7 +3909,7 @@
       <c r="U118" s="2" t="n"/>
       <c r="V118" s="3" t="n"/>
       <c r="W118" s="2" t="n"/>
-      <c r="X118" s="3" t="n"/>
+      <c r="X118" s="2" t="n"/>
       <c r="Y118" s="2" t="n"/>
     </row>
     <row r="119">
@@ -3936,7 +3936,7 @@
       <c r="U119" s="4" t="n"/>
       <c r="V119" s="3" t="n"/>
       <c r="W119" s="4" t="n"/>
-      <c r="X119" s="3" t="n"/>
+      <c r="X119" s="4" t="n"/>
       <c r="Y119" s="4" t="n"/>
     </row>
     <row r="120">
@@ -3963,7 +3963,7 @@
       <c r="U120" s="2" t="n"/>
       <c r="V120" s="3" t="n"/>
       <c r="W120" s="2" t="n"/>
-      <c r="X120" s="3" t="n"/>
+      <c r="X120" s="2" t="n"/>
       <c r="Y120" s="2" t="n"/>
     </row>
     <row r="121">
@@ -3990,7 +3990,7 @@
       <c r="U121" s="4" t="n"/>
       <c r="V121" s="3" t="n"/>
       <c r="W121" s="4" t="n"/>
-      <c r="X121" s="3" t="n"/>
+      <c r="X121" s="4" t="n"/>
       <c r="Y121" s="4" t="n"/>
     </row>
     <row r="122">
@@ -4017,7 +4017,7 @@
       <c r="U122" s="2" t="n"/>
       <c r="V122" s="3" t="n"/>
       <c r="W122" s="2" t="n"/>
-      <c r="X122" s="3" t="n"/>
+      <c r="X122" s="2" t="n"/>
       <c r="Y122" s="2" t="n"/>
     </row>
     <row r="123">
@@ -4044,7 +4044,7 @@
       <c r="U123" s="4" t="n"/>
       <c r="V123" s="3" t="n"/>
       <c r="W123" s="4" t="n"/>
-      <c r="X123" s="3" t="n"/>
+      <c r="X123" s="4" t="n"/>
       <c r="Y123" s="4" t="n"/>
     </row>
     <row r="124">
@@ -4071,7 +4071,7 @@
       <c r="U124" s="2" t="n"/>
       <c r="V124" s="3" t="n"/>
       <c r="W124" s="2" t="n"/>
-      <c r="X124" s="3" t="n"/>
+      <c r="X124" s="2" t="n"/>
       <c r="Y124" s="2" t="n"/>
     </row>
     <row r="125">
@@ -4098,7 +4098,7 @@
       <c r="U125" s="4" t="n"/>
       <c r="V125" s="3" t="n"/>
       <c r="W125" s="4" t="n"/>
-      <c r="X125" s="3" t="n"/>
+      <c r="X125" s="4" t="n"/>
       <c r="Y125" s="4" t="n"/>
     </row>
     <row r="126">
@@ -4125,7 +4125,7 @@
       <c r="U126" s="2" t="n"/>
       <c r="V126" s="3" t="n"/>
       <c r="W126" s="2" t="n"/>
-      <c r="X126" s="3" t="n"/>
+      <c r="X126" s="2" t="n"/>
       <c r="Y126" s="2" t="n"/>
     </row>
     <row r="127">
@@ -4152,7 +4152,7 @@
       <c r="U127" s="4" t="n"/>
       <c r="V127" s="3" t="n"/>
       <c r="W127" s="4" t="n"/>
-      <c r="X127" s="3" t="n"/>
+      <c r="X127" s="4" t="n"/>
       <c r="Y127" s="4" t="n"/>
     </row>
     <row r="128">
@@ -4179,7 +4179,7 @@
       <c r="U128" s="2" t="n"/>
       <c r="V128" s="3" t="n"/>
       <c r="W128" s="2" t="n"/>
-      <c r="X128" s="3" t="n"/>
+      <c r="X128" s="2" t="n"/>
       <c r="Y128" s="2" t="n"/>
     </row>
     <row r="129">
@@ -4206,7 +4206,7 @@
       <c r="U129" s="4" t="n"/>
       <c r="V129" s="3" t="n"/>
       <c r="W129" s="4" t="n"/>
-      <c r="X129" s="3" t="n"/>
+      <c r="X129" s="4" t="n"/>
       <c r="Y129" s="4" t="n"/>
     </row>
     <row r="130">
@@ -4233,7 +4233,7 @@
       <c r="U130" s="2" t="n"/>
       <c r="V130" s="3" t="n"/>
       <c r="W130" s="2" t="n"/>
-      <c r="X130" s="3" t="n"/>
+      <c r="X130" s="2" t="n"/>
       <c r="Y130" s="2" t="n"/>
     </row>
     <row r="131">
@@ -4260,7 +4260,7 @@
       <c r="U131" s="4" t="n"/>
       <c r="V131" s="3" t="n"/>
       <c r="W131" s="4" t="n"/>
-      <c r="X131" s="3" t="n"/>
+      <c r="X131" s="4" t="n"/>
       <c r="Y131" s="4" t="n"/>
     </row>
     <row r="132">
@@ -4287,7 +4287,7 @@
       <c r="U132" s="2" t="n"/>
       <c r="V132" s="3" t="n"/>
       <c r="W132" s="2" t="n"/>
-      <c r="X132" s="3" t="n"/>
+      <c r="X132" s="2" t="n"/>
       <c r="Y132" s="2" t="n"/>
     </row>
     <row r="133">
@@ -4314,7 +4314,7 @@
       <c r="U133" s="4" t="n"/>
       <c r="V133" s="3" t="n"/>
       <c r="W133" s="4" t="n"/>
-      <c r="X133" s="3" t="n"/>
+      <c r="X133" s="4" t="n"/>
       <c r="Y133" s="4" t="n"/>
     </row>
     <row r="134">
@@ -4341,7 +4341,7 @@
       <c r="U134" s="2" t="n"/>
       <c r="V134" s="3" t="n"/>
       <c r="W134" s="2" t="n"/>
-      <c r="X134" s="3" t="n"/>
+      <c r="X134" s="2" t="n"/>
       <c r="Y134" s="2" t="n"/>
     </row>
     <row r="135">
@@ -4368,7 +4368,7 @@
       <c r="U135" s="4" t="n"/>
       <c r="V135" s="3" t="n"/>
       <c r="W135" s="4" t="n"/>
-      <c r="X135" s="3" t="n"/>
+      <c r="X135" s="4" t="n"/>
       <c r="Y135" s="4" t="n"/>
     </row>
     <row r="136">
@@ -4395,7 +4395,7 @@
       <c r="U136" s="2" t="n"/>
       <c r="V136" s="3" t="n"/>
       <c r="W136" s="2" t="n"/>
-      <c r="X136" s="3" t="n"/>
+      <c r="X136" s="2" t="n"/>
       <c r="Y136" s="2" t="n"/>
     </row>
     <row r="137">
@@ -4422,7 +4422,7 @@
       <c r="U137" s="4" t="n"/>
       <c r="V137" s="3" t="n"/>
       <c r="W137" s="4" t="n"/>
-      <c r="X137" s="3" t="n"/>
+      <c r="X137" s="4" t="n"/>
       <c r="Y137" s="4" t="n"/>
     </row>
     <row r="138">
@@ -4449,7 +4449,7 @@
       <c r="U138" s="2" t="n"/>
       <c r="V138" s="3" t="n"/>
       <c r="W138" s="2" t="n"/>
-      <c r="X138" s="3" t="n"/>
+      <c r="X138" s="2" t="n"/>
       <c r="Y138" s="2" t="n"/>
     </row>
     <row r="139">
@@ -4476,7 +4476,7 @@
       <c r="U139" s="4" t="n"/>
       <c r="V139" s="3" t="n"/>
       <c r="W139" s="4" t="n"/>
-      <c r="X139" s="3" t="n"/>
+      <c r="X139" s="4" t="n"/>
       <c r="Y139" s="4" t="n"/>
     </row>
     <row r="140">
@@ -4503,7 +4503,7 @@
       <c r="U140" s="2" t="n"/>
       <c r="V140" s="3" t="n"/>
       <c r="W140" s="2" t="n"/>
-      <c r="X140" s="3" t="n"/>
+      <c r="X140" s="2" t="n"/>
       <c r="Y140" s="2" t="n"/>
     </row>
     <row r="141">
@@ -4530,7 +4530,7 @@
       <c r="U141" s="4" t="n"/>
       <c r="V141" s="3" t="n"/>
       <c r="W141" s="4" t="n"/>
-      <c r="X141" s="3" t="n"/>
+      <c r="X141" s="4" t="n"/>
       <c r="Y141" s="4" t="n"/>
     </row>
     <row r="142">
@@ -4557,7 +4557,7 @@
       <c r="U142" s="2" t="n"/>
       <c r="V142" s="3" t="n"/>
       <c r="W142" s="2" t="n"/>
-      <c r="X142" s="3" t="n"/>
+      <c r="X142" s="2" t="n"/>
       <c r="Y142" s="2" t="n"/>
     </row>
     <row r="143">
@@ -4584,7 +4584,7 @@
       <c r="U143" s="4" t="n"/>
       <c r="V143" s="3" t="n"/>
       <c r="W143" s="4" t="n"/>
-      <c r="X143" s="3" t="n"/>
+      <c r="X143" s="4" t="n"/>
       <c r="Y143" s="4" t="n"/>
     </row>
     <row r="144">
@@ -4611,7 +4611,7 @@
       <c r="U144" s="2" t="n"/>
       <c r="V144" s="3" t="n"/>
       <c r="W144" s="2" t="n"/>
-      <c r="X144" s="3" t="n"/>
+      <c r="X144" s="2" t="n"/>
       <c r="Y144" s="2" t="n"/>
     </row>
     <row r="145">
@@ -4638,7 +4638,7 @@
       <c r="U145" s="4" t="n"/>
       <c r="V145" s="3" t="n"/>
       <c r="W145" s="4" t="n"/>
-      <c r="X145" s="3" t="n"/>
+      <c r="X145" s="4" t="n"/>
       <c r="Y145" s="4" t="n"/>
     </row>
     <row r="146">
@@ -4665,7 +4665,7 @@
       <c r="U146" s="2" t="n"/>
       <c r="V146" s="3" t="n"/>
       <c r="W146" s="2" t="n"/>
-      <c r="X146" s="3" t="n"/>
+      <c r="X146" s="2" t="n"/>
       <c r="Y146" s="2" t="n"/>
     </row>
     <row r="147">
@@ -4692,7 +4692,7 @@
       <c r="U147" s="4" t="n"/>
       <c r="V147" s="3" t="n"/>
       <c r="W147" s="4" t="n"/>
-      <c r="X147" s="3" t="n"/>
+      <c r="X147" s="4" t="n"/>
       <c r="Y147" s="4" t="n"/>
     </row>
     <row r="148">
@@ -4719,7 +4719,7 @@
       <c r="U148" s="2" t="n"/>
       <c r="V148" s="3" t="n"/>
       <c r="W148" s="2" t="n"/>
-      <c r="X148" s="3" t="n"/>
+      <c r="X148" s="2" t="n"/>
       <c r="Y148" s="2" t="n"/>
     </row>
     <row r="149">
@@ -4746,7 +4746,7 @@
       <c r="U149" s="4" t="n"/>
       <c r="V149" s="3" t="n"/>
       <c r="W149" s="4" t="n"/>
-      <c r="X149" s="3" t="n"/>
+      <c r="X149" s="4" t="n"/>
       <c r="Y149" s="4" t="n"/>
     </row>
     <row r="150">
@@ -4773,7 +4773,7 @@
       <c r="U150" s="2" t="n"/>
       <c r="V150" s="3" t="n"/>
       <c r="W150" s="2" t="n"/>
-      <c r="X150" s="3" t="n"/>
+      <c r="X150" s="2" t="n"/>
       <c r="Y150" s="2" t="n"/>
     </row>
     <row r="151">
@@ -4800,7 +4800,7 @@
       <c r="U151" s="4" t="n"/>
       <c r="V151" s="3" t="n"/>
       <c r="W151" s="4" t="n"/>
-      <c r="X151" s="3" t="n"/>
+      <c r="X151" s="4" t="n"/>
       <c r="Y151" s="4" t="n"/>
     </row>
     <row r="152">
@@ -4827,7 +4827,7 @@
       <c r="U152" s="2" t="n"/>
       <c r="V152" s="3" t="n"/>
       <c r="W152" s="2" t="n"/>
-      <c r="X152" s="3" t="n"/>
+      <c r="X152" s="2" t="n"/>
       <c r="Y152" s="2" t="n"/>
     </row>
     <row r="153">
@@ -4854,7 +4854,7 @@
       <c r="U153" s="4" t="n"/>
       <c r="V153" s="3" t="n"/>
       <c r="W153" s="4" t="n"/>
-      <c r="X153" s="3" t="n"/>
+      <c r="X153" s="4" t="n"/>
       <c r="Y153" s="4" t="n"/>
     </row>
     <row r="154">
@@ -4881,7 +4881,7 @@
       <c r="U154" s="2" t="n"/>
       <c r="V154" s="3" t="n"/>
       <c r="W154" s="2" t="n"/>
-      <c r="X154" s="3" t="n"/>
+      <c r="X154" s="2" t="n"/>
       <c r="Y154" s="2" t="n"/>
     </row>
     <row r="155">
@@ -4908,7 +4908,7 @@
       <c r="U155" s="4" t="n"/>
       <c r="V155" s="3" t="n"/>
       <c r="W155" s="4" t="n"/>
-      <c r="X155" s="3" t="n"/>
+      <c r="X155" s="4" t="n"/>
       <c r="Y155" s="4" t="n"/>
     </row>
     <row r="156">
@@ -4935,7 +4935,7 @@
       <c r="U156" s="2" t="n"/>
       <c r="V156" s="3" t="n"/>
       <c r="W156" s="2" t="n"/>
-      <c r="X156" s="3" t="n"/>
+      <c r="X156" s="2" t="n"/>
       <c r="Y156" s="2" t="n"/>
     </row>
     <row r="157">
@@ -4962,7 +4962,7 @@
       <c r="U157" s="4" t="n"/>
       <c r="V157" s="3" t="n"/>
       <c r="W157" s="4" t="n"/>
-      <c r="X157" s="3" t="n"/>
+      <c r="X157" s="4" t="n"/>
       <c r="Y157" s="4" t="n"/>
     </row>
     <row r="158">
@@ -4989,7 +4989,7 @@
       <c r="U158" s="2" t="n"/>
       <c r="V158" s="3" t="n"/>
       <c r="W158" s="2" t="n"/>
-      <c r="X158" s="3" t="n"/>
+      <c r="X158" s="2" t="n"/>
       <c r="Y158" s="2" t="n"/>
     </row>
     <row r="159">
@@ -5016,7 +5016,7 @@
       <c r="U159" s="4" t="n"/>
       <c r="V159" s="3" t="n"/>
       <c r="W159" s="4" t="n"/>
-      <c r="X159" s="3" t="n"/>
+      <c r="X159" s="4" t="n"/>
       <c r="Y159" s="4" t="n"/>
     </row>
     <row r="160">
@@ -5043,7 +5043,7 @@
       <c r="U160" s="2" t="n"/>
       <c r="V160" s="3" t="n"/>
       <c r="W160" s="2" t="n"/>
-      <c r="X160" s="3" t="n"/>
+      <c r="X160" s="2" t="n"/>
       <c r="Y160" s="2" t="n"/>
     </row>
     <row r="161">
@@ -5070,7 +5070,7 @@
       <c r="U161" s="4" t="n"/>
       <c r="V161" s="3" t="n"/>
       <c r="W161" s="4" t="n"/>
-      <c r="X161" s="3" t="n"/>
+      <c r="X161" s="4" t="n"/>
       <c r="Y161" s="4" t="n"/>
     </row>
     <row r="162">
@@ -5097,7 +5097,7 @@
       <c r="U162" s="2" t="n"/>
       <c r="V162" s="3" t="n"/>
       <c r="W162" s="2" t="n"/>
-      <c r="X162" s="3" t="n"/>
+      <c r="X162" s="2" t="n"/>
       <c r="Y162" s="2" t="n"/>
     </row>
     <row r="163">
@@ -5124,7 +5124,7 @@
       <c r="U163" s="4" t="n"/>
       <c r="V163" s="3" t="n"/>
       <c r="W163" s="4" t="n"/>
-      <c r="X163" s="3" t="n"/>
+      <c r="X163" s="4" t="n"/>
       <c r="Y163" s="4" t="n"/>
     </row>
     <row r="164">
@@ -5151,7 +5151,7 @@
       <c r="U164" s="2" t="n"/>
       <c r="V164" s="3" t="n"/>
       <c r="W164" s="2" t="n"/>
-      <c r="X164" s="3" t="n"/>
+      <c r="X164" s="2" t="n"/>
       <c r="Y164" s="2" t="n"/>
     </row>
     <row r="165">
@@ -5178,7 +5178,7 @@
       <c r="U165" s="4" t="n"/>
       <c r="V165" s="3" t="n"/>
       <c r="W165" s="4" t="n"/>
-      <c r="X165" s="3" t="n"/>
+      <c r="X165" s="4" t="n"/>
       <c r="Y165" s="4" t="n"/>
     </row>
     <row r="166">
@@ -5205,7 +5205,7 @@
       <c r="U166" s="2" t="n"/>
       <c r="V166" s="3" t="n"/>
       <c r="W166" s="2" t="n"/>
-      <c r="X166" s="3" t="n"/>
+      <c r="X166" s="2" t="n"/>
       <c r="Y166" s="2" t="n"/>
     </row>
     <row r="167">
@@ -5232,7 +5232,7 @@
       <c r="U167" s="4" t="n"/>
       <c r="V167" s="3" t="n"/>
       <c r="W167" s="4" t="n"/>
-      <c r="X167" s="3" t="n"/>
+      <c r="X167" s="4" t="n"/>
       <c r="Y167" s="4" t="n"/>
     </row>
     <row r="168">
@@ -5259,7 +5259,7 @@
       <c r="U168" s="2" t="n"/>
       <c r="V168" s="3" t="n"/>
       <c r="W168" s="2" t="n"/>
-      <c r="X168" s="3" t="n"/>
+      <c r="X168" s="2" t="n"/>
       <c r="Y168" s="2" t="n"/>
     </row>
     <row r="169">
@@ -5286,7 +5286,7 @@
       <c r="U169" s="4" t="n"/>
       <c r="V169" s="3" t="n"/>
       <c r="W169" s="4" t="n"/>
-      <c r="X169" s="3" t="n"/>
+      <c r="X169" s="4" t="n"/>
       <c r="Y169" s="4" t="n"/>
     </row>
     <row r="170">
@@ -5313,7 +5313,7 @@
       <c r="U170" s="2" t="n"/>
       <c r="V170" s="3" t="n"/>
       <c r="W170" s="2" t="n"/>
-      <c r="X170" s="3" t="n"/>
+      <c r="X170" s="2" t="n"/>
       <c r="Y170" s="2" t="n"/>
     </row>
     <row r="171">
@@ -5340,7 +5340,7 @@
       <c r="U171" s="4" t="n"/>
       <c r="V171" s="3" t="n"/>
       <c r="W171" s="4" t="n"/>
-      <c r="X171" s="3" t="n"/>
+      <c r="X171" s="4" t="n"/>
       <c r="Y171" s="4" t="n"/>
     </row>
     <row r="172">
@@ -5367,7 +5367,7 @@
       <c r="U172" s="2" t="n"/>
       <c r="V172" s="3" t="n"/>
       <c r="W172" s="2" t="n"/>
-      <c r="X172" s="3" t="n"/>
+      <c r="X172" s="2" t="n"/>
       <c r="Y172" s="2" t="n"/>
     </row>
     <row r="173">
@@ -5394,7 +5394,7 @@
       <c r="U173" s="4" t="n"/>
       <c r="V173" s="3" t="n"/>
       <c r="W173" s="4" t="n"/>
-      <c r="X173" s="3" t="n"/>
+      <c r="X173" s="4" t="n"/>
       <c r="Y173" s="4" t="n"/>
     </row>
     <row r="174">
@@ -5421,7 +5421,7 @@
       <c r="U174" s="2" t="n"/>
       <c r="V174" s="3" t="n"/>
       <c r="W174" s="2" t="n"/>
-      <c r="X174" s="3" t="n"/>
+      <c r="X174" s="2" t="n"/>
       <c r="Y174" s="2" t="n"/>
     </row>
     <row r="175">
@@ -5448,7 +5448,7 @@
       <c r="U175" s="4" t="n"/>
       <c r="V175" s="3" t="n"/>
       <c r="W175" s="4" t="n"/>
-      <c r="X175" s="3" t="n"/>
+      <c r="X175" s="4" t="n"/>
       <c r="Y175" s="4" t="n"/>
     </row>
     <row r="176">
@@ -5475,7 +5475,7 @@
       <c r="U176" s="2" t="n"/>
       <c r="V176" s="3" t="n"/>
       <c r="W176" s="2" t="n"/>
-      <c r="X176" s="3" t="n"/>
+      <c r="X176" s="2" t="n"/>
       <c r="Y176" s="2" t="n"/>
     </row>
     <row r="177">
@@ -5502,7 +5502,7 @@
       <c r="U177" s="4" t="n"/>
       <c r="V177" s="3" t="n"/>
       <c r="W177" s="4" t="n"/>
-      <c r="X177" s="3" t="n"/>
+      <c r="X177" s="4" t="n"/>
       <c r="Y177" s="4" t="n"/>
     </row>
     <row r="178">
@@ -5529,7 +5529,7 @@
       <c r="U178" s="2" t="n"/>
       <c r="V178" s="3" t="n"/>
       <c r="W178" s="2" t="n"/>
-      <c r="X178" s="3" t="n"/>
+      <c r="X178" s="2" t="n"/>
       <c r="Y178" s="2" t="n"/>
     </row>
     <row r="179">
@@ -5556,7 +5556,7 @@
       <c r="U179" s="4" t="n"/>
       <c r="V179" s="3" t="n"/>
       <c r="W179" s="4" t="n"/>
-      <c r="X179" s="3" t="n"/>
+      <c r="X179" s="4" t="n"/>
       <c r="Y179" s="4" t="n"/>
     </row>
     <row r="180">
@@ -5583,7 +5583,7 @@
       <c r="U180" s="2" t="n"/>
       <c r="V180" s="3" t="n"/>
       <c r="W180" s="2" t="n"/>
-      <c r="X180" s="3" t="n"/>
+      <c r="X180" s="2" t="n"/>
       <c r="Y180" s="2" t="n"/>
     </row>
     <row r="181">
@@ -5610,7 +5610,7 @@
       <c r="U181" s="4" t="n"/>
       <c r="V181" s="3" t="n"/>
       <c r="W181" s="4" t="n"/>
-      <c r="X181" s="3" t="n"/>
+      <c r="X181" s="4" t="n"/>
       <c r="Y181" s="4" t="n"/>
     </row>
     <row r="182">
@@ -5637,7 +5637,7 @@
       <c r="U182" s="2" t="n"/>
       <c r="V182" s="3" t="n"/>
       <c r="W182" s="2" t="n"/>
-      <c r="X182" s="3" t="n"/>
+      <c r="X182" s="2" t="n"/>
       <c r="Y182" s="2" t="n"/>
     </row>
     <row r="183">
@@ -5664,7 +5664,7 @@
       <c r="U183" s="4" t="n"/>
       <c r="V183" s="3" t="n"/>
       <c r="W183" s="4" t="n"/>
-      <c r="X183" s="3" t="n"/>
+      <c r="X183" s="4" t="n"/>
       <c r="Y183" s="4" t="n"/>
     </row>
     <row r="184">
@@ -5691,7 +5691,7 @@
       <c r="U184" s="2" t="n"/>
       <c r="V184" s="3" t="n"/>
       <c r="W184" s="2" t="n"/>
-      <c r="X184" s="3" t="n"/>
+      <c r="X184" s="2" t="n"/>
       <c r="Y184" s="2" t="n"/>
     </row>
     <row r="185">
@@ -5718,7 +5718,7 @@
       <c r="U185" s="4" t="n"/>
       <c r="V185" s="3" t="n"/>
       <c r="W185" s="4" t="n"/>
-      <c r="X185" s="3" t="n"/>
+      <c r="X185" s="4" t="n"/>
       <c r="Y185" s="4" t="n"/>
     </row>
     <row r="186">
@@ -5745,7 +5745,7 @@
       <c r="U186" s="2" t="n"/>
       <c r="V186" s="3" t="n"/>
       <c r="W186" s="2" t="n"/>
-      <c r="X186" s="3" t="n"/>
+      <c r="X186" s="2" t="n"/>
       <c r="Y186" s="2" t="n"/>
     </row>
     <row r="187">
@@ -5772,7 +5772,7 @@
       <c r="U187" s="4" t="n"/>
       <c r="V187" s="3" t="n"/>
       <c r="W187" s="4" t="n"/>
-      <c r="X187" s="3" t="n"/>
+      <c r="X187" s="4" t="n"/>
       <c r="Y187" s="4" t="n"/>
     </row>
     <row r="188">
@@ -5799,7 +5799,7 @@
       <c r="U188" s="2" t="n"/>
       <c r="V188" s="3" t="n"/>
       <c r="W188" s="2" t="n"/>
-      <c r="X188" s="3" t="n"/>
+      <c r="X188" s="2" t="n"/>
       <c r="Y188" s="2" t="n"/>
     </row>
     <row r="189">
@@ -5826,7 +5826,7 @@
       <c r="U189" s="4" t="n"/>
       <c r="V189" s="3" t="n"/>
       <c r="W189" s="4" t="n"/>
-      <c r="X189" s="3" t="n"/>
+      <c r="X189" s="4" t="n"/>
       <c r="Y189" s="4" t="n"/>
     </row>
     <row r="190">
@@ -5853,7 +5853,7 @@
       <c r="U190" s="2" t="n"/>
       <c r="V190" s="3" t="n"/>
       <c r="W190" s="2" t="n"/>
-      <c r="X190" s="3" t="n"/>
+      <c r="X190" s="2" t="n"/>
       <c r="Y190" s="2" t="n"/>
     </row>
     <row r="191">
@@ -5880,7 +5880,7 @@
       <c r="U191" s="4" t="n"/>
       <c r="V191" s="3" t="n"/>
       <c r="W191" s="4" t="n"/>
-      <c r="X191" s="3" t="n"/>
+      <c r="X191" s="4" t="n"/>
       <c r="Y191" s="4" t="n"/>
     </row>
     <row r="192">
@@ -5907,7 +5907,7 @@
       <c r="U192" s="2" t="n"/>
       <c r="V192" s="3" t="n"/>
       <c r="W192" s="2" t="n"/>
-      <c r="X192" s="3" t="n"/>
+      <c r="X192" s="2" t="n"/>
       <c r="Y192" s="2" t="n"/>
     </row>
     <row r="193">
@@ -5934,7 +5934,7 @@
       <c r="U193" s="4" t="n"/>
       <c r="V193" s="3" t="n"/>
       <c r="W193" s="4" t="n"/>
-      <c r="X193" s="3" t="n"/>
+      <c r="X193" s="4" t="n"/>
       <c r="Y193" s="4" t="n"/>
     </row>
     <row r="194">
@@ -5961,7 +5961,7 @@
       <c r="U194" s="2" t="n"/>
       <c r="V194" s="3" t="n"/>
       <c r="W194" s="2" t="n"/>
-      <c r="X194" s="3" t="n"/>
+      <c r="X194" s="2" t="n"/>
       <c r="Y194" s="2" t="n"/>
     </row>
     <row r="195">
@@ -5988,7 +5988,7 @@
       <c r="U195" s="4" t="n"/>
       <c r="V195" s="3" t="n"/>
       <c r="W195" s="4" t="n"/>
-      <c r="X195" s="3" t="n"/>
+      <c r="X195" s="4" t="n"/>
       <c r="Y195" s="4" t="n"/>
     </row>
     <row r="196">
@@ -6015,7 +6015,7 @@
       <c r="U196" s="2" t="n"/>
       <c r="V196" s="3" t="n"/>
       <c r="W196" s="2" t="n"/>
-      <c r="X196" s="3" t="n"/>
+      <c r="X196" s="2" t="n"/>
       <c r="Y196" s="2" t="n"/>
     </row>
     <row r="197">
@@ -6042,7 +6042,7 @@
       <c r="U197" s="4" t="n"/>
       <c r="V197" s="3" t="n"/>
       <c r="W197" s="4" t="n"/>
-      <c r="X197" s="3" t="n"/>
+      <c r="X197" s="4" t="n"/>
       <c r="Y197" s="4" t="n"/>
     </row>
     <row r="198">
@@ -6069,7 +6069,7 @@
       <c r="U198" s="2" t="n"/>
       <c r="V198" s="3" t="n"/>
       <c r="W198" s="2" t="n"/>
-      <c r="X198" s="3" t="n"/>
+      <c r="X198" s="2" t="n"/>
       <c r="Y198" s="2" t="n"/>
     </row>
     <row r="199">
@@ -6096,7 +6096,7 @@
       <c r="U199" s="4" t="n"/>
       <c r="V199" s="3" t="n"/>
       <c r="W199" s="4" t="n"/>
-      <c r="X199" s="3" t="n"/>
+      <c r="X199" s="4" t="n"/>
       <c r="Y199" s="4" t="n"/>
     </row>
     <row r="200">
@@ -6123,7 +6123,7 @@
       <c r="U200" s="2" t="n"/>
       <c r="V200" s="3" t="n"/>
       <c r="W200" s="2" t="n"/>
-      <c r="X200" s="3" t="n"/>
+      <c r="X200" s="2" t="n"/>
       <c r="Y200" s="2" t="n"/>
     </row>
     <row r="201">
@@ -6150,7 +6150,7 @@
       <c r="U201" s="4" t="n"/>
       <c r="V201" s="3" t="n"/>
       <c r="W201" s="4" t="n"/>
-      <c r="X201" s="3" t="n"/>
+      <c r="X201" s="4" t="n"/>
       <c r="Y201" s="4" t="n"/>
     </row>
     <row r="202">
@@ -6177,7 +6177,7 @@
       <c r="U202" s="2" t="n"/>
       <c r="V202" s="3" t="n"/>
       <c r="W202" s="2" t="n"/>
-      <c r="X202" s="3" t="n"/>
+      <c r="X202" s="2" t="n"/>
       <c r="Y202" s="2" t="n"/>
     </row>
     <row r="203">
@@ -6204,7 +6204,7 @@
       <c r="U203" s="4" t="n"/>
       <c r="V203" s="3" t="n"/>
       <c r="W203" s="4" t="n"/>
-      <c r="X203" s="3" t="n"/>
+      <c r="X203" s="4" t="n"/>
       <c r="Y203" s="4" t="n"/>
     </row>
     <row r="204">
@@ -6231,7 +6231,7 @@
       <c r="U204" s="2" t="n"/>
       <c r="V204" s="3" t="n"/>
       <c r="W204" s="2" t="n"/>
-      <c r="X204" s="3" t="n"/>
+      <c r="X204" s="2" t="n"/>
       <c r="Y204" s="2" t="n"/>
     </row>
     <row r="205">
@@ -6258,7 +6258,7 @@
       <c r="U205" s="4" t="n"/>
       <c r="V205" s="3" t="n"/>
       <c r="W205" s="4" t="n"/>
-      <c r="X205" s="3" t="n"/>
+      <c r="X205" s="4" t="n"/>
       <c r="Y205" s="4" t="n"/>
     </row>
     <row r="206">
@@ -6285,7 +6285,7 @@
       <c r="U206" s="2" t="n"/>
       <c r="V206" s="3" t="n"/>
       <c r="W206" s="2" t="n"/>
-      <c r="X206" s="3" t="n"/>
+      <c r="X206" s="2" t="n"/>
       <c r="Y206" s="2" t="n"/>
     </row>
     <row r="207">
@@ -6312,7 +6312,7 @@
       <c r="U207" s="4" t="n"/>
       <c r="V207" s="3" t="n"/>
       <c r="W207" s="4" t="n"/>
-      <c r="X207" s="3" t="n"/>
+      <c r="X207" s="4" t="n"/>
       <c r="Y207" s="4" t="n"/>
     </row>
     <row r="208">
@@ -6339,7 +6339,7 @@
       <c r="U208" s="2" t="n"/>
       <c r="V208" s="3" t="n"/>
       <c r="W208" s="2" t="n"/>
-      <c r="X208" s="3" t="n"/>
+      <c r="X208" s="2" t="n"/>
       <c r="Y208" s="2" t="n"/>
     </row>
     <row r="209">
@@ -6366,7 +6366,7 @@
       <c r="U209" s="4" t="n"/>
       <c r="V209" s="3" t="n"/>
       <c r="W209" s="4" t="n"/>
-      <c r="X209" s="3" t="n"/>
+      <c r="X209" s="4" t="n"/>
       <c r="Y209" s="4" t="n"/>
     </row>
     <row r="210">
@@ -6393,7 +6393,7 @@
       <c r="U210" s="2" t="n"/>
       <c r="V210" s="3" t="n"/>
       <c r="W210" s="2" t="n"/>
-      <c r="X210" s="3" t="n"/>
+      <c r="X210" s="2" t="n"/>
       <c r="Y210" s="2" t="n"/>
     </row>
     <row r="211">
@@ -6420,7 +6420,7 @@
       <c r="U211" s="4" t="n"/>
       <c r="V211" s="3" t="n"/>
       <c r="W211" s="4" t="n"/>
-      <c r="X211" s="3" t="n"/>
+      <c r="X211" s="4" t="n"/>
       <c r="Y211" s="4" t="n"/>
     </row>
     <row r="212">
@@ -6447,7 +6447,7 @@
       <c r="U212" s="2" t="n"/>
       <c r="V212" s="3" t="n"/>
       <c r="W212" s="2" t="n"/>
-      <c r="X212" s="3" t="n"/>
+      <c r="X212" s="2" t="n"/>
       <c r="Y212" s="2" t="n"/>
     </row>
     <row r="213">
@@ -6474,7 +6474,7 @@
       <c r="U213" s="4" t="n"/>
       <c r="V213" s="3" t="n"/>
       <c r="W213" s="4" t="n"/>
-      <c r="X213" s="3" t="n"/>
+      <c r="X213" s="4" t="n"/>
       <c r="Y213" s="4" t="n"/>
     </row>
     <row r="214">
@@ -6501,7 +6501,7 @@
       <c r="U214" s="2" t="n"/>
       <c r="V214" s="3" t="n"/>
       <c r="W214" s="2" t="n"/>
-      <c r="X214" s="3" t="n"/>
+      <c r="X214" s="2" t="n"/>
       <c r="Y214" s="2" t="n"/>
     </row>
     <row r="215">
@@ -6528,7 +6528,7 @@
       <c r="U215" s="4" t="n"/>
       <c r="V215" s="3" t="n"/>
       <c r="W215" s="4" t="n"/>
-      <c r="X215" s="3" t="n"/>
+      <c r="X215" s="4" t="n"/>
       <c r="Y215" s="4" t="n"/>
     </row>
     <row r="216">
@@ -6555,7 +6555,7 @@
       <c r="U216" s="2" t="n"/>
       <c r="V216" s="3" t="n"/>
       <c r="W216" s="2" t="n"/>
-      <c r="X216" s="3" t="n"/>
+      <c r="X216" s="2" t="n"/>
       <c r="Y216" s="2" t="n"/>
     </row>
     <row r="217">
@@ -6582,7 +6582,7 @@
       <c r="U217" s="4" t="n"/>
       <c r="V217" s="3" t="n"/>
       <c r="W217" s="4" t="n"/>
-      <c r="X217" s="3" t="n"/>
+      <c r="X217" s="4" t="n"/>
       <c r="Y217" s="4" t="n"/>
     </row>
     <row r="218">
@@ -6609,7 +6609,7 @@
       <c r="U218" s="2" t="n"/>
       <c r="V218" s="3" t="n"/>
       <c r="W218" s="2" t="n"/>
-      <c r="X218" s="3" t="n"/>
+      <c r="X218" s="2" t="n"/>
       <c r="Y218" s="2" t="n"/>
     </row>
     <row r="219">
@@ -6636,7 +6636,7 @@
       <c r="U219" s="4" t="n"/>
       <c r="V219" s="3" t="n"/>
       <c r="W219" s="4" t="n"/>
-      <c r="X219" s="3" t="n"/>
+      <c r="X219" s="4" t="n"/>
       <c r="Y219" s="4" t="n"/>
     </row>
     <row r="220">
@@ -6663,7 +6663,7 @@
       <c r="U220" s="2" t="n"/>
       <c r="V220" s="3" t="n"/>
       <c r="W220" s="2" t="n"/>
-      <c r="X220" s="3" t="n"/>
+      <c r="X220" s="2" t="n"/>
       <c r="Y220" s="2" t="n"/>
     </row>
     <row r="221">
@@ -6690,7 +6690,7 @@
       <c r="U221" s="4" t="n"/>
       <c r="V221" s="3" t="n"/>
       <c r="W221" s="4" t="n"/>
-      <c r="X221" s="3" t="n"/>
+      <c r="X221" s="4" t="n"/>
       <c r="Y221" s="4" t="n"/>
     </row>
     <row r="222">
@@ -6717,7 +6717,7 @@
       <c r="U222" s="2" t="n"/>
       <c r="V222" s="3" t="n"/>
       <c r="W222" s="2" t="n"/>
-      <c r="X222" s="3" t="n"/>
+      <c r="X222" s="2" t="n"/>
       <c r="Y222" s="2" t="n"/>
     </row>
     <row r="223">
@@ -6744,7 +6744,7 @@
       <c r="U223" s="4" t="n"/>
       <c r="V223" s="3" t="n"/>
       <c r="W223" s="4" t="n"/>
-      <c r="X223" s="3" t="n"/>
+      <c r="X223" s="4" t="n"/>
       <c r="Y223" s="4" t="n"/>
     </row>
     <row r="224">
@@ -6771,7 +6771,7 @@
       <c r="U224" s="2" t="n"/>
       <c r="V224" s="3" t="n"/>
       <c r="W224" s="2" t="n"/>
-      <c r="X224" s="3" t="n"/>
+      <c r="X224" s="2" t="n"/>
       <c r="Y224" s="2" t="n"/>
     </row>
     <row r="225">
@@ -6798,7 +6798,7 @@
       <c r="U225" s="4" t="n"/>
       <c r="V225" s="3" t="n"/>
       <c r="W225" s="4" t="n"/>
-      <c r="X225" s="3" t="n"/>
+      <c r="X225" s="4" t="n"/>
       <c r="Y225" s="4" t="n"/>
     </row>
     <row r="226">
@@ -6825,7 +6825,7 @@
       <c r="U226" s="2" t="n"/>
       <c r="V226" s="3" t="n"/>
       <c r="W226" s="2" t="n"/>
-      <c r="X226" s="3" t="n"/>
+      <c r="X226" s="2" t="n"/>
       <c r="Y226" s="2" t="n"/>
     </row>
     <row r="227">
@@ -6852,7 +6852,7 @@
       <c r="U227" s="4" t="n"/>
       <c r="V227" s="3" t="n"/>
       <c r="W227" s="4" t="n"/>
-      <c r="X227" s="3" t="n"/>
+      <c r="X227" s="4" t="n"/>
       <c r="Y227" s="4" t="n"/>
     </row>
     <row r="228">
@@ -6879,7 +6879,7 @@
       <c r="U228" s="2" t="n"/>
       <c r="V228" s="3" t="n"/>
       <c r="W228" s="2" t="n"/>
-      <c r="X228" s="3" t="n"/>
+      <c r="X228" s="2" t="n"/>
       <c r="Y228" s="2" t="n"/>
     </row>
     <row r="229">
@@ -6906,7 +6906,7 @@
       <c r="U229" s="4" t="n"/>
       <c r="V229" s="3" t="n"/>
       <c r="W229" s="4" t="n"/>
-      <c r="X229" s="3" t="n"/>
+      <c r="X229" s="4" t="n"/>
       <c r="Y229" s="4" t="n"/>
     </row>
     <row r="230">
@@ -6933,7 +6933,7 @@
       <c r="U230" s="2" t="n"/>
       <c r="V230" s="3" t="n"/>
       <c r="W230" s="2" t="n"/>
-      <c r="X230" s="3" t="n"/>
+      <c r="X230" s="2" t="n"/>
       <c r="Y230" s="2" t="n"/>
     </row>
     <row r="231">
@@ -6960,7 +6960,7 @@
       <c r="U231" s="4" t="n"/>
       <c r="V231" s="3" t="n"/>
       <c r="W231" s="4" t="n"/>
-      <c r="X231" s="3" t="n"/>
+      <c r="X231" s="4" t="n"/>
       <c r="Y231" s="4" t="n"/>
     </row>
     <row r="232">
@@ -6987,7 +6987,7 @@
       <c r="U232" s="2" t="n"/>
       <c r="V232" s="3" t="n"/>
       <c r="W232" s="2" t="n"/>
-      <c r="X232" s="3" t="n"/>
+      <c r="X232" s="2" t="n"/>
       <c r="Y232" s="2" t="n"/>
     </row>
     <row r="233">
@@ -7014,7 +7014,7 @@
       <c r="U233" s="4" t="n"/>
       <c r="V233" s="3" t="n"/>
       <c r="W233" s="4" t="n"/>
-      <c r="X233" s="3" t="n"/>
+      <c r="X233" s="4" t="n"/>
       <c r="Y233" s="4" t="n"/>
     </row>
     <row r="234">
@@ -7041,7 +7041,7 @@
       <c r="U234" s="2" t="n"/>
       <c r="V234" s="3" t="n"/>
       <c r="W234" s="2" t="n"/>
-      <c r="X234" s="3" t="n"/>
+      <c r="X234" s="2" t="n"/>
       <c r="Y234" s="2" t="n"/>
     </row>
     <row r="235">
@@ -7068,7 +7068,7 @@
       <c r="U235" s="4" t="n"/>
       <c r="V235" s="3" t="n"/>
       <c r="W235" s="4" t="n"/>
-      <c r="X235" s="3" t="n"/>
+      <c r="X235" s="4" t="n"/>
       <c r="Y235" s="4" t="n"/>
     </row>
     <row r="236">
@@ -7095,7 +7095,7 @@
       <c r="U236" s="2" t="n"/>
       <c r="V236" s="3" t="n"/>
       <c r="W236" s="2" t="n"/>
-      <c r="X236" s="3" t="n"/>
+      <c r="X236" s="2" t="n"/>
       <c r="Y236" s="2" t="n"/>
     </row>
     <row r="237">
@@ -7122,7 +7122,7 @@
       <c r="U237" s="4" t="n"/>
       <c r="V237" s="3" t="n"/>
       <c r="W237" s="4" t="n"/>
-      <c r="X237" s="3" t="n"/>
+      <c r="X237" s="4" t="n"/>
       <c r="Y237" s="4" t="n"/>
     </row>
     <row r="238">
@@ -7149,7 +7149,7 @@
       <c r="U238" s="2" t="n"/>
       <c r="V238" s="3" t="n"/>
       <c r="W238" s="2" t="n"/>
-      <c r="X238" s="3" t="n"/>
+      <c r="X238" s="2" t="n"/>
       <c r="Y238" s="2" t="n"/>
     </row>
     <row r="239">
@@ -7176,7 +7176,7 @@
       <c r="U239" s="4" t="n"/>
       <c r="V239" s="3" t="n"/>
       <c r="W239" s="4" t="n"/>
-      <c r="X239" s="3" t="n"/>
+      <c r="X239" s="4" t="n"/>
       <c r="Y239" s="4" t="n"/>
     </row>
     <row r="240">
@@ -7203,7 +7203,7 @@
       <c r="U240" s="2" t="n"/>
       <c r="V240" s="3" t="n"/>
       <c r="W240" s="2" t="n"/>
-      <c r="X240" s="3" t="n"/>
+      <c r="X240" s="2" t="n"/>
       <c r="Y240" s="2" t="n"/>
     </row>
     <row r="241">
@@ -7230,7 +7230,7 @@
       <c r="U241" s="4" t="n"/>
       <c r="V241" s="3" t="n"/>
       <c r="W241" s="4" t="n"/>
-      <c r="X241" s="3" t="n"/>
+      <c r="X241" s="4" t="n"/>
       <c r="Y241" s="4" t="n"/>
     </row>
     <row r="242">
@@ -7257,7 +7257,7 @@
       <c r="U242" s="2" t="n"/>
       <c r="V242" s="3" t="n"/>
       <c r="W242" s="2" t="n"/>
-      <c r="X242" s="3" t="n"/>
+      <c r="X242" s="2" t="n"/>
       <c r="Y242" s="2" t="n"/>
     </row>
     <row r="243">
@@ -7284,7 +7284,7 @@
       <c r="U243" s="4" t="n"/>
       <c r="V243" s="3" t="n"/>
       <c r="W243" s="4" t="n"/>
-      <c r="X243" s="3" t="n"/>
+      <c r="X243" s="4" t="n"/>
       <c r="Y243" s="4" t="n"/>
     </row>
     <row r="244">
@@ -7311,7 +7311,7 @@
       <c r="U244" s="2" t="n"/>
       <c r="V244" s="3" t="n"/>
       <c r="W244" s="2" t="n"/>
-      <c r="X244" s="3" t="n"/>
+      <c r="X244" s="2" t="n"/>
       <c r="Y244" s="2" t="n"/>
     </row>
     <row r="245">
@@ -7338,7 +7338,7 @@
       <c r="U245" s="4" t="n"/>
       <c r="V245" s="3" t="n"/>
       <c r="W245" s="4" t="n"/>
-      <c r="X245" s="3" t="n"/>
+      <c r="X245" s="4" t="n"/>
       <c r="Y245" s="4" t="n"/>
     </row>
     <row r="246">
@@ -7365,7 +7365,7 @@
       <c r="U246" s="2" t="n"/>
       <c r="V246" s="3" t="n"/>
       <c r="W246" s="2" t="n"/>
-      <c r="X246" s="3" t="n"/>
+      <c r="X246" s="2" t="n"/>
       <c r="Y246" s="2" t="n"/>
     </row>
     <row r="247">
@@ -7392,7 +7392,7 @@
       <c r="U247" s="4" t="n"/>
       <c r="V247" s="3" t="n"/>
       <c r="W247" s="4" t="n"/>
-      <c r="X247" s="3" t="n"/>
+      <c r="X247" s="4" t="n"/>
       <c r="Y247" s="4" t="n"/>
     </row>
     <row r="248">
@@ -7419,7 +7419,7 @@
       <c r="U248" s="2" t="n"/>
       <c r="V248" s="3" t="n"/>
       <c r="W248" s="2" t="n"/>
-      <c r="X248" s="3" t="n"/>
+      <c r="X248" s="2" t="n"/>
       <c r="Y248" s="2" t="n"/>
     </row>
     <row r="249">
@@ -7446,7 +7446,7 @@
       <c r="U249" s="4" t="n"/>
       <c r="V249" s="3" t="n"/>
       <c r="W249" s="4" t="n"/>
-      <c r="X249" s="3" t="n"/>
+      <c r="X249" s="4" t="n"/>
       <c r="Y249" s="4" t="n"/>
     </row>
     <row r="250">
@@ -7473,7 +7473,7 @@
       <c r="U250" s="2" t="n"/>
       <c r="V250" s="3" t="n"/>
       <c r="W250" s="2" t="n"/>
-      <c r="X250" s="3" t="n"/>
+      <c r="X250" s="2" t="n"/>
       <c r="Y250" s="2" t="n"/>
     </row>
     <row r="251">
@@ -7500,7 +7500,7 @@
       <c r="U251" s="4" t="n"/>
       <c r="V251" s="3" t="n"/>
       <c r="W251" s="4" t="n"/>
-      <c r="X251" s="3" t="n"/>
+      <c r="X251" s="4" t="n"/>
       <c r="Y251" s="4" t="n"/>
     </row>
     <row r="252">
@@ -7527,7 +7527,7 @@
       <c r="U252" s="2" t="n"/>
       <c r="V252" s="3" t="n"/>
       <c r="W252" s="2" t="n"/>
-      <c r="X252" s="3" t="n"/>
+      <c r="X252" s="2" t="n"/>
       <c r="Y252" s="2" t="n"/>
     </row>
     <row r="253">
@@ -7554,7 +7554,7 @@
       <c r="U253" s="4" t="n"/>
       <c r="V253" s="3" t="n"/>
       <c r="W253" s="4" t="n"/>
-      <c r="X253" s="3" t="n"/>
+      <c r="X253" s="4" t="n"/>
       <c r="Y253" s="4" t="n"/>
     </row>
     <row r="254">
@@ -7581,7 +7581,7 @@
       <c r="U254" s="2" t="n"/>
       <c r="V254" s="3" t="n"/>
       <c r="W254" s="2" t="n"/>
-      <c r="X254" s="3" t="n"/>
+      <c r="X254" s="2" t="n"/>
       <c r="Y254" s="2" t="n"/>
     </row>
     <row r="255">
@@ -7608,7 +7608,7 @@
       <c r="U255" s="4" t="n"/>
       <c r="V255" s="3" t="n"/>
       <c r="W255" s="4" t="n"/>
-      <c r="X255" s="3" t="n"/>
+      <c r="X255" s="4" t="n"/>
       <c r="Y255" s="4" t="n"/>
     </row>
     <row r="256">
@@ -7635,7 +7635,7 @@
       <c r="U256" s="2" t="n"/>
       <c r="V256" s="3" t="n"/>
       <c r="W256" s="2" t="n"/>
-      <c r="X256" s="3" t="n"/>
+      <c r="X256" s="2" t="n"/>
       <c r="Y256" s="2" t="n"/>
     </row>
     <row r="257">
@@ -7662,7 +7662,7 @@
       <c r="U257" s="4" t="n"/>
       <c r="V257" s="3" t="n"/>
       <c r="W257" s="4" t="n"/>
-      <c r="X257" s="3" t="n"/>
+      <c r="X257" s="4" t="n"/>
       <c r="Y257" s="4" t="n"/>
     </row>
     <row r="258">
@@ -7689,7 +7689,7 @@
       <c r="U258" s="2" t="n"/>
       <c r="V258" s="3" t="n"/>
       <c r="W258" s="2" t="n"/>
-      <c r="X258" s="3" t="n"/>
+      <c r="X258" s="2" t="n"/>
       <c r="Y258" s="2" t="n"/>
     </row>
     <row r="259">
@@ -7716,7 +7716,7 @@
       <c r="U259" s="4" t="n"/>
       <c r="V259" s="3" t="n"/>
       <c r="W259" s="4" t="n"/>
-      <c r="X259" s="3" t="n"/>
+      <c r="X259" s="4" t="n"/>
       <c r="Y259" s="4" t="n"/>
     </row>
     <row r="260">
@@ -7743,7 +7743,7 @@
       <c r="U260" s="2" t="n"/>
       <c r="V260" s="3" t="n"/>
       <c r="W260" s="2" t="n"/>
-      <c r="X260" s="3" t="n"/>
+      <c r="X260" s="2" t="n"/>
       <c r="Y260" s="2" t="n"/>
     </row>
     <row r="261">
@@ -7770,7 +7770,7 @@
       <c r="U261" s="4" t="n"/>
       <c r="V261" s="3" t="n"/>
       <c r="W261" s="4" t="n"/>
-      <c r="X261" s="3" t="n"/>
+      <c r="X261" s="4" t="n"/>
       <c r="Y261" s="4" t="n"/>
     </row>
     <row r="262">
@@ -7797,7 +7797,7 @@
       <c r="U262" s="2" t="n"/>
       <c r="V262" s="3" t="n"/>
       <c r="W262" s="2" t="n"/>
-      <c r="X262" s="3" t="n"/>
+      <c r="X262" s="2" t="n"/>
       <c r="Y262" s="2" t="n"/>
     </row>
     <row r="263">
@@ -7824,7 +7824,7 @@
       <c r="U263" s="4" t="n"/>
       <c r="V263" s="3" t="n"/>
       <c r="W263" s="4" t="n"/>
-      <c r="X263" s="3" t="n"/>
+      <c r="X263" s="4" t="n"/>
       <c r="Y263" s="4" t="n"/>
     </row>
     <row r="264">
@@ -7851,7 +7851,7 @@
       <c r="U264" s="2" t="n"/>
       <c r="V264" s="3" t="n"/>
       <c r="W264" s="2" t="n"/>
-      <c r="X264" s="3" t="n"/>
+      <c r="X264" s="2" t="n"/>
       <c r="Y264" s="2" t="n"/>
     </row>
     <row r="265">
@@ -7878,7 +7878,7 @@
       <c r="U265" s="4" t="n"/>
       <c r="V265" s="3" t="n"/>
       <c r="W265" s="4" t="n"/>
-      <c r="X265" s="3" t="n"/>
+      <c r="X265" s="4" t="n"/>
       <c r="Y265" s="4" t="n"/>
     </row>
     <row r="266">
@@ -7905,7 +7905,7 @@
       <c r="U266" s="2" t="n"/>
       <c r="V266" s="3" t="n"/>
       <c r="W266" s="2" t="n"/>
-      <c r="X266" s="3" t="n"/>
+      <c r="X266" s="2" t="n"/>
       <c r="Y266" s="2" t="n"/>
     </row>
     <row r="267">
@@ -7932,7 +7932,7 @@
       <c r="U267" s="4" t="n"/>
       <c r="V267" s="3" t="n"/>
       <c r="W267" s="4" t="n"/>
-      <c r="X267" s="3" t="n"/>
+      <c r="X267" s="4" t="n"/>
       <c r="Y267" s="4" t="n"/>
     </row>
     <row r="268">
@@ -7959,7 +7959,7 @@
       <c r="U268" s="2" t="n"/>
       <c r="V268" s="3" t="n"/>
       <c r="W268" s="2" t="n"/>
-      <c r="X268" s="3" t="n"/>
+      <c r="X268" s="2" t="n"/>
       <c r="Y268" s="2" t="n"/>
     </row>
     <row r="269">
@@ -7986,7 +7986,7 @@
       <c r="U269" s="4" t="n"/>
       <c r="V269" s="3" t="n"/>
       <c r="W269" s="4" t="n"/>
-      <c r="X269" s="3" t="n"/>
+      <c r="X269" s="4" t="n"/>
       <c r="Y269" s="4" t="n"/>
     </row>
     <row r="270">
@@ -8013,7 +8013,7 @@
       <c r="U270" s="2" t="n"/>
       <c r="V270" s="3" t="n"/>
       <c r="W270" s="2" t="n"/>
-      <c r="X270" s="3" t="n"/>
+      <c r="X270" s="2" t="n"/>
       <c r="Y270" s="2" t="n"/>
     </row>
     <row r="271">
@@ -8040,7 +8040,7 @@
       <c r="U271" s="4" t="n"/>
       <c r="V271" s="3" t="n"/>
       <c r="W271" s="4" t="n"/>
-      <c r="X271" s="3" t="n"/>
+      <c r="X271" s="4" t="n"/>
       <c r="Y271" s="4" t="n"/>
     </row>
     <row r="272">
@@ -8067,7 +8067,7 @@
       <c r="U272" s="2" t="n"/>
       <c r="V272" s="3" t="n"/>
       <c r="W272" s="2" t="n"/>
-      <c r="X272" s="3" t="n"/>
+      <c r="X272" s="2" t="n"/>
       <c r="Y272" s="2" t="n"/>
     </row>
     <row r="273">
@@ -8094,7 +8094,7 @@
       <c r="U273" s="4" t="n"/>
       <c r="V273" s="3" t="n"/>
       <c r="W273" s="4" t="n"/>
-      <c r="X273" s="3" t="n"/>
+      <c r="X273" s="4" t="n"/>
       <c r="Y273" s="4" t="n"/>
     </row>
     <row r="274">
@@ -8121,7 +8121,7 @@
       <c r="U274" s="2" t="n"/>
       <c r="V274" s="3" t="n"/>
       <c r="W274" s="2" t="n"/>
-      <c r="X274" s="3" t="n"/>
+      <c r="X274" s="2" t="n"/>
       <c r="Y274" s="2" t="n"/>
     </row>
     <row r="275">
@@ -8148,7 +8148,7 @@
       <c r="U275" s="4" t="n"/>
       <c r="V275" s="3" t="n"/>
       <c r="W275" s="4" t="n"/>
-      <c r="X275" s="3" t="n"/>
+      <c r="X275" s="4" t="n"/>
       <c r="Y275" s="4" t="n"/>
     </row>
     <row r="276">
@@ -8175,7 +8175,7 @@
       <c r="U276" s="2" t="n"/>
       <c r="V276" s="3" t="n"/>
       <c r="W276" s="2" t="n"/>
-      <c r="X276" s="3" t="n"/>
+      <c r="X276" s="2" t="n"/>
       <c r="Y276" s="2" t="n"/>
     </row>
     <row r="277">
@@ -8202,7 +8202,7 @@
       <c r="U277" s="4" t="n"/>
       <c r="V277" s="3" t="n"/>
       <c r="W277" s="4" t="n"/>
-      <c r="X277" s="3" t="n"/>
+      <c r="X277" s="4" t="n"/>
       <c r="Y277" s="4" t="n"/>
     </row>
     <row r="278">
@@ -8229,7 +8229,7 @@
       <c r="U278" s="2" t="n"/>
       <c r="V278" s="3" t="n"/>
       <c r="W278" s="2" t="n"/>
-      <c r="X278" s="3" t="n"/>
+      <c r="X278" s="2" t="n"/>
       <c r="Y278" s="2" t="n"/>
     </row>
     <row r="279">
@@ -8256,7 +8256,7 @@
       <c r="U279" s="4" t="n"/>
       <c r="V279" s="3" t="n"/>
       <c r="W279" s="4" t="n"/>
-      <c r="X279" s="3" t="n"/>
+      <c r="X279" s="4" t="n"/>
       <c r="Y279" s="4" t="n"/>
     </row>
     <row r="280">
@@ -8283,7 +8283,7 @@
       <c r="U280" s="2" t="n"/>
       <c r="V280" s="3" t="n"/>
       <c r="W280" s="2" t="n"/>
-      <c r="X280" s="3" t="n"/>
+      <c r="X280" s="2" t="n"/>
       <c r="Y280" s="2" t="n"/>
     </row>
     <row r="281">
@@ -8310,7 +8310,7 @@
       <c r="U281" s="4" t="n"/>
       <c r="V281" s="3" t="n"/>
       <c r="W281" s="4" t="n"/>
-      <c r="X281" s="3" t="n"/>
+      <c r="X281" s="4" t="n"/>
       <c r="Y281" s="4" t="n"/>
     </row>
     <row r="282">
@@ -8337,7 +8337,7 @@
       <c r="U282" s="2" t="n"/>
       <c r="V282" s="3" t="n"/>
       <c r="W282" s="2" t="n"/>
-      <c r="X282" s="3" t="n"/>
+      <c r="X282" s="2" t="n"/>
       <c r="Y282" s="2" t="n"/>
     </row>
     <row r="283">
@@ -8364,7 +8364,7 @@
       <c r="U283" s="4" t="n"/>
       <c r="V283" s="3" t="n"/>
       <c r="W283" s="4" t="n"/>
-      <c r="X283" s="3" t="n"/>
+      <c r="X283" s="4" t="n"/>
       <c r="Y283" s="4" t="n"/>
     </row>
     <row r="284">
@@ -8391,7 +8391,7 @@
       <c r="U284" s="2" t="n"/>
       <c r="V284" s="3" t="n"/>
       <c r="W284" s="2" t="n"/>
-      <c r="X284" s="3" t="n"/>
+      <c r="X284" s="2" t="n"/>
       <c r="Y284" s="2" t="n"/>
     </row>
     <row r="285">
@@ -8418,7 +8418,7 @@
       <c r="U285" s="4" t="n"/>
       <c r="V285" s="3" t="n"/>
       <c r="W285" s="4" t="n"/>
-      <c r="X285" s="3" t="n"/>
+      <c r="X285" s="4" t="n"/>
       <c r="Y285" s="4" t="n"/>
     </row>
     <row r="286">
@@ -8445,7 +8445,7 @@
       <c r="U286" s="2" t="n"/>
       <c r="V286" s="3" t="n"/>
       <c r="W286" s="2" t="n"/>
-      <c r="X286" s="3" t="n"/>
+      <c r="X286" s="2" t="n"/>
       <c r="Y286" s="2" t="n"/>
     </row>
     <row r="287">
@@ -8472,7 +8472,7 @@
       <c r="U287" s="4" t="n"/>
       <c r="V287" s="3" t="n"/>
       <c r="W287" s="4" t="n"/>
-      <c r="X287" s="3" t="n"/>
+      <c r="X287" s="4" t="n"/>
       <c r="Y287" s="4" t="n"/>
     </row>
     <row r="288">
@@ -8499,7 +8499,7 @@
       <c r="U288" s="2" t="n"/>
       <c r="V288" s="3" t="n"/>
       <c r="W288" s="2" t="n"/>
-      <c r="X288" s="3" t="n"/>
+      <c r="X288" s="2" t="n"/>
       <c r="Y288" s="2" t="n"/>
     </row>
     <row r="289">
@@ -8526,7 +8526,7 @@
       <c r="U289" s="4" t="n"/>
       <c r="V289" s="3" t="n"/>
       <c r="W289" s="4" t="n"/>
-      <c r="X289" s="3" t="n"/>
+      <c r="X289" s="4" t="n"/>
       <c r="Y289" s="4" t="n"/>
     </row>
     <row r="290">
@@ -8553,7 +8553,7 @@
       <c r="U290" s="2" t="n"/>
       <c r="V290" s="3" t="n"/>
       <c r="W290" s="2" t="n"/>
-      <c r="X290" s="3" t="n"/>
+      <c r="X290" s="2" t="n"/>
       <c r="Y290" s="2" t="n"/>
     </row>
     <row r="291">
@@ -8580,7 +8580,7 @@
       <c r="U291" s="4" t="n"/>
       <c r="V291" s="3" t="n"/>
       <c r="W291" s="4" t="n"/>
-      <c r="X291" s="3" t="n"/>
+      <c r="X291" s="4" t="n"/>
       <c r="Y291" s="4" t="n"/>
     </row>
     <row r="292">
@@ -8607,7 +8607,7 @@
       <c r="U292" s="2" t="n"/>
       <c r="V292" s="3" t="n"/>
       <c r="W292" s="2" t="n"/>
-      <c r="X292" s="3" t="n"/>
+      <c r="X292" s="2" t="n"/>
       <c r="Y292" s="2" t="n"/>
     </row>
     <row r="293">
@@ -8634,7 +8634,7 @@
       <c r="U293" s="4" t="n"/>
       <c r="V293" s="3" t="n"/>
       <c r="W293" s="4" t="n"/>
-      <c r="X293" s="3" t="n"/>
+      <c r="X293" s="4" t="n"/>
       <c r="Y293" s="4" t="n"/>
     </row>
     <row r="294">
@@ -8661,7 +8661,7 @@
       <c r="U294" s="2" t="n"/>
       <c r="V294" s="3" t="n"/>
       <c r="W294" s="2" t="n"/>
-      <c r="X294" s="3" t="n"/>
+      <c r="X294" s="2" t="n"/>
       <c r="Y294" s="2" t="n"/>
     </row>
     <row r="295">
@@ -8688,7 +8688,7 @@
       <c r="U295" s="4" t="n"/>
       <c r="V295" s="3" t="n"/>
       <c r="W295" s="4" t="n"/>
-      <c r="X295" s="3" t="n"/>
+      <c r="X295" s="4" t="n"/>
       <c r="Y295" s="4" t="n"/>
     </row>
     <row r="296">
@@ -8715,7 +8715,7 @@
       <c r="U296" s="2" t="n"/>
       <c r="V296" s="3" t="n"/>
       <c r="W296" s="2" t="n"/>
-      <c r="X296" s="3" t="n"/>
+      <c r="X296" s="2" t="n"/>
       <c r="Y296" s="2" t="n"/>
     </row>
     <row r="297">
@@ -8742,7 +8742,7 @@
       <c r="U297" s="4" t="n"/>
       <c r="V297" s="3" t="n"/>
       <c r="W297" s="4" t="n"/>
-      <c r="X297" s="3" t="n"/>
+      <c r="X297" s="4" t="n"/>
       <c r="Y297" s="4" t="n"/>
     </row>
     <row r="298">
@@ -8769,7 +8769,7 @@
       <c r="U298" s="2" t="n"/>
       <c r="V298" s="3" t="n"/>
       <c r="W298" s="2" t="n"/>
-      <c r="X298" s="3" t="n"/>
+      <c r="X298" s="2" t="n"/>
       <c r="Y298" s="2" t="n"/>
     </row>
     <row r="299">
@@ -8796,7 +8796,7 @@
       <c r="U299" s="4" t="n"/>
       <c r="V299" s="3" t="n"/>
       <c r="W299" s="4" t="n"/>
-      <c r="X299" s="3" t="n"/>
+      <c r="X299" s="4" t="n"/>
       <c r="Y299" s="4" t="n"/>
     </row>
     <row r="300">
@@ -8823,7 +8823,7 @@
       <c r="U300" s="2" t="n"/>
       <c r="V300" s="3" t="n"/>
       <c r="W300" s="2" t="n"/>
-      <c r="X300" s="3" t="n"/>
+      <c r="X300" s="2" t="n"/>
       <c r="Y300" s="2" t="n"/>
     </row>
     <row r="301">
@@ -8850,7 +8850,7 @@
       <c r="U301" s="4" t="n"/>
       <c r="V301" s="3" t="n"/>
       <c r="W301" s="4" t="n"/>
-      <c r="X301" s="3" t="n"/>
+      <c r="X301" s="4" t="n"/>
       <c r="Y301" s="4" t="n"/>
     </row>
     <row r="302">
@@ -8877,7 +8877,7 @@
       <c r="U302" s="2" t="n"/>
       <c r="V302" s="3" t="n"/>
       <c r="W302" s="2" t="n"/>
-      <c r="X302" s="3" t="n"/>
+      <c r="X302" s="2" t="n"/>
       <c r="Y302" s="2" t="n"/>
     </row>
     <row r="303">
@@ -8904,7 +8904,7 @@
       <c r="U303" s="4" t="n"/>
       <c r="V303" s="3" t="n"/>
       <c r="W303" s="4" t="n"/>
-      <c r="X303" s="3" t="n"/>
+      <c r="X303" s="4" t="n"/>
       <c r="Y303" s="4" t="n"/>
     </row>
     <row r="304">
@@ -8931,7 +8931,7 @@
       <c r="U304" s="2" t="n"/>
       <c r="V304" s="3" t="n"/>
       <c r="W304" s="2" t="n"/>
-      <c r="X304" s="3" t="n"/>
+      <c r="X304" s="2" t="n"/>
       <c r="Y304" s="2" t="n"/>
     </row>
     <row r="305">
@@ -8958,7 +8958,7 @@
       <c r="U305" s="4" t="n"/>
       <c r="V305" s="3" t="n"/>
       <c r="W305" s="4" t="n"/>
-      <c r="X305" s="3" t="n"/>
+      <c r="X305" s="4" t="n"/>
       <c r="Y305" s="4" t="n"/>
     </row>
     <row r="306">
@@ -8985,7 +8985,7 @@
       <c r="U306" s="2" t="n"/>
       <c r="V306" s="3" t="n"/>
       <c r="W306" s="2" t="n"/>
-      <c r="X306" s="3" t="n"/>
+      <c r="X306" s="2" t="n"/>
       <c r="Y306" s="2" t="n"/>
     </row>
     <row r="307">
@@ -9012,7 +9012,7 @@
       <c r="U307" s="4" t="n"/>
       <c r="V307" s="3" t="n"/>
       <c r="W307" s="4" t="n"/>
-      <c r="X307" s="3" t="n"/>
+      <c r="X307" s="4" t="n"/>
       <c r="Y307" s="4" t="n"/>
     </row>
     <row r="308">
@@ -9039,7 +9039,7 @@
       <c r="U308" s="2" t="n"/>
       <c r="V308" s="3" t="n"/>
       <c r="W308" s="2" t="n"/>
-      <c r="X308" s="3" t="n"/>
+      <c r="X308" s="2" t="n"/>
       <c r="Y308" s="2" t="n"/>
     </row>
     <row r="309">
@@ -9066,7 +9066,7 @@
       <c r="U309" s="4" t="n"/>
       <c r="V309" s="3" t="n"/>
       <c r="W309" s="4" t="n"/>
-      <c r="X309" s="3" t="n"/>
+      <c r="X309" s="4" t="n"/>
       <c r="Y309" s="4" t="n"/>
     </row>
     <row r="310">
@@ -9093,7 +9093,7 @@
       <c r="U310" s="2" t="n"/>
       <c r="V310" s="3" t="n"/>
       <c r="W310" s="2" t="n"/>
-      <c r="X310" s="3" t="n"/>
+      <c r="X310" s="2" t="n"/>
       <c r="Y310" s="2" t="n"/>
     </row>
     <row r="311">
@@ -9120,7 +9120,7 @@
       <c r="U311" s="4" t="n"/>
       <c r="V311" s="3" t="n"/>
       <c r="W311" s="4" t="n"/>
-      <c r="X311" s="3" t="n"/>
+      <c r="X311" s="4" t="n"/>
       <c r="Y311" s="4" t="n"/>
     </row>
     <row r="312">
@@ -9147,7 +9147,7 @@
       <c r="U312" s="2" t="n"/>
       <c r="V312" s="3" t="n"/>
       <c r="W312" s="2" t="n"/>
-      <c r="X312" s="3" t="n"/>
+      <c r="X312" s="2" t="n"/>
       <c r="Y312" s="2" t="n"/>
     </row>
     <row r="313">
@@ -9174,7 +9174,7 @@
       <c r="U313" s="4" t="n"/>
       <c r="V313" s="3" t="n"/>
       <c r="W313" s="4" t="n"/>
-      <c r="X313" s="3" t="n"/>
+      <c r="X313" s="4" t="n"/>
       <c r="Y313" s="4" t="n"/>
     </row>
     <row r="314">
@@ -9201,7 +9201,7 @@
       <c r="U314" s="2" t="n"/>
       <c r="V314" s="3" t="n"/>
       <c r="W314" s="2" t="n"/>
-      <c r="X314" s="3" t="n"/>
+      <c r="X314" s="2" t="n"/>
       <c r="Y314" s="2" t="n"/>
     </row>
     <row r="315">
@@ -9228,7 +9228,7 @@
       <c r="U315" s="4" t="n"/>
       <c r="V315" s="3" t="n"/>
       <c r="W315" s="4" t="n"/>
-      <c r="X315" s="3" t="n"/>
+      <c r="X315" s="4" t="n"/>
       <c r="Y315" s="4" t="n"/>
     </row>
     <row r="316">
@@ -9255,7 +9255,7 @@
       <c r="U316" s="2" t="n"/>
       <c r="V316" s="3" t="n"/>
       <c r="W316" s="2" t="n"/>
-      <c r="X316" s="3" t="n"/>
+      <c r="X316" s="2" t="n"/>
       <c r="Y316" s="2" t="n"/>
     </row>
     <row r="317">
@@ -9282,7 +9282,7 @@
       <c r="U317" s="4" t="n"/>
       <c r="V317" s="3" t="n"/>
       <c r="W317" s="4" t="n"/>
-      <c r="X317" s="3" t="n"/>
+      <c r="X317" s="4" t="n"/>
       <c r="Y317" s="4" t="n"/>
     </row>
     <row r="318">
@@ -9309,7 +9309,7 @@
       <c r="U318" s="2" t="n"/>
       <c r="V318" s="3" t="n"/>
       <c r="W318" s="2" t="n"/>
-      <c r="X318" s="3" t="n"/>
+      <c r="X318" s="2" t="n"/>
       <c r="Y318" s="2" t="n"/>
     </row>
     <row r="319">
@@ -9336,7 +9336,7 @@
       <c r="U319" s="4" t="n"/>
       <c r="V319" s="3" t="n"/>
       <c r="W319" s="4" t="n"/>
-      <c r="X319" s="3" t="n"/>
+      <c r="X319" s="4" t="n"/>
       <c r="Y319" s="4" t="n"/>
     </row>
     <row r="320">
@@ -9363,7 +9363,7 @@
       <c r="U320" s="2" t="n"/>
       <c r="V320" s="3" t="n"/>
       <c r="W320" s="2" t="n"/>
-      <c r="X320" s="3" t="n"/>
+      <c r="X320" s="2" t="n"/>
       <c r="Y320" s="2" t="n"/>
     </row>
     <row r="321">
@@ -9390,7 +9390,7 @@
       <c r="U321" s="4" t="n"/>
       <c r="V321" s="3" t="n"/>
       <c r="W321" s="4" t="n"/>
-      <c r="X321" s="3" t="n"/>
+      <c r="X321" s="4" t="n"/>
       <c r="Y321" s="4" t="n"/>
     </row>
     <row r="322">
@@ -9417,7 +9417,7 @@
       <c r="U322" s="2" t="n"/>
       <c r="V322" s="3" t="n"/>
       <c r="W322" s="2" t="n"/>
-      <c r="X322" s="3" t="n"/>
+      <c r="X322" s="2" t="n"/>
       <c r="Y322" s="2" t="n"/>
     </row>
     <row r="323">
@@ -9444,7 +9444,7 @@
       <c r="U323" s="4" t="n"/>
       <c r="V323" s="3" t="n"/>
       <c r="W323" s="4" t="n"/>
-      <c r="X323" s="3" t="n"/>
+      <c r="X323" s="4" t="n"/>
       <c r="Y323" s="4" t="n"/>
     </row>
     <row r="324">
@@ -9471,7 +9471,7 @@
       <c r="U324" s="2" t="n"/>
       <c r="V324" s="3" t="n"/>
       <c r="W324" s="2" t="n"/>
-      <c r="X324" s="3" t="n"/>
+      <c r="X324" s="2" t="n"/>
       <c r="Y324" s="2" t="n"/>
     </row>
     <row r="325">
@@ -9498,7 +9498,7 @@
       <c r="U325" s="4" t="n"/>
       <c r="V325" s="3" t="n"/>
       <c r="W325" s="4" t="n"/>
-      <c r="X325" s="3" t="n"/>
+      <c r="X325" s="4" t="n"/>
       <c r="Y325" s="4" t="n"/>
     </row>
     <row r="326">
@@ -9525,7 +9525,7 @@
       <c r="U326" s="2" t="n"/>
       <c r="V326" s="3" t="n"/>
       <c r="W326" s="2" t="n"/>
-      <c r="X326" s="3" t="n"/>
+      <c r="X326" s="2" t="n"/>
       <c r="Y326" s="2" t="n"/>
     </row>
     <row r="327">
@@ -9552,7 +9552,7 @@
       <c r="U327" s="4" t="n"/>
       <c r="V327" s="3" t="n"/>
       <c r="W327" s="4" t="n"/>
-      <c r="X327" s="3" t="n"/>
+      <c r="X327" s="4" t="n"/>
       <c r="Y327" s="4" t="n"/>
     </row>
     <row r="328">
@@ -9579,7 +9579,7 @@
       <c r="U328" s="2" t="n"/>
       <c r="V328" s="3" t="n"/>
       <c r="W328" s="2" t="n"/>
-      <c r="X328" s="3" t="n"/>
+      <c r="X328" s="2" t="n"/>
       <c r="Y328" s="2" t="n"/>
     </row>
     <row r="329">
@@ -9606,7 +9606,7 @@
       <c r="U329" s="4" t="n"/>
       <c r="V329" s="3" t="n"/>
       <c r="W329" s="4" t="n"/>
-      <c r="X329" s="3" t="n"/>
+      <c r="X329" s="4" t="n"/>
       <c r="Y329" s="4" t="n"/>
     </row>
     <row r="330">
@@ -9633,7 +9633,7 @@
       <c r="U330" s="2" t="n"/>
       <c r="V330" s="3" t="n"/>
       <c r="W330" s="2" t="n"/>
-      <c r="X330" s="3" t="n"/>
+      <c r="X330" s="2" t="n"/>
       <c r="Y330" s="2" t="n"/>
     </row>
     <row r="331">
@@ -9660,7 +9660,7 @@
       <c r="U331" s="4" t="n"/>
       <c r="V331" s="3" t="n"/>
       <c r="W331" s="4" t="n"/>
-      <c r="X331" s="3" t="n"/>
+      <c r="X331" s="4" t="n"/>
       <c r="Y331" s="4" t="n"/>
     </row>
     <row r="332">
@@ -9687,7 +9687,7 @@
       <c r="U332" s="2" t="n"/>
       <c r="V332" s="3" t="n"/>
       <c r="W332" s="2" t="n"/>
-      <c r="X332" s="3" t="n"/>
+      <c r="X332" s="2" t="n"/>
       <c r="Y332" s="2" t="n"/>
     </row>
     <row r="333">
@@ -9714,7 +9714,7 @@
       <c r="U333" s="4" t="n"/>
       <c r="V333" s="3" t="n"/>
       <c r="W333" s="4" t="n"/>
-      <c r="X333" s="3" t="n"/>
+      <c r="X333" s="4" t="n"/>
       <c r="Y333" s="4" t="n"/>
     </row>
     <row r="334">
@@ -9741,7 +9741,7 @@
       <c r="U334" s="2" t="n"/>
       <c r="V334" s="3" t="n"/>
       <c r="W334" s="2" t="n"/>
-      <c r="X334" s="3" t="n"/>
+      <c r="X334" s="2" t="n"/>
       <c r="Y334" s="2" t="n"/>
     </row>
     <row r="335">
@@ -9768,7 +9768,7 @@
       <c r="U335" s="4" t="n"/>
       <c r="V335" s="3" t="n"/>
       <c r="W335" s="4" t="n"/>
-      <c r="X335" s="3" t="n"/>
+      <c r="X335" s="4" t="n"/>
       <c r="Y335" s="4" t="n"/>
     </row>
     <row r="336">
@@ -9795,7 +9795,7 @@
       <c r="U336" s="2" t="n"/>
       <c r="V336" s="3" t="n"/>
       <c r="W336" s="2" t="n"/>
-      <c r="X336" s="3" t="n"/>
+      <c r="X336" s="2" t="n"/>
       <c r="Y336" s="2" t="n"/>
     </row>
     <row r="337">
@@ -9822,7 +9822,7 @@
       <c r="U337" s="4" t="n"/>
       <c r="V337" s="3" t="n"/>
       <c r="W337" s="4" t="n"/>
-      <c r="X337" s="3" t="n"/>
+      <c r="X337" s="4" t="n"/>
       <c r="Y337" s="4" t="n"/>
     </row>
     <row r="338">
@@ -9849,7 +9849,7 @@
       <c r="U338" s="2" t="n"/>
       <c r="V338" s="3" t="n"/>
       <c r="W338" s="2" t="n"/>
-      <c r="X338" s="3" t="n"/>
+      <c r="X338" s="2" t="n"/>
       <c r="Y338" s="2" t="n"/>
     </row>
     <row r="339">
@@ -9876,7 +9876,7 @@
       <c r="U339" s="4" t="n"/>
       <c r="V339" s="3" t="n"/>
       <c r="W339" s="4" t="n"/>
-      <c r="X339" s="3" t="n"/>
+      <c r="X339" s="4" t="n"/>
       <c r="Y339" s="4" t="n"/>
     </row>
     <row r="340">
@@ -9903,7 +9903,7 @@
       <c r="U340" s="2" t="n"/>
       <c r="V340" s="3" t="n"/>
       <c r="W340" s="2" t="n"/>
-      <c r="X340" s="3" t="n"/>
+      <c r="X340" s="2" t="n"/>
       <c r="Y340" s="2" t="n"/>
     </row>
     <row r="341">
@@ -9930,7 +9930,7 @@
       <c r="U341" s="4" t="n"/>
       <c r="V341" s="3" t="n"/>
       <c r="W341" s="4" t="n"/>
-      <c r="X341" s="3" t="n"/>
+      <c r="X341" s="4" t="n"/>
       <c r="Y341" s="4" t="n"/>
     </row>
     <row r="342">
@@ -9957,7 +9957,7 @@
       <c r="U342" s="2" t="n"/>
       <c r="V342" s="3" t="n"/>
       <c r="W342" s="2" t="n"/>
-      <c r="X342" s="3" t="n"/>
+      <c r="X342" s="2" t="n"/>
       <c r="Y342" s="2" t="n"/>
     </row>
     <row r="343">
@@ -9984,7 +9984,7 @@
       <c r="U343" s="4" t="n"/>
       <c r="V343" s="3" t="n"/>
       <c r="W343" s="4" t="n"/>
-      <c r="X343" s="3" t="n"/>
+      <c r="X343" s="4" t="n"/>
       <c r="Y343" s="4" t="n"/>
     </row>
     <row r="344">
@@ -10011,7 +10011,7 @@
       <c r="U344" s="2" t="n"/>
       <c r="V344" s="3" t="n"/>
       <c r="W344" s="2" t="n"/>
-      <c r="X344" s="3" t="n"/>
+      <c r="X344" s="2" t="n"/>
       <c r="Y344" s="2" t="n"/>
     </row>
     <row r="345">
@@ -10038,7 +10038,7 @@
       <c r="U345" s="4" t="n"/>
       <c r="V345" s="3" t="n"/>
       <c r="W345" s="4" t="n"/>
-      <c r="X345" s="3" t="n"/>
+      <c r="X345" s="4" t="n"/>
       <c r="Y345" s="4" t="n"/>
     </row>
     <row r="346">
@@ -10065,7 +10065,7 @@
       <c r="U346" s="2" t="n"/>
       <c r="V346" s="3" t="n"/>
       <c r="W346" s="2" t="n"/>
-      <c r="X346" s="3" t="n"/>
+      <c r="X346" s="2" t="n"/>
       <c r="Y346" s="2" t="n"/>
     </row>
     <row r="347">
@@ -10092,7 +10092,7 @@
       <c r="U347" s="4" t="n"/>
       <c r="V347" s="3" t="n"/>
       <c r="W347" s="4" t="n"/>
-      <c r="X347" s="3" t="n"/>
+      <c r="X347" s="4" t="n"/>
       <c r="Y347" s="4" t="n"/>
     </row>
     <row r="348">
@@ -10119,7 +10119,7 @@
       <c r="U348" s="2" t="n"/>
       <c r="V348" s="3" t="n"/>
       <c r="W348" s="2" t="n"/>
-      <c r="X348" s="3" t="n"/>
+      <c r="X348" s="2" t="n"/>
       <c r="Y348" s="2" t="n"/>
     </row>
     <row r="349">
@@ -10146,7 +10146,7 @@
       <c r="U349" s="4" t="n"/>
       <c r="V349" s="3" t="n"/>
       <c r="W349" s="4" t="n"/>
-      <c r="X349" s="3" t="n"/>
+      <c r="X349" s="4" t="n"/>
       <c r="Y349" s="4" t="n"/>
     </row>
     <row r="350">
@@ -10173,7 +10173,7 @@
       <c r="U350" s="2" t="n"/>
       <c r="V350" s="3" t="n"/>
       <c r="W350" s="2" t="n"/>
-      <c r="X350" s="3" t="n"/>
+      <c r="X350" s="2" t="n"/>
       <c r="Y350" s="2" t="n"/>
     </row>
     <row r="351">
@@ -10200,7 +10200,7 @@
       <c r="U351" s="4" t="n"/>
       <c r="V351" s="3" t="n"/>
       <c r="W351" s="4" t="n"/>
-      <c r="X351" s="3" t="n"/>
+      <c r="X351" s="4" t="n"/>
       <c r="Y351" s="4" t="n"/>
     </row>
     <row r="352">
@@ -10227,7 +10227,7 @@
       <c r="U352" s="2" t="n"/>
       <c r="V352" s="3" t="n"/>
       <c r="W352" s="2" t="n"/>
-      <c r="X352" s="3" t="n"/>
+      <c r="X352" s="2" t="n"/>
       <c r="Y352" s="2" t="n"/>
     </row>
     <row r="353">
@@ -10254,7 +10254,7 @@
       <c r="U353" s="4" t="n"/>
       <c r="V353" s="3" t="n"/>
       <c r="W353" s="4" t="n"/>
-      <c r="X353" s="3" t="n"/>
+      <c r="X353" s="4" t="n"/>
       <c r="Y353" s="4" t="n"/>
     </row>
     <row r="354">
@@ -10281,7 +10281,7 @@
       <c r="U354" s="2" t="n"/>
       <c r="V354" s="3" t="n"/>
       <c r="W354" s="2" t="n"/>
-      <c r="X354" s="3" t="n"/>
+      <c r="X354" s="2" t="n"/>
       <c r="Y354" s="2" t="n"/>
     </row>
     <row r="355">
@@ -10308,7 +10308,7 @@
       <c r="U355" s="4" t="n"/>
       <c r="V355" s="3" t="n"/>
       <c r="W355" s="4" t="n"/>
-      <c r="X355" s="3" t="n"/>
+      <c r="X355" s="4" t="n"/>
       <c r="Y355" s="4" t="n"/>
     </row>
     <row r="356">
@@ -10335,7 +10335,7 @@
       <c r="U356" s="2" t="n"/>
       <c r="V356" s="3" t="n"/>
       <c r="W356" s="2" t="n"/>
-      <c r="X356" s="3" t="n"/>
+      <c r="X356" s="2" t="n"/>
       <c r="Y356" s="2" t="n"/>
     </row>
     <row r="357">
@@ -10362,7 +10362,7 @@
       <c r="U357" s="4" t="n"/>
       <c r="V357" s="3" t="n"/>
       <c r="W357" s="4" t="n"/>
-      <c r="X357" s="3" t="n"/>
+      <c r="X357" s="4" t="n"/>
       <c r="Y357" s="4" t="n"/>
     </row>
     <row r="358">
@@ -10389,7 +10389,7 @@
       <c r="U358" s="2" t="n"/>
       <c r="V358" s="3" t="n"/>
       <c r="W358" s="2" t="n"/>
-      <c r="X358" s="3" t="n"/>
+      <c r="X358" s="2" t="n"/>
       <c r="Y358" s="2" t="n"/>
     </row>
     <row r="359">
@@ -10416,7 +10416,7 @@
       <c r="U359" s="4" t="n"/>
       <c r="V359" s="3" t="n"/>
       <c r="W359" s="4" t="n"/>
-      <c r="X359" s="3" t="n"/>
+      <c r="X359" s="4" t="n"/>
       <c r="Y359" s="4" t="n"/>
     </row>
     <row r="360">
@@ -10443,7 +10443,7 @@
       <c r="U360" s="2" t="n"/>
       <c r="V360" s="3" t="n"/>
       <c r="W360" s="2" t="n"/>
-      <c r="X360" s="3" t="n"/>
+      <c r="X360" s="2" t="n"/>
       <c r="Y360" s="2" t="n"/>
     </row>
     <row r="361">
@@ -10470,7 +10470,7 @@
       <c r="U361" s="4" t="n"/>
       <c r="V361" s="3" t="n"/>
       <c r="W361" s="4" t="n"/>
-      <c r="X361" s="3" t="n"/>
+      <c r="X361" s="4" t="n"/>
       <c r="Y361" s="4" t="n"/>
     </row>
     <row r="362">
@@ -10497,7 +10497,7 @@
       <c r="U362" s="2" t="n"/>
       <c r="V362" s="3" t="n"/>
       <c r="W362" s="2" t="n"/>
-      <c r="X362" s="3" t="n"/>
+      <c r="X362" s="2" t="n"/>
       <c r="Y362" s="2" t="n"/>
     </row>
     <row r="363">
@@ -10524,7 +10524,7 @@
       <c r="U363" s="4" t="n"/>
       <c r="V363" s="3" t="n"/>
       <c r="W363" s="4" t="n"/>
-      <c r="X363" s="3" t="n"/>
+      <c r="X363" s="4" t="n"/>
       <c r="Y363" s="4" t="n"/>
     </row>
     <row r="364">
@@ -10551,7 +10551,7 @@
       <c r="U364" s="2" t="n"/>
       <c r="V364" s="3" t="n"/>
       <c r="W364" s="2" t="n"/>
-      <c r="X364" s="3" t="n"/>
+      <c r="X364" s="2" t="n"/>
       <c r="Y364" s="2" t="n"/>
     </row>
     <row r="365">
@@ -10578,7 +10578,7 @@
       <c r="U365" s="4" t="n"/>
       <c r="V365" s="3" t="n"/>
       <c r="W365" s="4" t="n"/>
-      <c r="X365" s="3" t="n"/>
+      <c r="X365" s="4" t="n"/>
       <c r="Y365" s="4" t="n"/>
     </row>
     <row r="366">
@@ -10605,7 +10605,7 @@
       <c r="U366" s="2" t="n"/>
       <c r="V366" s="3" t="n"/>
       <c r="W366" s="2" t="n"/>
-      <c r="X366" s="3" t="n"/>
+      <c r="X366" s="2" t="n"/>
       <c r="Y366" s="2" t="n"/>
     </row>
     <row r="367">
@@ -10632,7 +10632,7 @@
       <c r="U367" s="4" t="n"/>
       <c r="V367" s="3" t="n"/>
       <c r="W367" s="4" t="n"/>
-      <c r="X367" s="3" t="n"/>
+      <c r="X367" s="4" t="n"/>
       <c r="Y367" s="4" t="n"/>
     </row>
     <row r="368">
@@ -10659,7 +10659,7 @@
       <c r="U368" s="2" t="n"/>
       <c r="V368" s="3" t="n"/>
       <c r="W368" s="2" t="n"/>
-      <c r="X368" s="3" t="n"/>
+      <c r="X368" s="2" t="n"/>
       <c r="Y368" s="2" t="n"/>
     </row>
     <row r="369">
@@ -10686,7 +10686,7 @@
       <c r="U369" s="4" t="n"/>
       <c r="V369" s="3" t="n"/>
       <c r="W369" s="4" t="n"/>
-      <c r="X369" s="3" t="n"/>
+      <c r="X369" s="4" t="n"/>
       <c r="Y369" s="4" t="n"/>
     </row>
     <row r="370">
@@ -10713,7 +10713,7 @@
       <c r="U370" s="2" t="n"/>
       <c r="V370" s="3" t="n"/>
       <c r="W370" s="2" t="n"/>
-      <c r="X370" s="3" t="n"/>
+      <c r="X370" s="2" t="n"/>
       <c r="Y370" s="2" t="n"/>
     </row>
     <row r="371">
@@ -10740,7 +10740,7 @@
       <c r="U371" s="4" t="n"/>
       <c r="V371" s="3" t="n"/>
       <c r="W371" s="4" t="n"/>
-      <c r="X371" s="3" t="n"/>
+      <c r="X371" s="4" t="n"/>
       <c r="Y371" s="4" t="n"/>
     </row>
     <row r="372">
@@ -10767,7 +10767,7 @@
       <c r="U372" s="2" t="n"/>
       <c r="V372" s="3" t="n"/>
       <c r="W372" s="2" t="n"/>
-      <c r="X372" s="3" t="n"/>
+      <c r="X372" s="2" t="n"/>
       <c r="Y372" s="2" t="n"/>
     </row>
     <row r="373">
@@ -10794,7 +10794,7 @@
       <c r="U373" s="4" t="n"/>
       <c r="V373" s="3" t="n"/>
       <c r="W373" s="4" t="n"/>
-      <c r="X373" s="3" t="n"/>
+      <c r="X373" s="4" t="n"/>
       <c r="Y373" s="4" t="n"/>
     </row>
     <row r="374">
@@ -10821,7 +10821,7 @@
       <c r="U374" s="2" t="n"/>
       <c r="V374" s="3" t="n"/>
       <c r="W374" s="2" t="n"/>
-      <c r="X374" s="3" t="n"/>
+      <c r="X374" s="2" t="n"/>
       <c r="Y374" s="2" t="n"/>
     </row>
     <row r="375">
@@ -10848,7 +10848,7 @@
       <c r="U375" s="4" t="n"/>
       <c r="V375" s="3" t="n"/>
       <c r="W375" s="4" t="n"/>
-      <c r="X375" s="3" t="n"/>
+      <c r="X375" s="4" t="n"/>
       <c r="Y375" s="4" t="n"/>
     </row>
     <row r="376">
@@ -10875,7 +10875,7 @@
       <c r="U376" s="2" t="n"/>
       <c r="V376" s="3" t="n"/>
       <c r="W376" s="2" t="n"/>
-      <c r="X376" s="3" t="n"/>
+      <c r="X376" s="2" t="n"/>
       <c r="Y376" s="2" t="n"/>
     </row>
     <row r="377">
@@ -10902,7 +10902,7 @@
       <c r="U377" s="4" t="n"/>
       <c r="V377" s="3" t="n"/>
       <c r="W377" s="4" t="n"/>
-      <c r="X377" s="3" t="n"/>
+      <c r="X377" s="4" t="n"/>
       <c r="Y377" s="4" t="n"/>
     </row>
     <row r="378">
@@ -10929,7 +10929,7 @@
       <c r="U378" s="2" t="n"/>
       <c r="V378" s="3" t="n"/>
       <c r="W378" s="2" t="n"/>
-      <c r="X378" s="3" t="n"/>
+      <c r="X378" s="2" t="n"/>
       <c r="Y378" s="2" t="n"/>
     </row>
     <row r="379">
@@ -10956,7 +10956,7 @@
       <c r="U379" s="4" t="n"/>
       <c r="V379" s="3" t="n"/>
       <c r="W379" s="4" t="n"/>
-      <c r="X379" s="3" t="n"/>
+      <c r="X379" s="4" t="n"/>
       <c r="Y379" s="4" t="n"/>
     </row>
     <row r="380">
@@ -10983,7 +10983,7 @@
       <c r="U380" s="2" t="n"/>
       <c r="V380" s="3" t="n"/>
       <c r="W380" s="2" t="n"/>
-      <c r="X380" s="3" t="n"/>
+      <c r="X380" s="2" t="n"/>
       <c r="Y380" s="2" t="n"/>
     </row>
     <row r="381">
@@ -11010,7 +11010,7 @@
       <c r="U381" s="4" t="n"/>
       <c r="V381" s="3" t="n"/>
       <c r="W381" s="4" t="n"/>
-      <c r="X381" s="3" t="n"/>
+      <c r="X381" s="4" t="n"/>
       <c r="Y381" s="4" t="n"/>
     </row>
     <row r="382">
@@ -11037,7 +11037,7 @@
       <c r="U382" s="2" t="n"/>
       <c r="V382" s="3" t="n"/>
       <c r="W382" s="2" t="n"/>
-      <c r="X382" s="3" t="n"/>
+      <c r="X382" s="2" t="n"/>
       <c r="Y382" s="2" t="n"/>
     </row>
     <row r="383">
@@ -11064,7 +11064,7 @@
       <c r="U383" s="4" t="n"/>
       <c r="V383" s="3" t="n"/>
       <c r="W383" s="4" t="n"/>
-      <c r="X383" s="3" t="n"/>
+      <c r="X383" s="4" t="n"/>
       <c r="Y383" s="4" t="n"/>
     </row>
     <row r="384">
@@ -11091,7 +11091,7 @@
       <c r="U384" s="2" t="n"/>
       <c r="V384" s="3" t="n"/>
       <c r="W384" s="2" t="n"/>
-      <c r="X384" s="3" t="n"/>
+      <c r="X384" s="2" t="n"/>
       <c r="Y384" s="2" t="n"/>
     </row>
     <row r="385">
@@ -11118,7 +11118,7 @@
       <c r="U385" s="4" t="n"/>
       <c r="V385" s="3" t="n"/>
       <c r="W385" s="4" t="n"/>
-      <c r="X385" s="3" t="n"/>
+      <c r="X385" s="4" t="n"/>
       <c r="Y385" s="4" t="n"/>
     </row>
     <row r="386">
@@ -11145,7 +11145,7 @@
       <c r="U386" s="2" t="n"/>
       <c r="V386" s="3" t="n"/>
       <c r="W386" s="2" t="n"/>
-      <c r="X386" s="3" t="n"/>
+      <c r="X386" s="2" t="n"/>
       <c r="Y386" s="2" t="n"/>
     </row>
     <row r="387">
@@ -11172,7 +11172,7 @@
       <c r="U387" s="4" t="n"/>
       <c r="V387" s="3" t="n"/>
       <c r="W387" s="4" t="n"/>
-      <c r="X387" s="3" t="n"/>
+      <c r="X387" s="4" t="n"/>
       <c r="Y387" s="4" t="n"/>
     </row>
     <row r="388">
@@ -11199,7 +11199,7 @@
       <c r="U388" s="2" t="n"/>
       <c r="V388" s="3" t="n"/>
       <c r="W388" s="2" t="n"/>
-      <c r="X388" s="3" t="n"/>
+      <c r="X388" s="2" t="n"/>
       <c r="Y388" s="2" t="n"/>
     </row>
     <row r="389">
@@ -11226,7 +11226,7 @@
       <c r="U389" s="4" t="n"/>
       <c r="V389" s="3" t="n"/>
       <c r="W389" s="4" t="n"/>
-      <c r="X389" s="3" t="n"/>
+      <c r="X389" s="4" t="n"/>
       <c r="Y389" s="4" t="n"/>
     </row>
     <row r="390">
@@ -11253,7 +11253,7 @@
       <c r="U390" s="2" t="n"/>
       <c r="V390" s="3" t="n"/>
       <c r="W390" s="2" t="n"/>
-      <c r="X390" s="3" t="n"/>
+      <c r="X390" s="2" t="n"/>
       <c r="Y390" s="2" t="n"/>
     </row>
     <row r="391">
@@ -11280,7 +11280,7 @@
       <c r="U391" s="4" t="n"/>
       <c r="V391" s="3" t="n"/>
       <c r="W391" s="4" t="n"/>
-      <c r="X391" s="3" t="n"/>
+      <c r="X391" s="4" t="n"/>
       <c r="Y391" s="4" t="n"/>
     </row>
     <row r="392">
@@ -11307,7 +11307,7 @@
       <c r="U392" s="2" t="n"/>
       <c r="V392" s="3" t="n"/>
       <c r="W392" s="2" t="n"/>
-      <c r="X392" s="3" t="n"/>
+      <c r="X392" s="2" t="n"/>
       <c r="Y392" s="2" t="n"/>
     </row>
     <row r="393">
@@ -11334,7 +11334,7 @@
       <c r="U393" s="4" t="n"/>
       <c r="V393" s="3" t="n"/>
       <c r="W393" s="4" t="n"/>
-      <c r="X393" s="3" t="n"/>
+      <c r="X393" s="4" t="n"/>
       <c r="Y393" s="4" t="n"/>
     </row>
     <row r="394">
@@ -11361,7 +11361,7 @@
       <c r="U394" s="2" t="n"/>
       <c r="V394" s="3" t="n"/>
       <c r="W394" s="2" t="n"/>
-      <c r="X394" s="3" t="n"/>
+      <c r="X394" s="2" t="n"/>
       <c r="Y394" s="2" t="n"/>
     </row>
     <row r="395">
@@ -11388,7 +11388,7 @@
       <c r="U395" s="4" t="n"/>
       <c r="V395" s="3" t="n"/>
       <c r="W395" s="4" t="n"/>
-      <c r="X395" s="3" t="n"/>
+      <c r="X395" s="4" t="n"/>
       <c r="Y395" s="4" t="n"/>
     </row>
     <row r="396">
@@ -11415,7 +11415,7 @@
       <c r="U396" s="2" t="n"/>
       <c r="V396" s="3" t="n"/>
       <c r="W396" s="2" t="n"/>
-      <c r="X396" s="3" t="n"/>
+      <c r="X396" s="2" t="n"/>
       <c r="Y396" s="2" t="n"/>
     </row>
     <row r="397">
@@ -11442,7 +11442,7 @@
       <c r="U397" s="4" t="n"/>
       <c r="V397" s="3" t="n"/>
       <c r="W397" s="4" t="n"/>
-      <c r="X397" s="3" t="n"/>
+      <c r="X397" s="4" t="n"/>
       <c r="Y397" s="4" t="n"/>
     </row>
     <row r="398">
@@ -11469,7 +11469,7 @@
       <c r="U398" s="2" t="n"/>
       <c r="V398" s="3" t="n"/>
       <c r="W398" s="2" t="n"/>
-      <c r="X398" s="3" t="n"/>
+      <c r="X398" s="2" t="n"/>
       <c r="Y398" s="2" t="n"/>
     </row>
     <row r="399">
@@ -11496,7 +11496,7 @@
       <c r="U399" s="4" t="n"/>
       <c r="V399" s="3" t="n"/>
       <c r="W399" s="4" t="n"/>
-      <c r="X399" s="3" t="n"/>
+      <c r="X399" s="4" t="n"/>
       <c r="Y399" s="4" t="n"/>
     </row>
     <row r="400">
@@ -11523,7 +11523,7 @@
       <c r="U400" s="2" t="n"/>
       <c r="V400" s="3" t="n"/>
       <c r="W400" s="2" t="n"/>
-      <c r="X400" s="3" t="n"/>
+      <c r="X400" s="2" t="n"/>
       <c r="Y400" s="2" t="n"/>
     </row>
     <row r="401">
@@ -11550,7 +11550,7 @@
       <c r="U401" s="4" t="n"/>
       <c r="V401" s="3" t="n"/>
       <c r="W401" s="4" t="n"/>
-      <c r="X401" s="3" t="n"/>
+      <c r="X401" s="4" t="n"/>
       <c r="Y401" s="4" t="n"/>
     </row>
     <row r="402">
@@ -11577,7 +11577,7 @@
       <c r="U402" s="2" t="n"/>
       <c r="V402" s="3" t="n"/>
       <c r="W402" s="2" t="n"/>
-      <c r="X402" s="3" t="n"/>
+      <c r="X402" s="2" t="n"/>
       <c r="Y402" s="2" t="n"/>
     </row>
     <row r="403">
@@ -11604,7 +11604,7 @@
       <c r="U403" s="4" t="n"/>
       <c r="V403" s="3" t="n"/>
       <c r="W403" s="4" t="n"/>
-      <c r="X403" s="3" t="n"/>
+      <c r="X403" s="4" t="n"/>
       <c r="Y403" s="4" t="n"/>
     </row>
     <row r="404">
@@ -11631,7 +11631,7 @@
       <c r="U404" s="2" t="n"/>
       <c r="V404" s="3" t="n"/>
       <c r="W404" s="2" t="n"/>
-      <c r="X404" s="3" t="n"/>
+      <c r="X404" s="2" t="n"/>
       <c r="Y404" s="2" t="n"/>
     </row>
     <row r="405">
@@ -11658,7 +11658,7 @@
       <c r="U405" s="4" t="n"/>
       <c r="V405" s="3" t="n"/>
       <c r="W405" s="4" t="n"/>
-      <c r="X405" s="3" t="n"/>
+      <c r="X405" s="4" t="n"/>
       <c r="Y405" s="4" t="n"/>
     </row>
     <row r="406">
@@ -11685,7 +11685,7 @@
       <c r="U406" s="2" t="n"/>
       <c r="V406" s="3" t="n"/>
       <c r="W406" s="2" t="n"/>
-      <c r="X406" s="3" t="n"/>
+      <c r="X406" s="2" t="n"/>
       <c r="Y406" s="2" t="n"/>
     </row>
     <row r="407">
@@ -11712,7 +11712,7 @@
       <c r="U407" s="4" t="n"/>
       <c r="V407" s="3" t="n"/>
       <c r="W407" s="4" t="n"/>
-      <c r="X407" s="3" t="n"/>
+      <c r="X407" s="4" t="n"/>
       <c r="Y407" s="4" t="n"/>
     </row>
     <row r="408">
@@ -11739,7 +11739,7 @@
       <c r="U408" s="2" t="n"/>
       <c r="V408" s="3" t="n"/>
       <c r="W408" s="2" t="n"/>
-      <c r="X408" s="3" t="n"/>
+      <c r="X408" s="2" t="n"/>
       <c r="Y408" s="2" t="n"/>
     </row>
     <row r="409">
@@ -11766,7 +11766,7 @@
       <c r="U409" s="4" t="n"/>
       <c r="V409" s="3" t="n"/>
       <c r="W409" s="4" t="n"/>
-      <c r="X409" s="3" t="n"/>
+      <c r="X409" s="4" t="n"/>
       <c r="Y409" s="4" t="n"/>
     </row>
     <row r="410">
@@ -11793,7 +11793,7 @@
       <c r="U410" s="2" t="n"/>
       <c r="V410" s="3" t="n"/>
       <c r="W410" s="2" t="n"/>
-      <c r="X410" s="3" t="n"/>
+      <c r="X410" s="2" t="n"/>
       <c r="Y410" s="2" t="n"/>
     </row>
     <row r="411">
@@ -11820,7 +11820,7 @@
       <c r="U411" s="4" t="n"/>
       <c r="V411" s="3" t="n"/>
       <c r="W411" s="4" t="n"/>
-      <c r="X411" s="3" t="n"/>
+      <c r="X411" s="4" t="n"/>
       <c r="Y411" s="4" t="n"/>
     </row>
     <row r="412">
@@ -11847,7 +11847,7 @@
       <c r="U412" s="2" t="n"/>
       <c r="V412" s="3" t="n"/>
       <c r="W412" s="2" t="n"/>
-      <c r="X412" s="3" t="n"/>
+      <c r="X412" s="2" t="n"/>
       <c r="Y412" s="2" t="n"/>
     </row>
     <row r="413">
@@ -11874,7 +11874,7 @@
       <c r="U413" s="4" t="n"/>
       <c r="V413" s="3" t="n"/>
       <c r="W413" s="4" t="n"/>
-      <c r="X413" s="3" t="n"/>
+      <c r="X413" s="4" t="n"/>
       <c r="Y413" s="4" t="n"/>
     </row>
     <row r="414">
@@ -11901,7 +11901,7 @@
       <c r="U414" s="2" t="n"/>
       <c r="V414" s="3" t="n"/>
       <c r="W414" s="2" t="n"/>
-      <c r="X414" s="3" t="n"/>
+      <c r="X414" s="2" t="n"/>
       <c r="Y414" s="2" t="n"/>
     </row>
     <row r="415">
@@ -11928,7 +11928,7 @@
       <c r="U415" s="4" t="n"/>
       <c r="V415" s="3" t="n"/>
       <c r="W415" s="4" t="n"/>
-      <c r="X415" s="3" t="n"/>
+      <c r="X415" s="4" t="n"/>
       <c r="Y415" s="4" t="n"/>
     </row>
     <row r="416">
@@ -11955,7 +11955,7 @@
       <c r="U416" s="2" t="n"/>
       <c r="V416" s="3" t="n"/>
       <c r="W416" s="2" t="n"/>
-      <c r="X416" s="3" t="n"/>
+      <c r="X416" s="2" t="n"/>
       <c r="Y416" s="2" t="n"/>
     </row>
     <row r="417">
@@ -11982,7 +11982,7 @@
       <c r="U417" s="4" t="n"/>
       <c r="V417" s="3" t="n"/>
       <c r="W417" s="4" t="n"/>
-      <c r="X417" s="3" t="n"/>
+      <c r="X417" s="4" t="n"/>
       <c r="Y417" s="4" t="n"/>
     </row>
     <row r="418">
@@ -12009,7 +12009,7 @@
       <c r="U418" s="2" t="n"/>
       <c r="V418" s="3" t="n"/>
       <c r="W418" s="2" t="n"/>
-      <c r="X418" s="3" t="n"/>
+      <c r="X418" s="2" t="n"/>
       <c r="Y418" s="2" t="n"/>
     </row>
     <row r="419">
@@ -12036,7 +12036,7 @@
       <c r="U419" s="4" t="n"/>
       <c r="V419" s="3" t="n"/>
       <c r="W419" s="4" t="n"/>
-      <c r="X419" s="3" t="n"/>
+      <c r="X419" s="4" t="n"/>
       <c r="Y419" s="4" t="n"/>
     </row>
     <row r="420">
@@ -12063,7 +12063,7 @@
       <c r="U420" s="2" t="n"/>
       <c r="V420" s="3" t="n"/>
       <c r="W420" s="2" t="n"/>
-      <c r="X420" s="3" t="n"/>
+      <c r="X420" s="2" t="n"/>
       <c r="Y420" s="2" t="n"/>
     </row>
     <row r="421">
@@ -12090,7 +12090,7 @@
       <c r="U421" s="4" t="n"/>
       <c r="V421" s="3" t="n"/>
       <c r="W421" s="4" t="n"/>
-      <c r="X421" s="3" t="n"/>
+      <c r="X421" s="4" t="n"/>
       <c r="Y421" s="4" t="n"/>
     </row>
     <row r="422">
@@ -12117,7 +12117,7 @@
       <c r="U422" s="2" t="n"/>
       <c r="V422" s="3" t="n"/>
       <c r="W422" s="2" t="n"/>
-      <c r="X422" s="3" t="n"/>
+      <c r="X422" s="2" t="n"/>
       <c r="Y422" s="2" t="n"/>
     </row>
     <row r="423">
@@ -12144,7 +12144,7 @@
       <c r="U423" s="4" t="n"/>
       <c r="V423" s="3" t="n"/>
       <c r="W423" s="4" t="n"/>
-      <c r="X423" s="3" t="n"/>
+      <c r="X423" s="4" t="n"/>
       <c r="Y423" s="4" t="n"/>
     </row>
     <row r="424">
@@ -12171,7 +12171,7 @@
       <c r="U424" s="2" t="n"/>
       <c r="V424" s="3" t="n"/>
       <c r="W424" s="2" t="n"/>
-      <c r="X424" s="3" t="n"/>
+      <c r="X424" s="2" t="n"/>
       <c r="Y424" s="2" t="n"/>
     </row>
     <row r="425">
@@ -12198,7 +12198,7 @@
       <c r="U425" s="4" t="n"/>
       <c r="V425" s="3" t="n"/>
       <c r="W425" s="4" t="n"/>
-      <c r="X425" s="3" t="n"/>
+      <c r="X425" s="4" t="n"/>
       <c r="Y425" s="4" t="n"/>
     </row>
     <row r="426">
@@ -12225,7 +12225,7 @@
       <c r="U426" s="2" t="n"/>
       <c r="V426" s="3" t="n"/>
       <c r="W426" s="2" t="n"/>
-      <c r="X426" s="3" t="n"/>
+      <c r="X426" s="2" t="n"/>
       <c r="Y426" s="2" t="n"/>
     </row>
     <row r="427">
@@ -12252,7 +12252,7 @@
       <c r="U427" s="4" t="n"/>
       <c r="V427" s="3" t="n"/>
       <c r="W427" s="4" t="n"/>
-      <c r="X427" s="3" t="n"/>
+      <c r="X427" s="4" t="n"/>
       <c r="Y427" s="4" t="n"/>
     </row>
     <row r="428">
@@ -12279,7 +12279,7 @@
       <c r="U428" s="2" t="n"/>
       <c r="V428" s="3" t="n"/>
       <c r="W428" s="2" t="n"/>
-      <c r="X428" s="3" t="n"/>
+      <c r="X428" s="2" t="n"/>
       <c r="Y428" s="2" t="n"/>
     </row>
     <row r="429">
@@ -12306,7 +12306,7 @@
       <c r="U429" s="4" t="n"/>
       <c r="V429" s="3" t="n"/>
       <c r="W429" s="4" t="n"/>
-      <c r="X429" s="3" t="n"/>
+      <c r="X429" s="4" t="n"/>
       <c r="Y429" s="4" t="n"/>
     </row>
     <row r="430">
@@ -12333,7 +12333,7 @@
       <c r="U430" s="2" t="n"/>
       <c r="V430" s="3" t="n"/>
       <c r="W430" s="2" t="n"/>
-      <c r="X430" s="3" t="n"/>
+      <c r="X430" s="2" t="n"/>
       <c r="Y430" s="2" t="n"/>
     </row>
     <row r="431">
@@ -12360,7 +12360,7 @@
       <c r="U431" s="4" t="n"/>
       <c r="V431" s="3" t="n"/>
       <c r="W431" s="4" t="n"/>
-      <c r="X431" s="3" t="n"/>
+      <c r="X431" s="4" t="n"/>
       <c r="Y431" s="4" t="n"/>
     </row>
     <row r="432">
@@ -12387,7 +12387,7 @@
       <c r="U432" s="2" t="n"/>
       <c r="V432" s="3" t="n"/>
       <c r="W432" s="2" t="n"/>
-      <c r="X432" s="3" t="n"/>
+      <c r="X432" s="2" t="n"/>
       <c r="Y432" s="2" t="n"/>
     </row>
     <row r="433">
@@ -12414,7 +12414,7 @@
       <c r="U433" s="4" t="n"/>
       <c r="V433" s="3" t="n"/>
       <c r="W433" s="4" t="n"/>
-      <c r="X433" s="3" t="n"/>
+      <c r="X433" s="4" t="n"/>
       <c r="Y433" s="4" t="n"/>
     </row>
     <row r="434">
@@ -12441,7 +12441,7 @@
       <c r="U434" s="2" t="n"/>
       <c r="V434" s="3" t="n"/>
       <c r="W434" s="2" t="n"/>
-      <c r="X434" s="3" t="n"/>
+      <c r="X434" s="2" t="n"/>
       <c r="Y434" s="2" t="n"/>
     </row>
     <row r="435">
@@ -12468,7 +12468,7 @@
       <c r="U435" s="4" t="n"/>
       <c r="V435" s="3" t="n"/>
       <c r="W435" s="4" t="n"/>
-      <c r="X435" s="3" t="n"/>
+      <c r="X435" s="4" t="n"/>
       <c r="Y435" s="4" t="n"/>
     </row>
     <row r="436">
@@ -12495,7 +12495,7 @@
       <c r="U436" s="2" t="n"/>
       <c r="V436" s="3" t="n"/>
       <c r="W436" s="2" t="n"/>
-      <c r="X436" s="3" t="n"/>
+      <c r="X436" s="2" t="n"/>
       <c r="Y436" s="2" t="n"/>
     </row>
     <row r="437">
@@ -12522,7 +12522,7 @@
       <c r="U437" s="4" t="n"/>
       <c r="V437" s="3" t="n"/>
       <c r="W437" s="4" t="n"/>
-      <c r="X437" s="3" t="n"/>
+      <c r="X437" s="4" t="n"/>
       <c r="Y437" s="4" t="n"/>
     </row>
     <row r="438">
@@ -12549,7 +12549,7 @@
       <c r="U438" s="2" t="n"/>
       <c r="V438" s="3" t="n"/>
       <c r="W438" s="2" t="n"/>
-      <c r="X438" s="3" t="n"/>
+      <c r="X438" s="2" t="n"/>
       <c r="Y438" s="2" t="n"/>
     </row>
     <row r="439">
@@ -12576,7 +12576,7 @@
       <c r="U439" s="4" t="n"/>
       <c r="V439" s="3" t="n"/>
       <c r="W439" s="4" t="n"/>
-      <c r="X439" s="3" t="n"/>
+      <c r="X439" s="4" t="n"/>
       <c r="Y439" s="4" t="n"/>
     </row>
     <row r="440">
@@ -12603,7 +12603,7 @@
       <c r="U440" s="2" t="n"/>
       <c r="V440" s="3" t="n"/>
       <c r="W440" s="2" t="n"/>
-      <c r="X440" s="3" t="n"/>
+      <c r="X440" s="2" t="n"/>
       <c r="Y440" s="2" t="n"/>
     </row>
     <row r="441">
@@ -12630,7 +12630,7 @@
       <c r="U441" s="4" t="n"/>
       <c r="V441" s="3" t="n"/>
       <c r="W441" s="4" t="n"/>
-      <c r="X441" s="3" t="n"/>
+      <c r="X441" s="4" t="n"/>
       <c r="Y441" s="4" t="n"/>
     </row>
     <row r="442">
@@ -12657,7 +12657,7 @@
       <c r="U442" s="2" t="n"/>
       <c r="V442" s="3" t="n"/>
       <c r="W442" s="2" t="n"/>
-      <c r="X442" s="3" t="n"/>
+      <c r="X442" s="2" t="n"/>
       <c r="Y442" s="2" t="n"/>
     </row>
     <row r="443">
@@ -12684,7 +12684,7 @@
       <c r="U443" s="4" t="n"/>
       <c r="V443" s="3" t="n"/>
       <c r="W443" s="4" t="n"/>
-      <c r="X443" s="3" t="n"/>
+      <c r="X443" s="4" t="n"/>
       <c r="Y443" s="4" t="n"/>
     </row>
     <row r="444">
@@ -12711,7 +12711,7 @@
       <c r="U444" s="2" t="n"/>
       <c r="V444" s="3" t="n"/>
       <c r="W444" s="2" t="n"/>
-      <c r="X444" s="3" t="n"/>
+      <c r="X444" s="2" t="n"/>
       <c r="Y444" s="2" t="n"/>
     </row>
     <row r="445">
@@ -12738,7 +12738,7 @@
       <c r="U445" s="4" t="n"/>
       <c r="V445" s="3" t="n"/>
       <c r="W445" s="4" t="n"/>
-      <c r="X445" s="3" t="n"/>
+      <c r="X445" s="4" t="n"/>
       <c r="Y445" s="4" t="n"/>
     </row>
     <row r="446">
@@ -12765,7 +12765,7 @@
       <c r="U446" s="2" t="n"/>
       <c r="V446" s="3" t="n"/>
       <c r="W446" s="2" t="n"/>
-      <c r="X446" s="3" t="n"/>
+      <c r="X446" s="2" t="n"/>
       <c r="Y446" s="2" t="n"/>
     </row>
     <row r="447">
@@ -12792,7 +12792,7 @@
       <c r="U447" s="4" t="n"/>
       <c r="V447" s="3" t="n"/>
       <c r="W447" s="4" t="n"/>
-      <c r="X447" s="3" t="n"/>
+      <c r="X447" s="4" t="n"/>
       <c r="Y447" s="4" t="n"/>
     </row>
     <row r="448">
@@ -12819,7 +12819,7 @@
       <c r="U448" s="2" t="n"/>
       <c r="V448" s="3" t="n"/>
       <c r="W448" s="2" t="n"/>
-      <c r="X448" s="3" t="n"/>
+      <c r="X448" s="2" t="n"/>
       <c r="Y448" s="2" t="n"/>
     </row>
     <row r="449">
@@ -12846,7 +12846,7 @@
       <c r="U449" s="4" t="n"/>
       <c r="V449" s="3" t="n"/>
       <c r="W449" s="4" t="n"/>
-      <c r="X449" s="3" t="n"/>
+      <c r="X449" s="4" t="n"/>
       <c r="Y449" s="4" t="n"/>
     </row>
     <row r="450">
@@ -12873,7 +12873,7 @@
       <c r="U450" s="2" t="n"/>
       <c r="V450" s="3" t="n"/>
       <c r="W450" s="2" t="n"/>
-      <c r="X450" s="3" t="n"/>
+      <c r="X450" s="2" t="n"/>
       <c r="Y450" s="2" t="n"/>
     </row>
     <row r="451">
@@ -12900,7 +12900,7 @@
       <c r="U451" s="4" t="n"/>
       <c r="V451" s="3" t="n"/>
       <c r="W451" s="4" t="n"/>
-      <c r="X451" s="3" t="n"/>
+      <c r="X451" s="4" t="n"/>
       <c r="Y451" s="4" t="n"/>
     </row>
     <row r="452">
@@ -12927,7 +12927,7 @@
       <c r="U452" s="2" t="n"/>
       <c r="V452" s="3" t="n"/>
       <c r="W452" s="2" t="n"/>
-      <c r="X452" s="3" t="n"/>
+      <c r="X452" s="2" t="n"/>
       <c r="Y452" s="2" t="n"/>
     </row>
     <row r="453">
@@ -12954,7 +12954,7 @@
       <c r="U453" s="4" t="n"/>
       <c r="V453" s="3" t="n"/>
       <c r="W453" s="4" t="n"/>
-      <c r="X453" s="3" t="n"/>
+      <c r="X453" s="4" t="n"/>
       <c r="Y453" s="4" t="n"/>
     </row>
     <row r="454">
@@ -12981,7 +12981,7 @@
       <c r="U454" s="2" t="n"/>
       <c r="V454" s="3" t="n"/>
       <c r="W454" s="2" t="n"/>
-      <c r="X454" s="3" t="n"/>
+      <c r="X454" s="2" t="n"/>
       <c r="Y454" s="2" t="n"/>
     </row>
     <row r="455">
@@ -13008,7 +13008,7 @@
       <c r="U455" s="4" t="n"/>
       <c r="V455" s="3" t="n"/>
       <c r="W455" s="4" t="n"/>
-      <c r="X455" s="3" t="n"/>
+      <c r="X455" s="4" t="n"/>
       <c r="Y455" s="4" t="n"/>
     </row>
     <row r="456">
@@ -13035,7 +13035,7 @@
       <c r="U456" s="2" t="n"/>
       <c r="V456" s="3" t="n"/>
       <c r="W456" s="2" t="n"/>
-      <c r="X456" s="3" t="n"/>
+      <c r="X456" s="2" t="n"/>
       <c r="Y456" s="2" t="n"/>
     </row>
     <row r="457">
@@ -13062,7 +13062,7 @@
       <c r="U457" s="4" t="n"/>
       <c r="V457" s="3" t="n"/>
       <c r="W457" s="4" t="n"/>
-      <c r="X457" s="3" t="n"/>
+      <c r="X457" s="4" t="n"/>
       <c r="Y457" s="4" t="n"/>
     </row>
     <row r="458">
@@ -13089,7 +13089,7 @@
       <c r="U458" s="2" t="n"/>
       <c r="V458" s="3" t="n"/>
       <c r="W458" s="2" t="n"/>
-      <c r="X458" s="3" t="n"/>
+      <c r="X458" s="2" t="n"/>
       <c r="Y458" s="2" t="n"/>
     </row>
     <row r="459">
@@ -13116,7 +13116,7 @@
       <c r="U459" s="4" t="n"/>
       <c r="V459" s="3" t="n"/>
       <c r="W459" s="4" t="n"/>
-      <c r="X459" s="3" t="n"/>
+      <c r="X459" s="4" t="n"/>
       <c r="Y459" s="4" t="n"/>
     </row>
     <row r="460">
@@ -13143,7 +13143,7 @@
       <c r="U460" s="2" t="n"/>
       <c r="V460" s="3" t="n"/>
       <c r="W460" s="2" t="n"/>
-      <c r="X460" s="3" t="n"/>
+      <c r="X460" s="2" t="n"/>
       <c r="Y460" s="2" t="n"/>
     </row>
     <row r="461">
@@ -13170,7 +13170,7 @@
       <c r="U461" s="4" t="n"/>
       <c r="V461" s="3" t="n"/>
       <c r="W461" s="4" t="n"/>
-      <c r="X461" s="3" t="n"/>
+      <c r="X461" s="4" t="n"/>
       <c r="Y461" s="4" t="n"/>
     </row>
     <row r="462">
@@ -13197,7 +13197,7 @@
       <c r="U462" s="2" t="n"/>
       <c r="V462" s="3" t="n"/>
       <c r="W462" s="2" t="n"/>
-      <c r="X462" s="3" t="n"/>
+      <c r="X462" s="2" t="n"/>
       <c r="Y462" s="2" t="n"/>
     </row>
     <row r="463">
@@ -13224,7 +13224,7 @@
       <c r="U463" s="4" t="n"/>
       <c r="V463" s="3" t="n"/>
       <c r="W463" s="4" t="n"/>
-      <c r="X463" s="3" t="n"/>
+      <c r="X463" s="4" t="n"/>
       <c r="Y463" s="4" t="n"/>
     </row>
     <row r="464">
@@ -13251,7 +13251,7 @@
       <c r="U464" s="2" t="n"/>
       <c r="V464" s="3" t="n"/>
       <c r="W464" s="2" t="n"/>
-      <c r="X464" s="3" t="n"/>
+      <c r="X464" s="2" t="n"/>
       <c r="Y464" s="2" t="n"/>
     </row>
     <row r="465">
@@ -13278,7 +13278,7 @@
       <c r="U465" s="4" t="n"/>
       <c r="V465" s="3" t="n"/>
       <c r="W465" s="4" t="n"/>
-      <c r="X465" s="3" t="n"/>
+      <c r="X465" s="4" t="n"/>
       <c r="Y465" s="4" t="n"/>
     </row>
     <row r="466">
@@ -13305,7 +13305,7 @@
       <c r="U466" s="2" t="n"/>
       <c r="V466" s="3" t="n"/>
       <c r="W466" s="2" t="n"/>
-      <c r="X466" s="3" t="n"/>
+      <c r="X466" s="2" t="n"/>
       <c r="Y466" s="2" t="n"/>
     </row>
     <row r="467">
@@ -13332,7 +13332,7 @@
       <c r="U467" s="4" t="n"/>
       <c r="V467" s="3" t="n"/>
       <c r="W467" s="4" t="n"/>
-      <c r="X467" s="3" t="n"/>
+      <c r="X467" s="4" t="n"/>
       <c r="Y467" s="4" t="n"/>
     </row>
     <row r="468">
@@ -13359,7 +13359,7 @@
       <c r="U468" s="2" t="n"/>
       <c r="V468" s="3" t="n"/>
       <c r="W468" s="2" t="n"/>
-      <c r="X468" s="3" t="n"/>
+      <c r="X468" s="2" t="n"/>
       <c r="Y468" s="2" t="n"/>
     </row>
     <row r="469">
@@ -13386,7 +13386,7 @@
       <c r="U469" s="4" t="n"/>
       <c r="V469" s="3" t="n"/>
       <c r="W469" s="4" t="n"/>
-      <c r="X469" s="3" t="n"/>
+      <c r="X469" s="4" t="n"/>
       <c r="Y469" s="4" t="n"/>
     </row>
     <row r="470">
@@ -13413,7 +13413,7 @@
       <c r="U470" s="2" t="n"/>
       <c r="V470" s="3" t="n"/>
       <c r="W470" s="2" t="n"/>
-      <c r="X470" s="3" t="n"/>
+      <c r="X470" s="2" t="n"/>
       <c r="Y470" s="2" t="n"/>
     </row>
     <row r="471">
@@ -13440,7 +13440,7 @@
       <c r="U471" s="4" t="n"/>
       <c r="V471" s="3" t="n"/>
       <c r="W471" s="4" t="n"/>
-      <c r="X471" s="3" t="n"/>
+      <c r="X471" s="4" t="n"/>
       <c r="Y471" s="4" t="n"/>
     </row>
     <row r="472">
@@ -13467,7 +13467,7 @@
       <c r="U472" s="2" t="n"/>
       <c r="V472" s="3" t="n"/>
       <c r="W472" s="2" t="n"/>
-      <c r="X472" s="3" t="n"/>
+      <c r="X472" s="2" t="n"/>
       <c r="Y472" s="2" t="n"/>
     </row>
     <row r="473">
@@ -13494,7 +13494,7 @@
       <c r="U473" s="4" t="n"/>
       <c r="V473" s="3" t="n"/>
       <c r="W473" s="4" t="n"/>
-      <c r="X473" s="3" t="n"/>
+      <c r="X473" s="4" t="n"/>
       <c r="Y473" s="4" t="n"/>
     </row>
     <row r="474">
@@ -13521,7 +13521,7 @@
       <c r="U474" s="2" t="n"/>
       <c r="V474" s="3" t="n"/>
       <c r="W474" s="2" t="n"/>
-      <c r="X474" s="3" t="n"/>
+      <c r="X474" s="2" t="n"/>
       <c r="Y474" s="2" t="n"/>
     </row>
     <row r="475">
@@ -13548,7 +13548,7 @@
       <c r="U475" s="4" t="n"/>
       <c r="V475" s="3" t="n"/>
       <c r="W475" s="4" t="n"/>
-      <c r="X475" s="3" t="n"/>
+      <c r="X475" s="4" t="n"/>
       <c r="Y475" s="4" t="n"/>
     </row>
     <row r="476">
@@ -13575,7 +13575,7 @@
       <c r="U476" s="2" t="n"/>
       <c r="V476" s="3" t="n"/>
       <c r="W476" s="2" t="n"/>
-      <c r="X476" s="3" t="n"/>
+      <c r="X476" s="2" t="n"/>
       <c r="Y476" s="2" t="n"/>
     </row>
     <row r="477">
@@ -13602,7 +13602,7 @@
       <c r="U477" s="4" t="n"/>
       <c r="V477" s="3" t="n"/>
       <c r="W477" s="4" t="n"/>
-      <c r="X477" s="3" t="n"/>
+      <c r="X477" s="4" t="n"/>
       <c r="Y477" s="4" t="n"/>
     </row>
     <row r="478">
@@ -13629,7 +13629,7 @@
       <c r="U478" s="2" t="n"/>
       <c r="V478" s="3" t="n"/>
       <c r="W478" s="2" t="n"/>
-      <c r="X478" s="3" t="n"/>
+      <c r="X478" s="2" t="n"/>
       <c r="Y478" s="2" t="n"/>
     </row>
     <row r="479">
@@ -13656,7 +13656,7 @@
       <c r="U479" s="4" t="n"/>
       <c r="V479" s="3" t="n"/>
       <c r="W479" s="4" t="n"/>
-      <c r="X479" s="3" t="n"/>
+      <c r="X479" s="4" t="n"/>
       <c r="Y479" s="4" t="n"/>
     </row>
     <row r="480">
@@ -13683,7 +13683,7 @@
       <c r="U480" s="2" t="n"/>
       <c r="V480" s="3" t="n"/>
       <c r="W480" s="2" t="n"/>
-      <c r="X480" s="3" t="n"/>
+      <c r="X480" s="2" t="n"/>
       <c r="Y480" s="2" t="n"/>
     </row>
     <row r="481">
@@ -13710,7 +13710,7 @@
       <c r="U481" s="4" t="n"/>
       <c r="V481" s="3" t="n"/>
       <c r="W481" s="4" t="n"/>
-      <c r="X481" s="3" t="n"/>
+      <c r="X481" s="4" t="n"/>
       <c r="Y481" s="4" t="n"/>
     </row>
     <row r="482">
@@ -13737,7 +13737,7 @@
       <c r="U482" s="2" t="n"/>
       <c r="V482" s="3" t="n"/>
       <c r="W482" s="2" t="n"/>
-      <c r="X482" s="3" t="n"/>
+      <c r="X482" s="2" t="n"/>
       <c r="Y482" s="2" t="n"/>
     </row>
     <row r="483">
@@ -13764,7 +13764,7 @@
       <c r="U483" s="4" t="n"/>
       <c r="V483" s="3" t="n"/>
       <c r="W483" s="4" t="n"/>
-      <c r="X483" s="3" t="n"/>
+      <c r="X483" s="4" t="n"/>
       <c r="Y483" s="4" t="n"/>
     </row>
     <row r="484">
@@ -13791,7 +13791,7 @@
       <c r="U484" s="2" t="n"/>
       <c r="V484" s="3" t="n"/>
       <c r="W484" s="2" t="n"/>
-      <c r="X484" s="3" t="n"/>
+      <c r="X484" s="2" t="n"/>
       <c r="Y484" s="2" t="n"/>
     </row>
     <row r="485">
@@ -13818,7 +13818,7 @@
       <c r="U485" s="4" t="n"/>
       <c r="V485" s="3" t="n"/>
       <c r="W485" s="4" t="n"/>
-      <c r="X485" s="3" t="n"/>
+      <c r="X485" s="4" t="n"/>
       <c r="Y485" s="4" t="n"/>
     </row>
     <row r="486">
@@ -13845,7 +13845,7 @@
       <c r="U486" s="2" t="n"/>
       <c r="V486" s="3" t="n"/>
       <c r="W486" s="2" t="n"/>
-      <c r="X486" s="3" t="n"/>
+      <c r="X486" s="2" t="n"/>
       <c r="Y486" s="2" t="n"/>
     </row>
     <row r="487">
@@ -13872,7 +13872,7 @@
       <c r="U487" s="4" t="n"/>
       <c r="V487" s="3" t="n"/>
       <c r="W487" s="4" t="n"/>
-      <c r="X487" s="3" t="n"/>
+      <c r="X487" s="4" t="n"/>
       <c r="Y487" s="4" t="n"/>
     </row>
     <row r="488">
@@ -13899,7 +13899,7 @@
       <c r="U488" s="2" t="n"/>
       <c r="V488" s="3" t="n"/>
       <c r="W488" s="2" t="n"/>
-      <c r="X488" s="3" t="n"/>
+      <c r="X488" s="2" t="n"/>
       <c r="Y488" s="2" t="n"/>
     </row>
     <row r="489">
@@ -13926,7 +13926,7 @@
       <c r="U489" s="4" t="n"/>
       <c r="V489" s="3" t="n"/>
       <c r="W489" s="4" t="n"/>
-      <c r="X489" s="3" t="n"/>
+      <c r="X489" s="4" t="n"/>
       <c r="Y489" s="4" t="n"/>
     </row>
     <row r="490">
@@ -13953,7 +13953,7 @@
       <c r="U490" s="2" t="n"/>
       <c r="V490" s="3" t="n"/>
       <c r="W490" s="2" t="n"/>
-      <c r="X490" s="3" t="n"/>
+      <c r="X490" s="2" t="n"/>
       <c r="Y490" s="2" t="n"/>
     </row>
     <row r="491">
@@ -13980,7 +13980,7 @@
       <c r="U491" s="4" t="n"/>
       <c r="V491" s="3" t="n"/>
       <c r="W491" s="4" t="n"/>
-      <c r="X491" s="3" t="n"/>
+      <c r="X491" s="4" t="n"/>
       <c r="Y491" s="4" t="n"/>
     </row>
     <row r="492">
@@ -14007,7 +14007,7 @@
       <c r="U492" s="2" t="n"/>
       <c r="V492" s="3" t="n"/>
       <c r="W492" s="2" t="n"/>
-      <c r="X492" s="3" t="n"/>
+      <c r="X492" s="2" t="n"/>
       <c r="Y492" s="2" t="n"/>
     </row>
     <row r="493">
@@ -14034,7 +14034,7 @@
       <c r="U493" s="4" t="n"/>
       <c r="V493" s="3" t="n"/>
       <c r="W493" s="4" t="n"/>
-      <c r="X493" s="3" t="n"/>
+      <c r="X493" s="4" t="n"/>
       <c r="Y493" s="4" t="n"/>
     </row>
     <row r="494">
@@ -14061,7 +14061,7 @@
       <c r="U494" s="2" t="n"/>
       <c r="V494" s="3" t="n"/>
       <c r="W494" s="2" t="n"/>
-      <c r="X494" s="3" t="n"/>
+      <c r="X494" s="2" t="n"/>
       <c r="Y494" s="2" t="n"/>
     </row>
     <row r="495">
@@ -14088,7 +14088,7 @@
       <c r="U495" s="4" t="n"/>
       <c r="V495" s="3" t="n"/>
       <c r="W495" s="4" t="n"/>
-      <c r="X495" s="3" t="n"/>
+      <c r="X495" s="4" t="n"/>
       <c r="Y495" s="4" t="n"/>
     </row>
     <row r="496">
@@ -14115,7 +14115,7 @@
       <c r="U496" s="2" t="n"/>
       <c r="V496" s="3" t="n"/>
       <c r="W496" s="2" t="n"/>
-      <c r="X496" s="3" t="n"/>
+      <c r="X496" s="2" t="n"/>
       <c r="Y496" s="2" t="n"/>
     </row>
     <row r="497">
@@ -14142,7 +14142,7 @@
       <c r="U497" s="4" t="n"/>
       <c r="V497" s="3" t="n"/>
       <c r="W497" s="4" t="n"/>
-      <c r="X497" s="3" t="n"/>
+      <c r="X497" s="4" t="n"/>
       <c r="Y497" s="4" t="n"/>
     </row>
     <row r="498">
@@ -14169,7 +14169,7 @@
       <c r="U498" s="2" t="n"/>
       <c r="V498" s="3" t="n"/>
       <c r="W498" s="2" t="n"/>
-      <c r="X498" s="3" t="n"/>
+      <c r="X498" s="2" t="n"/>
       <c r="Y498" s="2" t="n"/>
     </row>
     <row r="499">
@@ -14196,7 +14196,7 @@
       <c r="U499" s="4" t="n"/>
       <c r="V499" s="3" t="n"/>
       <c r="W499" s="4" t="n"/>
-      <c r="X499" s="3" t="n"/>
+      <c r="X499" s="4" t="n"/>
       <c r="Y499" s="4" t="n"/>
     </row>
     <row r="500">
@@ -14223,7 +14223,7 @@
       <c r="U500" s="2" t="n"/>
       <c r="V500" s="3" t="n"/>
       <c r="W500" s="2" t="n"/>
-      <c r="X500" s="3" t="n"/>
+      <c r="X500" s="2" t="n"/>
       <c r="Y500" s="2" t="n"/>
     </row>
     <row r="501">
@@ -14250,7 +14250,7 @@
       <c r="U501" s="4" t="n"/>
       <c r="V501" s="3" t="n"/>
       <c r="W501" s="4" t="n"/>
-      <c r="X501" s="3" t="n"/>
+      <c r="X501" s="4" t="n"/>
       <c r="Y501" s="4" t="n"/>
     </row>
     <row r="502">
@@ -14277,7 +14277,7 @@
       <c r="U502" s="2" t="n"/>
       <c r="V502" s="3" t="n"/>
       <c r="W502" s="2" t="n"/>
-      <c r="X502" s="3" t="n"/>
+      <c r="X502" s="2" t="n"/>
       <c r="Y502" s="2" t="n"/>
     </row>
     <row r="503">
@@ -14304,7 +14304,7 @@
       <c r="U503" s="4" t="n"/>
       <c r="V503" s="3" t="n"/>
       <c r="W503" s="4" t="n"/>
-      <c r="X503" s="3" t="n"/>
+      <c r="X503" s="4" t="n"/>
       <c r="Y503" s="4" t="n"/>
     </row>
     <row r="504">
@@ -14331,7 +14331,7 @@
       <c r="U504" s="2" t="n"/>
       <c r="V504" s="3" t="n"/>
       <c r="W504" s="2" t="n"/>
-      <c r="X504" s="3" t="n"/>
+      <c r="X504" s="2" t="n"/>
       <c r="Y504" s="2" t="n"/>
     </row>
     <row r="505">
@@ -14358,7 +14358,7 @@
       <c r="U505" s="4" t="n"/>
       <c r="V505" s="3" t="n"/>
       <c r="W505" s="4" t="n"/>
-      <c r="X505" s="3" t="n"/>
+      <c r="X505" s="4" t="n"/>
       <c r="Y505" s="4" t="n"/>
     </row>
     <row r="506">
@@ -14385,7 +14385,7 @@
       <c r="U506" s="2" t="n"/>
       <c r="V506" s="3" t="n"/>
       <c r="W506" s="2" t="n"/>
-      <c r="X506" s="3" t="n"/>
+      <c r="X506" s="2" t="n"/>
       <c r="Y506" s="2" t="n"/>
     </row>
     <row r="507">
@@ -14412,7 +14412,7 @@
       <c r="U507" s="4" t="n"/>
       <c r="V507" s="3" t="n"/>
       <c r="W507" s="4" t="n"/>
-      <c r="X507" s="3" t="n"/>
+      <c r="X507" s="4" t="n"/>
       <c r="Y507" s="4" t="n"/>
     </row>
     <row r="508">
@@ -14439,7 +14439,7 @@
       <c r="U508" s="2" t="n"/>
       <c r="V508" s="3" t="n"/>
       <c r="W508" s="2" t="n"/>
-      <c r="X508" s="3" t="n"/>
+      <c r="X508" s="2" t="n"/>
       <c r="Y508" s="2" t="n"/>
     </row>
     <row r="509">
@@ -14466,7 +14466,7 @@
       <c r="U509" s="4" t="n"/>
       <c r="V509" s="3" t="n"/>
       <c r="W509" s="4" t="n"/>
-      <c r="X509" s="3" t="n"/>
+      <c r="X509" s="4" t="n"/>
       <c r="Y509" s="4" t="n"/>
     </row>
     <row r="510">
@@ -14493,7 +14493,7 @@
       <c r="U510" s="2" t="n"/>
       <c r="V510" s="3" t="n"/>
       <c r="W510" s="2" t="n"/>
-      <c r="X510" s="3" t="n"/>
+      <c r="X510" s="2" t="n"/>
       <c r="Y510" s="2" t="n"/>
     </row>
     <row r="511">
@@ -14520,7 +14520,7 @@
       <c r="U511" s="4" t="n"/>
       <c r="V511" s="3" t="n"/>
       <c r="W511" s="4" t="n"/>
-      <c r="X511" s="3" t="n"/>
+      <c r="X511" s="4" t="n"/>
       <c r="Y511" s="4" t="n"/>
     </row>
     <row r="512">
@@ -14547,7 +14547,7 @@
       <c r="U512" s="2" t="n"/>
       <c r="V512" s="3" t="n"/>
       <c r="W512" s="2" t="n"/>
-      <c r="X512" s="3" t="n"/>
+      <c r="X512" s="2" t="n"/>
       <c r="Y512" s="2" t="n"/>
     </row>
     <row r="513">
@@ -14574,7 +14574,7 @@
       <c r="U513" s="4" t="n"/>
       <c r="V513" s="3" t="n"/>
       <c r="W513" s="4" t="n"/>
-      <c r="X513" s="3" t="n"/>
+      <c r="X513" s="4" t="n"/>
       <c r="Y513" s="4" t="n"/>
     </row>
     <row r="514">
@@ -14601,7 +14601,7 @@
       <c r="U514" s="2" t="n"/>
       <c r="V514" s="3" t="n"/>
       <c r="W514" s="2" t="n"/>
-      <c r="X514" s="3" t="n"/>
+      <c r="X514" s="2" t="n"/>
       <c r="Y514" s="2" t="n"/>
     </row>
     <row r="515">
@@ -14628,7 +14628,7 @@
       <c r="U515" s="4" t="n"/>
       <c r="V515" s="3" t="n"/>
       <c r="W515" s="4" t="n"/>
-      <c r="X515" s="3" t="n"/>
+      <c r="X515" s="4" t="n"/>
       <c r="Y515" s="4" t="n"/>
     </row>
     <row r="516">
@@ -14655,7 +14655,7 @@
       <c r="U516" s="2" t="n"/>
       <c r="V516" s="3" t="n"/>
       <c r="W516" s="2" t="n"/>
-      <c r="X516" s="3" t="n"/>
+      <c r="X516" s="2" t="n"/>
       <c r="Y516" s="2" t="n"/>
     </row>
     <row r="517">
@@ -14682,7 +14682,7 @@
       <c r="U517" s="4" t="n"/>
       <c r="V517" s="3" t="n"/>
       <c r="W517" s="4" t="n"/>
-      <c r="X517" s="3" t="n"/>
+      <c r="X517" s="4" t="n"/>
       <c r="Y517" s="4" t="n"/>
     </row>
     <row r="518">
@@ -14709,7 +14709,7 @@
       <c r="U518" s="2" t="n"/>
       <c r="V518" s="3" t="n"/>
       <c r="W518" s="2" t="n"/>
-      <c r="X518" s="3" t="n"/>
+      <c r="X518" s="2" t="n"/>
       <c r="Y518" s="2" t="n"/>
     </row>
     <row r="519">
@@ -14736,7 +14736,7 @@
       <c r="U519" s="4" t="n"/>
       <c r="V519" s="3" t="n"/>
       <c r="W519" s="4" t="n"/>
-      <c r="X519" s="3" t="n"/>
+      <c r="X519" s="4" t="n"/>
       <c r="Y519" s="4" t="n"/>
     </row>
     <row r="520">
@@ -14763,7 +14763,7 @@
       <c r="U520" s="2" t="n"/>
       <c r="V520" s="3" t="n"/>
       <c r="W520" s="2" t="n"/>
-      <c r="X520" s="3" t="n"/>
+      <c r="X520" s="2" t="n"/>
       <c r="Y520" s="2" t="n"/>
     </row>
     <row r="521">
@@ -14790,7 +14790,7 @@
       <c r="U521" s="4" t="n"/>
       <c r="V521" s="3" t="n"/>
       <c r="W521" s="4" t="n"/>
-      <c r="X521" s="3" t="n"/>
+      <c r="X521" s="4" t="n"/>
       <c r="Y521" s="4" t="n"/>
     </row>
     <row r="522">
@@ -14817,7 +14817,7 @@
       <c r="U522" s="2" t="n"/>
       <c r="V522" s="3" t="n"/>
       <c r="W522" s="2" t="n"/>
-      <c r="X522" s="3" t="n"/>
+      <c r="X522" s="2" t="n"/>
       <c r="Y522" s="2" t="n"/>
     </row>
     <row r="523">
@@ -14844,7 +14844,7 @@
       <c r="U523" s="4" t="n"/>
       <c r="V523" s="3" t="n"/>
       <c r="W523" s="4" t="n"/>
-      <c r="X523" s="3" t="n"/>
+      <c r="X523" s="4" t="n"/>
       <c r="Y523" s="4" t="n"/>
     </row>
     <row r="524">
@@ -14871,7 +14871,7 @@
       <c r="U524" s="2" t="n"/>
       <c r="V524" s="3" t="n"/>
       <c r="W524" s="2" t="n"/>
-      <c r="X524" s="3" t="n"/>
+      <c r="X524" s="2" t="n"/>
       <c r="Y524" s="2" t="n"/>
     </row>
     <row r="525">
@@ -14898,7 +14898,7 @@
       <c r="U525" s="4" t="n"/>
       <c r="V525" s="3" t="n"/>
       <c r="W525" s="4" t="n"/>
-      <c r="X525" s="3" t="n"/>
+      <c r="X525" s="4" t="n"/>
       <c r="Y525" s="4" t="n"/>
     </row>
     <row r="526">
@@ -14925,7 +14925,7 @@
       <c r="U526" s="2" t="n"/>
       <c r="V526" s="3" t="n"/>
       <c r="W526" s="2" t="n"/>
-      <c r="X526" s="3" t="n"/>
+      <c r="X526" s="2" t="n"/>
       <c r="Y526" s="2" t="n"/>
     </row>
     <row r="527">
@@ -14952,7 +14952,7 @@
       <c r="U527" s="4" t="n"/>
       <c r="V527" s="3" t="n"/>
       <c r="W527" s="4" t="n"/>
-      <c r="X527" s="3" t="n"/>
+      <c r="X527" s="4" t="n"/>
       <c r="Y527" s="4" t="n"/>
     </row>
     <row r="528">
@@ -14979,7 +14979,7 @@
       <c r="U528" s="2" t="n"/>
       <c r="V528" s="3" t="n"/>
       <c r="W528" s="2" t="n"/>
-      <c r="X528" s="3" t="n"/>
+      <c r="X528" s="2" t="n"/>
       <c r="Y528" s="2" t="n"/>
     </row>
     <row r="529">
@@ -15006,7 +15006,7 @@
       <c r="U529" s="4" t="n"/>
       <c r="V529" s="3" t="n"/>
       <c r="W529" s="4" t="n"/>
-      <c r="X529" s="3" t="n"/>
+      <c r="X529" s="4" t="n"/>
       <c r="Y529" s="4" t="n"/>
     </row>
     <row r="530">
@@ -15033,7 +15033,7 @@
       <c r="U530" s="2" t="n"/>
       <c r="V530" s="3" t="n"/>
       <c r="W530" s="2" t="n"/>
-      <c r="X530" s="3" t="n"/>
+      <c r="X530" s="2" t="n"/>
       <c r="Y530" s="2" t="n"/>
     </row>
     <row r="531">
@@ -15060,7 +15060,7 @@
       <c r="U531" s="4" t="n"/>
       <c r="V531" s="3" t="n"/>
       <c r="W531" s="4" t="n"/>
-      <c r="X531" s="3" t="n"/>
+      <c r="X531" s="4" t="n"/>
       <c r="Y531" s="4" t="n"/>
     </row>
     <row r="532">
@@ -15087,7 +15087,7 @@
       <c r="U532" s="2" t="n"/>
       <c r="V532" s="3" t="n"/>
       <c r="W532" s="2" t="n"/>
-      <c r="X532" s="3" t="n"/>
+      <c r="X532" s="2" t="n"/>
       <c r="Y532" s="2" t="n"/>
     </row>
     <row r="533">
@@ -15114,7 +15114,7 @@
       <c r="U533" s="4" t="n"/>
       <c r="V533" s="3" t="n"/>
       <c r="W533" s="4" t="n"/>
-      <c r="X533" s="3" t="n"/>
+      <c r="X533" s="4" t="n"/>
       <c r="Y533" s="4" t="n"/>
     </row>
     <row r="534">
@@ -15141,7 +15141,7 @@
       <c r="U534" s="2" t="n"/>
       <c r="V534" s="3" t="n"/>
       <c r="W534" s="2" t="n"/>
-      <c r="X534" s="3" t="n"/>
+      <c r="X534" s="2" t="n"/>
       <c r="Y534" s="2" t="n"/>
     </row>
     <row r="535">
@@ -15168,7 +15168,7 @@
       <c r="U535" s="4" t="n"/>
       <c r="V535" s="3" t="n"/>
       <c r="W535" s="4" t="n"/>
-      <c r="X535" s="3" t="n"/>
+      <c r="X535" s="4" t="n"/>
       <c r="Y535" s="4" t="n"/>
     </row>
     <row r="536">
@@ -15195,7 +15195,7 @@
       <c r="U536" s="2" t="n"/>
       <c r="V536" s="3" t="n"/>
       <c r="W536" s="2" t="n"/>
-      <c r="X536" s="3" t="n"/>
+      <c r="X536" s="2" t="n"/>
       <c r="Y536" s="2" t="n"/>
     </row>
     <row r="537">
@@ -15222,7 +15222,7 @@
       <c r="U537" s="4" t="n"/>
       <c r="V537" s="3" t="n"/>
       <c r="W537" s="4" t="n"/>
-      <c r="X537" s="3" t="n"/>
+      <c r="X537" s="4" t="n"/>
       <c r="Y537" s="4" t="n"/>
     </row>
     <row r="538">
@@ -15249,7 +15249,7 @@
       <c r="U538" s="2" t="n"/>
       <c r="V538" s="3" t="n"/>
       <c r="W538" s="2" t="n"/>
-      <c r="X538" s="3" t="n"/>
+      <c r="X538" s="2" t="n"/>
       <c r="Y538" s="2" t="n"/>
     </row>
     <row r="539">
@@ -15276,7 +15276,7 @@
       <c r="U539" s="4" t="n"/>
       <c r="V539" s="3" t="n"/>
       <c r="W539" s="4" t="n"/>
-      <c r="X539" s="3" t="n"/>
+      <c r="X539" s="4" t="n"/>
       <c r="Y539" s="4" t="n"/>
     </row>
     <row r="540">
@@ -15303,7 +15303,7 @@
       <c r="U540" s="2" t="n"/>
       <c r="V540" s="3" t="n"/>
       <c r="W540" s="2" t="n"/>
-      <c r="X540" s="3" t="n"/>
+      <c r="X540" s="2" t="n"/>
       <c r="Y540" s="2" t="n"/>
     </row>
     <row r="541">
@@ -15330,7 +15330,7 @@
       <c r="U541" s="4" t="n"/>
       <c r="V541" s="3" t="n"/>
       <c r="W541" s="4" t="n"/>
-      <c r="X541" s="3" t="n"/>
+      <c r="X541" s="4" t="n"/>
       <c r="Y541" s="4" t="n"/>
     </row>
     <row r="542">
@@ -15357,7 +15357,7 @@
       <c r="U542" s="2" t="n"/>
       <c r="V542" s="3" t="n"/>
       <c r="W542" s="2" t="n"/>
-      <c r="X542" s="3" t="n"/>
+      <c r="X542" s="2" t="n"/>
       <c r="Y542" s="2" t="n"/>
     </row>
     <row r="543">
@@ -15384,7 +15384,7 @@
       <c r="U543" s="4" t="n"/>
       <c r="V543" s="3" t="n"/>
       <c r="W543" s="4" t="n"/>
-      <c r="X543" s="3" t="n"/>
+      <c r="X543" s="4" t="n"/>
       <c r="Y543" s="4" t="n"/>
     </row>
     <row r="544">
@@ -15411,7 +15411,7 @@
       <c r="U544" s="2" t="n"/>
       <c r="V544" s="3" t="n"/>
       <c r="W544" s="2" t="n"/>
-      <c r="X544" s="3" t="n"/>
+      <c r="X544" s="2" t="n"/>
       <c r="Y544" s="2" t="n"/>
     </row>
     <row r="545">
@@ -15438,7 +15438,7 @@
       <c r="U545" s="4" t="n"/>
       <c r="V545" s="3" t="n"/>
       <c r="W545" s="4" t="n"/>
-      <c r="X545" s="3" t="n"/>
+      <c r="X545" s="4" t="n"/>
       <c r="Y545" s="4" t="n"/>
     </row>
     <row r="546">
@@ -15465,7 +15465,7 @@
       <c r="U546" s="2" t="n"/>
       <c r="V546" s="3" t="n"/>
       <c r="W546" s="2" t="n"/>
-      <c r="X546" s="3" t="n"/>
+      <c r="X546" s="2" t="n"/>
       <c r="Y546" s="2" t="n"/>
     </row>
     <row r="547">
@@ -15492,7 +15492,7 @@
       <c r="U547" s="4" t="n"/>
       <c r="V547" s="3" t="n"/>
       <c r="W547" s="4" t="n"/>
-      <c r="X547" s="3" t="n"/>
+      <c r="X547" s="4" t="n"/>
       <c r="Y547" s="4" t="n"/>
     </row>
     <row r="548">
@@ -15519,7 +15519,7 @@
       <c r="U548" s="2" t="n"/>
       <c r="V548" s="3" t="n"/>
       <c r="W548" s="2" t="n"/>
-      <c r="X548" s="3" t="n"/>
+      <c r="X548" s="2" t="n"/>
       <c r="Y548" s="2" t="n"/>
     </row>
     <row r="549">
@@ -15546,7 +15546,7 @@
       <c r="U549" s="4" t="n"/>
       <c r="V549" s="3" t="n"/>
       <c r="W549" s="4" t="n"/>
-      <c r="X549" s="3" t="n"/>
+      <c r="X549" s="4" t="n"/>
       <c r="Y549" s="4" t="n"/>
     </row>
     <row r="550">
@@ -15573,7 +15573,7 @@
       <c r="U550" s="2" t="n"/>
       <c r="V550" s="3" t="n"/>
       <c r="W550" s="2" t="n"/>
-      <c r="X550" s="3" t="n"/>
+      <c r="X550" s="2" t="n"/>
       <c r="Y550" s="2" t="n"/>
     </row>
     <row r="551">
@@ -15600,7 +15600,7 @@
       <c r="U551" s="4" t="n"/>
       <c r="V551" s="3" t="n"/>
       <c r="W551" s="4" t="n"/>
-      <c r="X551" s="3" t="n"/>
+      <c r="X551" s="4" t="n"/>
       <c r="Y551" s="4" t="n"/>
     </row>
     <row r="552">
@@ -15627,7 +15627,7 @@
       <c r="U552" s="2" t="n"/>
       <c r="V552" s="3" t="n"/>
       <c r="W552" s="2" t="n"/>
-      <c r="X552" s="3" t="n"/>
+      <c r="X552" s="2" t="n"/>
       <c r="Y552" s="2" t="n"/>
     </row>
     <row r="553">
@@ -15654,7 +15654,7 @@
       <c r="U553" s="4" t="n"/>
       <c r="V553" s="3" t="n"/>
       <c r="W553" s="4" t="n"/>
-      <c r="X553" s="3" t="n"/>
+      <c r="X553" s="4" t="n"/>
       <c r="Y553" s="4" t="n"/>
     </row>
     <row r="554">
@@ -15681,7 +15681,7 @@
       <c r="U554" s="2" t="n"/>
       <c r="V554" s="3" t="n"/>
       <c r="W554" s="2" t="n"/>
-      <c r="X554" s="3" t="n"/>
+      <c r="X554" s="2" t="n"/>
       <c r="Y554" s="2" t="n"/>
     </row>
     <row r="555">
@@ -15708,7 +15708,7 @@
       <c r="U555" s="4" t="n"/>
       <c r="V555" s="3" t="n"/>
       <c r="W555" s="4" t="n"/>
-      <c r="X555" s="3" t="n"/>
+      <c r="X555" s="4" t="n"/>
       <c r="Y555" s="4" t="n"/>
     </row>
     <row r="556">
@@ -15735,7 +15735,7 @@
       <c r="U556" s="2" t="n"/>
       <c r="V556" s="3" t="n"/>
       <c r="W556" s="2" t="n"/>
-      <c r="X556" s="3" t="n"/>
+      <c r="X556" s="2" t="n"/>
       <c r="Y556" s="2" t="n"/>
     </row>
     <row r="557">
@@ -15762,7 +15762,7 @@
       <c r="U557" s="4" t="n"/>
       <c r="V557" s="3" t="n"/>
       <c r="W557" s="4" t="n"/>
-      <c r="X557" s="3" t="n"/>
+      <c r="X557" s="4" t="n"/>
       <c r="Y557" s="4" t="n"/>
     </row>
     <row r="558">
@@ -15789,7 +15789,7 @@
       <c r="U558" s="2" t="n"/>
       <c r="V558" s="3" t="n"/>
       <c r="W558" s="2" t="n"/>
-      <c r="X558" s="3" t="n"/>
+      <c r="X558" s="2" t="n"/>
       <c r="Y558" s="2" t="n"/>
     </row>
     <row r="559">
@@ -15816,7 +15816,7 @@
       <c r="U559" s="4" t="n"/>
       <c r="V559" s="3" t="n"/>
       <c r="W559" s="4" t="n"/>
-      <c r="X559" s="3" t="n"/>
+      <c r="X559" s="4" t="n"/>
       <c r="Y559" s="4" t="n"/>
     </row>
     <row r="560">
@@ -15843,7 +15843,7 @@
       <c r="U560" s="2" t="n"/>
       <c r="V560" s="3" t="n"/>
       <c r="W560" s="2" t="n"/>
-      <c r="X560" s="3" t="n"/>
+      <c r="X560" s="2" t="n"/>
       <c r="Y560" s="2" t="n"/>
     </row>
     <row r="561">
@@ -15870,7 +15870,7 @@
       <c r="U561" s="4" t="n"/>
       <c r="V561" s="3" t="n"/>
       <c r="W561" s="4" t="n"/>
-      <c r="X561" s="3" t="n"/>
+      <c r="X561" s="4" t="n"/>
       <c r="Y561" s="4" t="n"/>
     </row>
     <row r="562">
@@ -15897,7 +15897,7 @@
       <c r="U562" s="2" t="n"/>
       <c r="V562" s="3" t="n"/>
       <c r="W562" s="2" t="n"/>
-      <c r="X562" s="3" t="n"/>
+      <c r="X562" s="2" t="n"/>
       <c r="Y562" s="2" t="n"/>
     </row>
     <row r="563">
@@ -15924,7 +15924,7 @@
       <c r="U563" s="4" t="n"/>
       <c r="V563" s="3" t="n"/>
       <c r="W563" s="4" t="n"/>
-      <c r="X563" s="3" t="n"/>
+      <c r="X563" s="4" t="n"/>
       <c r="Y563" s="4" t="n"/>
     </row>
     <row r="564">
@@ -15951,7 +15951,7 @@
       <c r="U564" s="2" t="n"/>
       <c r="V564" s="3" t="n"/>
       <c r="W564" s="2" t="n"/>
-      <c r="X564" s="3" t="n"/>
+      <c r="X564" s="2" t="n"/>
       <c r="Y564" s="2" t="n"/>
     </row>
     <row r="565">
@@ -15978,7 +15978,7 @@
       <c r="U565" s="4" t="n"/>
       <c r="V565" s="3" t="n"/>
       <c r="W565" s="4" t="n"/>
-      <c r="X565" s="3" t="n"/>
+      <c r="X565" s="4" t="n"/>
       <c r="Y565" s="4" t="n"/>
     </row>
     <row r="566">
@@ -16005,7 +16005,7 @@
       <c r="U566" s="2" t="n"/>
       <c r="V566" s="3" t="n"/>
       <c r="W566" s="2" t="n"/>
-      <c r="X566" s="3" t="n"/>
+      <c r="X566" s="2" t="n"/>
       <c r="Y566" s="2" t="n"/>
     </row>
     <row r="567">
@@ -16032,7 +16032,7 @@
       <c r="U567" s="4" t="n"/>
       <c r="V567" s="3" t="n"/>
       <c r="W567" s="4" t="n"/>
-      <c r="X567" s="3" t="n"/>
+      <c r="X567" s="4" t="n"/>
       <c r="Y567" s="4" t="n"/>
     </row>
     <row r="568">
@@ -16059,7 +16059,7 @@
       <c r="U568" s="2" t="n"/>
       <c r="V568" s="3" t="n"/>
       <c r="W568" s="2" t="n"/>
-      <c r="X568" s="3" t="n"/>
+      <c r="X568" s="2" t="n"/>
       <c r="Y568" s="2" t="n"/>
     </row>
     <row r="569">
@@ -16086,7 +16086,7 @@
       <c r="U569" s="4" t="n"/>
       <c r="V569" s="3" t="n"/>
       <c r="W569" s="4" t="n"/>
-      <c r="X569" s="3" t="n"/>
+      <c r="X569" s="4" t="n"/>
       <c r="Y569" s="4" t="n"/>
     </row>
     <row r="570">
@@ -16113,7 +16113,7 @@
       <c r="U570" s="2" t="n"/>
       <c r="V570" s="3" t="n"/>
       <c r="W570" s="2" t="n"/>
-      <c r="X570" s="3" t="n"/>
+      <c r="X570" s="2" t="n"/>
       <c r="Y570" s="2" t="n"/>
     </row>
     <row r="571">
@@ -16140,7 +16140,7 @@
       <c r="U571" s="4" t="n"/>
       <c r="V571" s="3" t="n"/>
       <c r="W571" s="4" t="n"/>
-      <c r="X571" s="3" t="n"/>
+      <c r="X571" s="4" t="n"/>
       <c r="Y571" s="4" t="n"/>
     </row>
     <row r="572">
@@ -16167,7 +16167,7 @@
       <c r="U572" s="2" t="n"/>
       <c r="V572" s="3" t="n"/>
       <c r="W572" s="2" t="n"/>
-      <c r="X572" s="3" t="n"/>
+      <c r="X572" s="2" t="n"/>
       <c r="Y572" s="2" t="n"/>
     </row>
     <row r="573">
@@ -16194,7 +16194,7 @@
       <c r="U573" s="4" t="n"/>
       <c r="V573" s="3" t="n"/>
       <c r="W573" s="4" t="n"/>
-      <c r="X573" s="3" t="n"/>
+      <c r="X573" s="4" t="n"/>
       <c r="Y573" s="4" t="n"/>
     </row>
     <row r="574">
@@ -16221,7 +16221,7 @@
       <c r="U574" s="2" t="n"/>
       <c r="V574" s="3" t="n"/>
       <c r="W574" s="2" t="n"/>
-      <c r="X574" s="3" t="n"/>
+      <c r="X574" s="2" t="n"/>
       <c r="Y574" s="2" t="n"/>
     </row>
     <row r="575">
@@ -16248,7 +16248,7 @@
       <c r="U575" s="4" t="n"/>
       <c r="V575" s="3" t="n"/>
       <c r="W575" s="4" t="n"/>
-      <c r="X575" s="3" t="n"/>
+      <c r="X575" s="4" t="n"/>
       <c r="Y575" s="4" t="n"/>
     </row>
     <row r="576">
@@ -16275,7 +16275,7 @@
       <c r="U576" s="2" t="n"/>
       <c r="V576" s="3" t="n"/>
       <c r="W576" s="2" t="n"/>
-      <c r="X576" s="3" t="n"/>
+      <c r="X576" s="2" t="n"/>
       <c r="Y576" s="2" t="n"/>
     </row>
     <row r="577">
@@ -16302,7 +16302,7 @@
       <c r="U577" s="4" t="n"/>
       <c r="V577" s="3" t="n"/>
       <c r="W577" s="4" t="n"/>
-      <c r="X577" s="3" t="n"/>
+      <c r="X577" s="4" t="n"/>
       <c r="Y577" s="4" t="n"/>
     </row>
     <row r="578">
@@ -16329,7 +16329,7 @@
       <c r="U578" s="2" t="n"/>
       <c r="V578" s="3" t="n"/>
       <c r="W578" s="2" t="n"/>
-      <c r="X578" s="3" t="n"/>
+      <c r="X578" s="2" t="n"/>
       <c r="Y578" s="2" t="n"/>
     </row>
     <row r="579">
@@ -16356,7 +16356,7 @@
       <c r="U579" s="4" t="n"/>
       <c r="V579" s="3" t="n"/>
       <c r="W579" s="4" t="n"/>
-      <c r="X579" s="3" t="n"/>
+      <c r="X579" s="4" t="n"/>
       <c r="Y579" s="4" t="n"/>
     </row>
     <row r="580">
@@ -16383,7 +16383,7 @@
       <c r="U580" s="2" t="n"/>
       <c r="V580" s="3" t="n"/>
       <c r="W580" s="2" t="n"/>
-      <c r="X580" s="3" t="n"/>
+      <c r="X580" s="2" t="n"/>
       <c r="Y580" s="2" t="n"/>
     </row>
     <row r="581">
@@ -16410,7 +16410,7 @@
       <c r="U581" s="4" t="n"/>
       <c r="V581" s="3" t="n"/>
       <c r="W581" s="4" t="n"/>
-      <c r="X581" s="3" t="n"/>
+      <c r="X581" s="4" t="n"/>
       <c r="Y581" s="4" t="n"/>
     </row>
     <row r="582">
@@ -16437,7 +16437,7 @@
       <c r="U582" s="2" t="n"/>
       <c r="V582" s="3" t="n"/>
       <c r="W582" s="2" t="n"/>
-      <c r="X582" s="3" t="n"/>
+      <c r="X582" s="2" t="n"/>
       <c r="Y582" s="2" t="n"/>
     </row>
     <row r="583">
@@ -16464,7 +16464,7 @@
       <c r="U583" s="4" t="n"/>
       <c r="V583" s="3" t="n"/>
       <c r="W583" s="4" t="n"/>
-      <c r="X583" s="3" t="n"/>
+      <c r="X583" s="4" t="n"/>
       <c r="Y583" s="4" t="n"/>
     </row>
     <row r="584">
@@ -16491,7 +16491,7 @@
       <c r="U584" s="2" t="n"/>
       <c r="V584" s="3" t="n"/>
       <c r="W584" s="2" t="n"/>
-      <c r="X584" s="3" t="n"/>
+      <c r="X584" s="2" t="n"/>
       <c r="Y584" s="2" t="n"/>
     </row>
     <row r="585">
@@ -16518,7 +16518,7 @@
       <c r="U585" s="4" t="n"/>
       <c r="V585" s="3" t="n"/>
       <c r="W585" s="4" t="n"/>
-      <c r="X585" s="3" t="n"/>
+      <c r="X585" s="4" t="n"/>
       <c r="Y585" s="4" t="n"/>
     </row>
     <row r="586">
@@ -16545,7 +16545,7 @@
       <c r="U586" s="2" t="n"/>
       <c r="V586" s="3" t="n"/>
       <c r="W586" s="2" t="n"/>
-      <c r="X586" s="3" t="n"/>
+      <c r="X586" s="2" t="n"/>
       <c r="Y586" s="2" t="n"/>
     </row>
     <row r="587">
@@ -16572,7 +16572,7 @@
       <c r="U587" s="4" t="n"/>
       <c r="V587" s="3" t="n"/>
       <c r="W587" s="4" t="n"/>
-      <c r="X587" s="3" t="n"/>
+      <c r="X587" s="4" t="n"/>
       <c r="Y587" s="4" t="n"/>
     </row>
     <row r="588">
@@ -16599,7 +16599,7 @@
       <c r="U588" s="2" t="n"/>
       <c r="V588" s="3" t="n"/>
       <c r="W588" s="2" t="n"/>
-      <c r="X588" s="3" t="n"/>
+      <c r="X588" s="2" t="n"/>
       <c r="Y588" s="2" t="n"/>
     </row>
     <row r="589">
@@ -16626,7 +16626,7 @@
       <c r="U589" s="4" t="n"/>
       <c r="V589" s="3" t="n"/>
       <c r="W589" s="4" t="n"/>
-      <c r="X589" s="3" t="n"/>
+      <c r="X589" s="4" t="n"/>
       <c r="Y589" s="4" t="n"/>
     </row>
     <row r="590">
@@ -16653,7 +16653,7 @@
       <c r="U590" s="2" t="n"/>
       <c r="V590" s="3" t="n"/>
       <c r="W590" s="2" t="n"/>
-      <c r="X590" s="3" t="n"/>
+      <c r="X590" s="2" t="n"/>
       <c r="Y590" s="2" t="n"/>
     </row>
     <row r="591">
@@ -16680,7 +16680,7 @@
       <c r="U591" s="4" t="n"/>
       <c r="V591" s="3" t="n"/>
       <c r="W591" s="4" t="n"/>
-      <c r="X591" s="3" t="n"/>
+      <c r="X591" s="4" t="n"/>
       <c r="Y591" s="4" t="n"/>
     </row>
     <row r="592">
@@ -16707,7 +16707,7 @@
       <c r="U592" s="2" t="n"/>
       <c r="V592" s="3" t="n"/>
       <c r="W592" s="2" t="n"/>
-      <c r="X592" s="3" t="n"/>
+      <c r="X592" s="2" t="n"/>
       <c r="Y592" s="2" t="n"/>
     </row>
     <row r="593">
@@ -16734,7 +16734,7 @@
       <c r="U593" s="4" t="n"/>
       <c r="V593" s="3" t="n"/>
       <c r="W593" s="4" t="n"/>
-      <c r="X593" s="3" t="n"/>
+      <c r="X593" s="4" t="n"/>
       <c r="Y593" s="4" t="n"/>
     </row>
     <row r="594">
@@ -16761,7 +16761,7 @@
       <c r="U594" s="2" t="n"/>
       <c r="V594" s="3" t="n"/>
       <c r="W594" s="2" t="n"/>
-      <c r="X594" s="3" t="n"/>
+      <c r="X594" s="2" t="n"/>
       <c r="Y594" s="2" t="n"/>
     </row>
     <row r="595">
@@ -16788,7 +16788,7 @@
       <c r="U595" s="4" t="n"/>
       <c r="V595" s="3" t="n"/>
       <c r="W595" s="4" t="n"/>
-      <c r="X595" s="3" t="n"/>
+      <c r="X595" s="4" t="n"/>
       <c r="Y595" s="4" t="n"/>
     </row>
     <row r="596">
@@ -16815,7 +16815,7 @@
       <c r="U596" s="2" t="n"/>
       <c r="V596" s="3" t="n"/>
       <c r="W596" s="2" t="n"/>
-      <c r="X596" s="3" t="n"/>
+      <c r="X596" s="2" t="n"/>
       <c r="Y596" s="2" t="n"/>
     </row>
     <row r="597">
@@ -16842,7 +16842,7 @@
       <c r="U597" s="4" t="n"/>
       <c r="V597" s="3" t="n"/>
       <c r="W597" s="4" t="n"/>
-      <c r="X597" s="3" t="n"/>
+      <c r="X597" s="4" t="n"/>
       <c r="Y597" s="4" t="n"/>
     </row>
     <row r="598">
@@ -16869,7 +16869,7 @@
       <c r="U598" s="2" t="n"/>
       <c r="V598" s="3" t="n"/>
       <c r="W598" s="2" t="n"/>
-      <c r="X598" s="3" t="n"/>
+      <c r="X598" s="2" t="n"/>
       <c r="Y598" s="2" t="n"/>
     </row>
     <row r="599">
@@ -16896,7 +16896,7 @@
       <c r="U599" s="4" t="n"/>
       <c r="V599" s="3" t="n"/>
       <c r="W599" s="4" t="n"/>
-      <c r="X599" s="3" t="n"/>
+      <c r="X599" s="4" t="n"/>
       <c r="Y599" s="4" t="n"/>
     </row>
     <row r="600">
@@ -16923,7 +16923,7 @@
       <c r="U600" s="2" t="n"/>
       <c r="V600" s="3" t="n"/>
       <c r="W600" s="2" t="n"/>
-      <c r="X600" s="3" t="n"/>
+      <c r="X600" s="2" t="n"/>
       <c r="Y600" s="2" t="n"/>
     </row>
     <row r="601">
@@ -16950,7 +16950,7 @@
       <c r="U601" s="4" t="n"/>
       <c r="V601" s="3" t="n"/>
       <c r="W601" s="4" t="n"/>
-      <c r="X601" s="3" t="n"/>
+      <c r="X601" s="4" t="n"/>
       <c r="Y601" s="4" t="n"/>
     </row>
     <row r="602">
@@ -16977,7 +16977,7 @@
       <c r="U602" s="2" t="n"/>
       <c r="V602" s="3" t="n"/>
       <c r="W602" s="2" t="n"/>
-      <c r="X602" s="3" t="n"/>
+      <c r="X602" s="2" t="n"/>
       <c r="Y602" s="2" t="n"/>
     </row>
     <row r="603">
@@ -17004,7 +17004,7 @@
       <c r="U603" s="4" t="n"/>
       <c r="V603" s="3" t="n"/>
       <c r="W603" s="4" t="n"/>
-      <c r="X603" s="3" t="n"/>
+      <c r="X603" s="4" t="n"/>
       <c r="Y603" s="4" t="n"/>
     </row>
     <row r="604">
@@ -17031,7 +17031,7 @@
       <c r="U604" s="2" t="n"/>
       <c r="V604" s="3" t="n"/>
       <c r="W604" s="2" t="n"/>
-      <c r="X604" s="3" t="n"/>
+      <c r="X604" s="2" t="n"/>
       <c r="Y604" s="2" t="n"/>
     </row>
     <row r="605">
@@ -17058,7 +17058,7 @@
       <c r="U605" s="4" t="n"/>
       <c r="V605" s="3" t="n"/>
       <c r="W605" s="4" t="n"/>
-      <c r="X605" s="3" t="n"/>
+      <c r="X605" s="4" t="n"/>
       <c r="Y605" s="4" t="n"/>
     </row>
     <row r="606">
@@ -17085,7 +17085,7 @@
       <c r="U606" s="2" t="n"/>
       <c r="V606" s="3" t="n"/>
       <c r="W606" s="2" t="n"/>
-      <c r="X606" s="3" t="n"/>
+      <c r="X606" s="2" t="n"/>
       <c r="Y606" s="2" t="n"/>
     </row>
     <row r="607">
@@ -17112,7 +17112,7 @@
       <c r="U607" s="4" t="n"/>
       <c r="V607" s="3" t="n"/>
       <c r="W607" s="4" t="n"/>
-      <c r="X607" s="3" t="n"/>
+      <c r="X607" s="4" t="n"/>
       <c r="Y607" s="4" t="n"/>
     </row>
     <row r="608">
@@ -17139,7 +17139,7 @@
       <c r="U608" s="2" t="n"/>
       <c r="V608" s="3" t="n"/>
       <c r="W608" s="2" t="n"/>
-      <c r="X608" s="3" t="n"/>
+      <c r="X608" s="2" t="n"/>
       <c r="Y608" s="2" t="n"/>
     </row>
     <row r="609">
@@ -17166,7 +17166,7 @@
       <c r="U609" s="4" t="n"/>
       <c r="V609" s="3" t="n"/>
       <c r="W609" s="4" t="n"/>
-      <c r="X609" s="3" t="n"/>
+      <c r="X609" s="4" t="n"/>
       <c r="Y609" s="4" t="n"/>
     </row>
     <row r="610">
@@ -17193,7 +17193,7 @@
       <c r="U610" s="2" t="n"/>
       <c r="V610" s="3" t="n"/>
       <c r="W610" s="2" t="n"/>
-      <c r="X610" s="3" t="n"/>
+      <c r="X610" s="2" t="n"/>
       <c r="Y610" s="2" t="n"/>
     </row>
     <row r="611">
@@ -17220,7 +17220,7 @@
       <c r="U611" s="4" t="n"/>
       <c r="V611" s="3" t="n"/>
       <c r="W611" s="4" t="n"/>
-      <c r="X611" s="3" t="n"/>
+      <c r="X611" s="4" t="n"/>
       <c r="Y611" s="4" t="n"/>
     </row>
     <row r="612">
@@ -17247,7 +17247,7 @@
       <c r="U612" s="2" t="n"/>
       <c r="V612" s="3" t="n"/>
       <c r="W612" s="2" t="n"/>
-      <c r="X612" s="3" t="n"/>
+      <c r="X612" s="2" t="n"/>
       <c r="Y612" s="2" t="n"/>
     </row>
     <row r="613">
@@ -17274,7 +17274,7 @@
       <c r="U613" s="4" t="n"/>
       <c r="V613" s="3" t="n"/>
       <c r="W613" s="4" t="n"/>
-      <c r="X613" s="3" t="n"/>
+      <c r="X613" s="4" t="n"/>
       <c r="Y613" s="4" t="n"/>
     </row>
     <row r="614">
@@ -17301,7 +17301,7 @@
       <c r="U614" s="2" t="n"/>
       <c r="V614" s="3" t="n"/>
       <c r="W614" s="2" t="n"/>
-      <c r="X614" s="3" t="n"/>
+      <c r="X614" s="2" t="n"/>
       <c r="Y614" s="2" t="n"/>
     </row>
     <row r="615">
@@ -17328,7 +17328,7 @@
       <c r="U615" s="4" t="n"/>
       <c r="V615" s="3" t="n"/>
       <c r="W615" s="4" t="n"/>
-      <c r="X615" s="3" t="n"/>
+      <c r="X615" s="4" t="n"/>
       <c r="Y615" s="4" t="n"/>
     </row>
     <row r="616">
@@ -17355,7 +17355,7 @@
       <c r="U616" s="2" t="n"/>
       <c r="V616" s="3" t="n"/>
       <c r="W616" s="2" t="n"/>
-      <c r="X616" s="3" t="n"/>
+      <c r="X616" s="2" t="n"/>
       <c r="Y616" s="2" t="n"/>
     </row>
     <row r="617">
@@ -17382,7 +17382,7 @@
       <c r="U617" s="4" t="n"/>
       <c r="V617" s="3" t="n"/>
       <c r="W617" s="4" t="n"/>
-      <c r="X617" s="3" t="n"/>
+      <c r="X617" s="4" t="n"/>
       <c r="Y617" s="4" t="n"/>
     </row>
     <row r="618">
@@ -17409,7 +17409,7 @@
       <c r="U618" s="2" t="n"/>
       <c r="V618" s="3" t="n"/>
       <c r="W618" s="2" t="n"/>
-      <c r="X618" s="3" t="n"/>
+      <c r="X618" s="2" t="n"/>
       <c r="Y618" s="2" t="n"/>
     </row>
     <row r="619">
@@ -17436,7 +17436,7 @@
       <c r="U619" s="4" t="n"/>
       <c r="V619" s="3" t="n"/>
       <c r="W619" s="4" t="n"/>
-      <c r="X619" s="3" t="n"/>
+      <c r="X619" s="4" t="n"/>
       <c r="Y619" s="4" t="n"/>
     </row>
     <row r="620">
@@ -17463,7 +17463,7 @@
       <c r="U620" s="2" t="n"/>
       <c r="V620" s="3" t="n"/>
       <c r="W620" s="2" t="n"/>
-      <c r="X620" s="3" t="n"/>
+      <c r="X620" s="2" t="n"/>
       <c r="Y620" s="2" t="n"/>
     </row>
     <row r="621">
@@ -17490,7 +17490,7 @@
       <c r="U621" s="4" t="n"/>
       <c r="V621" s="3" t="n"/>
       <c r="W621" s="4" t="n"/>
-      <c r="X621" s="3" t="n"/>
+      <c r="X621" s="4" t="n"/>
       <c r="Y621" s="4" t="n"/>
     </row>
     <row r="622">
@@ -17517,7 +17517,7 @@
       <c r="U622" s="2" t="n"/>
       <c r="V622" s="3" t="n"/>
       <c r="W622" s="2" t="n"/>
-      <c r="X622" s="3" t="n"/>
+      <c r="X622" s="2" t="n"/>
       <c r="Y622" s="2" t="n"/>
     </row>
     <row r="623">
@@ -17544,7 +17544,7 @@
       <c r="U623" s="4" t="n"/>
       <c r="V623" s="3" t="n"/>
       <c r="W623" s="4" t="n"/>
-      <c r="X623" s="3" t="n"/>
+      <c r="X623" s="4" t="n"/>
       <c r="Y623" s="4" t="n"/>
     </row>
     <row r="624">
@@ -17571,7 +17571,7 @@
       <c r="U624" s="2" t="n"/>
       <c r="V624" s="3" t="n"/>
       <c r="W624" s="2" t="n"/>
-      <c r="X624" s="3" t="n"/>
+      <c r="X624" s="2" t="n"/>
       <c r="Y624" s="2" t="n"/>
     </row>
     <row r="625">
@@ -17598,7 +17598,7 @@
       <c r="U625" s="4" t="n"/>
       <c r="V625" s="3" t="n"/>
       <c r="W625" s="4" t="n"/>
-      <c r="X625" s="3" t="n"/>
+      <c r="X625" s="4" t="n"/>
       <c r="Y625" s="4" t="n"/>
     </row>
     <row r="626">
@@ -17625,7 +17625,7 @@
       <c r="U626" s="2" t="n"/>
       <c r="V626" s="3" t="n"/>
       <c r="W626" s="2" t="n"/>
-      <c r="X626" s="3" t="n"/>
+      <c r="X626" s="2" t="n"/>
       <c r="Y626" s="2" t="n"/>
     </row>
     <row r="627">
@@ -17652,7 +17652,7 @@
       <c r="U627" s="4" t="n"/>
       <c r="V627" s="3" t="n"/>
       <c r="W627" s="4" t="n"/>
-      <c r="X627" s="3" t="n"/>
+      <c r="X627" s="4" t="n"/>
       <c r="Y627" s="4" t="n"/>
     </row>
     <row r="628">
@@ -17679,7 +17679,7 @@
       <c r="U628" s="2" t="n"/>
       <c r="V628" s="3" t="n"/>
       <c r="W628" s="2" t="n"/>
-      <c r="X628" s="3" t="n"/>
+      <c r="X628" s="2" t="n"/>
       <c r="Y628" s="2" t="n"/>
     </row>
     <row r="629">
@@ -17706,7 +17706,7 @@
       <c r="U629" s="4" t="n"/>
       <c r="V629" s="3" t="n"/>
       <c r="W629" s="4" t="n"/>
-      <c r="X629" s="3" t="n"/>
+      <c r="X629" s="4" t="n"/>
       <c r="Y629" s="4" t="n"/>
     </row>
     <row r="630">
@@ -17733,7 +17733,7 @@
       <c r="U630" s="2" t="n"/>
       <c r="V630" s="3" t="n"/>
       <c r="W630" s="2" t="n"/>
-      <c r="X630" s="3" t="n"/>
+      <c r="X630" s="2" t="n"/>
       <c r="Y630" s="2" t="n"/>
     </row>
     <row r="631">
@@ -17760,7 +17760,7 @@
       <c r="U631" s="4" t="n"/>
       <c r="V631" s="3" t="n"/>
       <c r="W631" s="4" t="n"/>
-      <c r="X631" s="3" t="n"/>
+      <c r="X631" s="4" t="n"/>
       <c r="Y631" s="4" t="n"/>
     </row>
     <row r="632">
@@ -17787,7 +17787,7 @@
       <c r="U632" s="2" t="n"/>
       <c r="V632" s="3" t="n"/>
       <c r="W632" s="2" t="n"/>
-      <c r="X632" s="3" t="n"/>
+      <c r="X632" s="2" t="n"/>
       <c r="Y632" s="2" t="n"/>
     </row>
     <row r="633">
@@ -17814,7 +17814,7 @@
       <c r="U633" s="4" t="n"/>
       <c r="V633" s="3" t="n"/>
       <c r="W633" s="4" t="n"/>
-      <c r="X633" s="3" t="n"/>
+      <c r="X633" s="4" t="n"/>
       <c r="Y633" s="4" t="n"/>
     </row>
     <row r="634">
@@ -17841,7 +17841,7 @@
       <c r="U634" s="2" t="n"/>
       <c r="V634" s="3" t="n"/>
       <c r="W634" s="2" t="n"/>
-      <c r="X634" s="3" t="n"/>
+      <c r="X634" s="2" t="n"/>
       <c r="Y634" s="2" t="n"/>
     </row>
     <row r="635">
@@ -17868,7 +17868,7 @@
       <c r="U635" s="4" t="n"/>
       <c r="V635" s="3" t="n"/>
       <c r="W635" s="4" t="n"/>
-      <c r="X635" s="3" t="n"/>
+      <c r="X635" s="4" t="n"/>
       <c r="Y635" s="4" t="n"/>
     </row>
     <row r="636">
@@ -17895,7 +17895,7 @@
       <c r="U636" s="2" t="n"/>
       <c r="V636" s="3" t="n"/>
       <c r="W636" s="2" t="n"/>
-      <c r="X636" s="3" t="n"/>
+      <c r="X636" s="2" t="n"/>
       <c r="Y636" s="2" t="n"/>
     </row>
     <row r="637">
@@ -17922,7 +17922,7 @@
       <c r="U637" s="4" t="n"/>
       <c r="V637" s="3" t="n"/>
       <c r="W637" s="4" t="n"/>
-      <c r="X637" s="3" t="n"/>
+      <c r="X637" s="4" t="n"/>
       <c r="Y637" s="4" t="n"/>
     </row>
     <row r="638">
@@ -17949,7 +17949,7 @@
       <c r="U638" s="2" t="n"/>
       <c r="V638" s="3" t="n"/>
       <c r="W638" s="2" t="n"/>
-      <c r="X638" s="3" t="n"/>
+      <c r="X638" s="2" t="n"/>
       <c r="Y638" s="2" t="n"/>
     </row>
     <row r="639">
@@ -17976,7 +17976,7 @@
       <c r="U639" s="4" t="n"/>
       <c r="V639" s="3" t="n"/>
       <c r="W639" s="4" t="n"/>
-      <c r="X639" s="3" t="n"/>
+      <c r="X639" s="4" t="n"/>
       <c r="Y639" s="4" t="n"/>
     </row>
     <row r="640">
@@ -18003,7 +18003,7 @@
       <c r="U640" s="2" t="n"/>
       <c r="V640" s="3" t="n"/>
       <c r="W640" s="2" t="n"/>
-      <c r="X640" s="3" t="n"/>
+      <c r="X640" s="2" t="n"/>
       <c r="Y640" s="2" t="n"/>
     </row>
     <row r="641">
@@ -18030,7 +18030,7 @@
       <c r="U641" s="4" t="n"/>
       <c r="V641" s="3" t="n"/>
       <c r="W641" s="4" t="n"/>
-      <c r="X641" s="3" t="n"/>
+      <c r="X641" s="4" t="n"/>
       <c r="Y641" s="4" t="n"/>
     </row>
     <row r="642">
@@ -18057,7 +18057,7 @@
       <c r="U642" s="2" t="n"/>
       <c r="V642" s="3" t="n"/>
       <c r="W642" s="2" t="n"/>
-      <c r="X642" s="3" t="n"/>
+      <c r="X642" s="2" t="n"/>
       <c r="Y642" s="2" t="n"/>
     </row>
     <row r="643">
@@ -18084,7 +18084,7 @@
       <c r="U643" s="4" t="n"/>
       <c r="V643" s="3" t="n"/>
       <c r="W643" s="4" t="n"/>
-      <c r="X643" s="3" t="n"/>
+      <c r="X643" s="4" t="n"/>
       <c r="Y643" s="4" t="n"/>
     </row>
     <row r="644">
@@ -18111,7 +18111,7 @@
       <c r="U644" s="2" t="n"/>
       <c r="V644" s="3" t="n"/>
       <c r="W644" s="2" t="n"/>
-      <c r="X644" s="3" t="n"/>
+      <c r="X644" s="2" t="n"/>
       <c r="Y644" s="2" t="n"/>
     </row>
     <row r="645">
@@ -18138,7 +18138,7 @@
       <c r="U645" s="4" t="n"/>
       <c r="V645" s="3" t="n"/>
       <c r="W645" s="4" t="n"/>
-      <c r="X645" s="3" t="n"/>
+      <c r="X645" s="4" t="n"/>
       <c r="Y645" s="4" t="n"/>
     </row>
     <row r="646">
@@ -18165,7 +18165,7 @@
       <c r="U646" s="2" t="n"/>
       <c r="V646" s="3" t="n"/>
       <c r="W646" s="2" t="n"/>
-      <c r="X646" s="3" t="n"/>
+      <c r="X646" s="2" t="n"/>
       <c r="Y646" s="2" t="n"/>
     </row>
     <row r="647">
@@ -18192,7 +18192,7 @@
       <c r="U647" s="4" t="n"/>
       <c r="V647" s="3" t="n"/>
       <c r="W647" s="4" t="n"/>
-      <c r="X647" s="3" t="n"/>
+      <c r="X647" s="4" t="n"/>
       <c r="Y647" s="4" t="n"/>
     </row>
     <row r="648">
@@ -18219,7 +18219,7 @@
       <c r="U648" s="2" t="n"/>
       <c r="V648" s="3" t="n"/>
       <c r="W648" s="2" t="n"/>
-      <c r="X648" s="3" t="n"/>
+      <c r="X648" s="2" t="n"/>
       <c r="Y648" s="2" t="n"/>
     </row>
     <row r="649">
@@ -18246,7 +18246,7 @@
       <c r="U649" s="4" t="n"/>
       <c r="V649" s="3" t="n"/>
       <c r="W649" s="4" t="n"/>
-      <c r="X649" s="3" t="n"/>
+      <c r="X649" s="4" t="n"/>
       <c r="Y649" s="4" t="n"/>
     </row>
     <row r="650">
@@ -18273,7 +18273,7 @@
       <c r="U650" s="2" t="n"/>
       <c r="V650" s="3" t="n"/>
       <c r="W650" s="2" t="n"/>
-      <c r="X650" s="3" t="n"/>
+      <c r="X650" s="2" t="n"/>
       <c r="Y650" s="2" t="n"/>
     </row>
     <row r="651">
@@ -18300,7 +18300,7 @@
       <c r="U651" s="4" t="n"/>
       <c r="V651" s="3" t="n"/>
       <c r="W651" s="4" t="n"/>
-      <c r="X651" s="3" t="n"/>
+      <c r="X651" s="4" t="n"/>
       <c r="Y651" s="4" t="n"/>
     </row>
     <row r="652">
@@ -18327,7 +18327,7 @@
       <c r="U652" s="2" t="n"/>
       <c r="V652" s="3" t="n"/>
       <c r="W652" s="2" t="n"/>
-      <c r="X652" s="3" t="n"/>
+      <c r="X652" s="2" t="n"/>
       <c r="Y652" s="2" t="n"/>
     </row>
     <row r="653">
@@ -18354,7 +18354,7 @@
       <c r="U653" s="4" t="n"/>
       <c r="V653" s="3" t="n"/>
       <c r="W653" s="4" t="n"/>
-      <c r="X653" s="3" t="n"/>
+      <c r="X653" s="4" t="n"/>
       <c r="Y653" s="4" t="n"/>
     </row>
     <row r="654">
@@ -18381,7 +18381,7 @@
       <c r="U654" s="2" t="n"/>
       <c r="V654" s="3" t="n"/>
       <c r="W654" s="2" t="n"/>
-      <c r="X654" s="3" t="n"/>
+      <c r="X654" s="2" t="n"/>
       <c r="Y654" s="2" t="n"/>
     </row>
     <row r="655">
@@ -18408,7 +18408,7 @@
       <c r="U655" s="4" t="n"/>
       <c r="V655" s="3" t="n"/>
       <c r="W655" s="4" t="n"/>
-      <c r="X655" s="3" t="n"/>
+      <c r="X655" s="4" t="n"/>
       <c r="Y655" s="4" t="n"/>
     </row>
     <row r="656">
@@ -18435,7 +18435,7 @@
       <c r="U656" s="2" t="n"/>
       <c r="V656" s="3" t="n"/>
       <c r="W656" s="2" t="n"/>
-      <c r="X656" s="3" t="n"/>
+      <c r="X656" s="2" t="n"/>
       <c r="Y656" s="2" t="n"/>
     </row>
     <row r="657">
@@ -18462,7 +18462,7 @@
       <c r="U657" s="4" t="n"/>
       <c r="V657" s="3" t="n"/>
       <c r="W657" s="4" t="n"/>
-      <c r="X657" s="3" t="n"/>
+      <c r="X657" s="4" t="n"/>
       <c r="Y657" s="4" t="n"/>
     </row>
     <row r="658">
@@ -18489,7 +18489,7 @@
       <c r="U658" s="2" t="n"/>
       <c r="V658" s="3" t="n"/>
       <c r="W658" s="2" t="n"/>
-      <c r="X658" s="3" t="n"/>
+      <c r="X658" s="2" t="n"/>
       <c r="Y658" s="2" t="n"/>
     </row>
     <row r="659">
@@ -18516,7 +18516,7 @@
       <c r="U659" s="4" t="n"/>
       <c r="V659" s="3" t="n"/>
       <c r="W659" s="4" t="n"/>
-      <c r="X659" s="3" t="n"/>
+      <c r="X659" s="4" t="n"/>
       <c r="Y659" s="4" t="n"/>
     </row>
     <row r="660">
@@ -18543,7 +18543,7 @@
       <c r="U660" s="2" t="n"/>
       <c r="V660" s="3" t="n"/>
       <c r="W660" s="2" t="n"/>
-      <c r="X660" s="3" t="n"/>
+      <c r="X660" s="2" t="n"/>
       <c r="Y660" s="2" t="n"/>
     </row>
     <row r="661">
@@ -18570,7 +18570,7 @@
       <c r="U661" s="4" t="n"/>
       <c r="V661" s="3" t="n"/>
       <c r="W661" s="4" t="n"/>
-      <c r="X661" s="3" t="n"/>
+      <c r="X661" s="4" t="n"/>
       <c r="Y661" s="4" t="n"/>
     </row>
     <row r="662">
@@ -18597,7 +18597,7 @@
       <c r="U662" s="2" t="n"/>
       <c r="V662" s="3" t="n"/>
       <c r="W662" s="2" t="n"/>
-      <c r="X662" s="3" t="n"/>
+      <c r="X662" s="2" t="n"/>
       <c r="Y662" s="2" t="n"/>
     </row>
     <row r="663">
@@ -18624,7 +18624,7 @@
       <c r="U663" s="4" t="n"/>
       <c r="V663" s="3" t="n"/>
       <c r="W663" s="4" t="n"/>
-      <c r="X663" s="3" t="n"/>
+      <c r="X663" s="4" t="n"/>
       <c r="Y663" s="4" t="n"/>
     </row>
     <row r="664">
@@ -18651,7 +18651,7 @@
       <c r="U664" s="2" t="n"/>
       <c r="V664" s="3" t="n"/>
       <c r="W664" s="2" t="n"/>
-      <c r="X664" s="3" t="n"/>
+      <c r="X664" s="2" t="n"/>
       <c r="Y664" s="2" t="n"/>
     </row>
     <row r="665">
@@ -18678,7 +18678,7 @@
       <c r="U665" s="4" t="n"/>
       <c r="V665" s="3" t="n"/>
       <c r="W665" s="4" t="n"/>
-      <c r="X665" s="3" t="n"/>
+      <c r="X665" s="4" t="n"/>
       <c r="Y665" s="4" t="n"/>
     </row>
     <row r="666">
@@ -18705,7 +18705,7 @@
       <c r="U666" s="2" t="n"/>
       <c r="V666" s="3" t="n"/>
       <c r="W666" s="2" t="n"/>
-      <c r="X666" s="3" t="n"/>
+      <c r="X666" s="2" t="n"/>
       <c r="Y666" s="2" t="n"/>
     </row>
     <row r="667">
@@ -18732,7 +18732,7 @@
       <c r="U667" s="4" t="n"/>
       <c r="V667" s="3" t="n"/>
       <c r="W667" s="4" t="n"/>
-      <c r="X667" s="3" t="n"/>
+      <c r="X667" s="4" t="n"/>
       <c r="Y667" s="4" t="n"/>
     </row>
     <row r="668">
@@ -18759,7 +18759,7 @@
       <c r="U668" s="2" t="n"/>
       <c r="V668" s="3" t="n"/>
       <c r="W668" s="2" t="n"/>
-      <c r="X668" s="3" t="n"/>
+      <c r="X668" s="2" t="n"/>
       <c r="Y668" s="2" t="n"/>
     </row>
     <row r="669">
@@ -18786,7 +18786,7 @@
       <c r="U669" s="4" t="n"/>
       <c r="V669" s="3" t="n"/>
       <c r="W669" s="4" t="n"/>
-      <c r="X669" s="3" t="n"/>
+      <c r="X669" s="4" t="n"/>
       <c r="Y669" s="4" t="n"/>
     </row>
     <row r="670">
@@ -18813,7 +18813,7 @@
       <c r="U670" s="2" t="n"/>
       <c r="V670" s="3" t="n"/>
       <c r="W670" s="2" t="n"/>
-      <c r="X670" s="3" t="n"/>
+      <c r="X670" s="2" t="n"/>
       <c r="Y670" s="2" t="n"/>
     </row>
     <row r="671">
@@ -18840,7 +18840,7 @@
       <c r="U671" s="4" t="n"/>
       <c r="V671" s="3" t="n"/>
       <c r="W671" s="4" t="n"/>
-      <c r="X671" s="3" t="n"/>
+      <c r="X671" s="4" t="n"/>
       <c r="Y671" s="4" t="n"/>
     </row>
     <row r="672">
@@ -18867,7 +18867,7 @@
       <c r="U672" s="2" t="n"/>
       <c r="V672" s="3" t="n"/>
       <c r="W672" s="2" t="n"/>
-      <c r="X672" s="3" t="n"/>
+      <c r="X672" s="2" t="n"/>
       <c r="Y672" s="2" t="n"/>
     </row>
     <row r="673">
@@ -18894,7 +18894,7 @@
       <c r="U673" s="4" t="n"/>
       <c r="V673" s="3" t="n"/>
       <c r="W673" s="4" t="n"/>
-      <c r="X673" s="3" t="n"/>
+      <c r="X673" s="4" t="n"/>
       <c r="Y673" s="4" t="n"/>
     </row>
     <row r="674">
@@ -18921,7 +18921,7 @@
       <c r="U674" s="2" t="n"/>
       <c r="V674" s="3" t="n"/>
       <c r="W674" s="2" t="n"/>
-      <c r="X674" s="3" t="n"/>
+      <c r="X674" s="2" t="n"/>
       <c r="Y674" s="2" t="n"/>
     </row>
     <row r="675">
@@ -18948,7 +18948,7 @@
       <c r="U675" s="4" t="n"/>
       <c r="V675" s="3" t="n"/>
       <c r="W675" s="4" t="n"/>
-      <c r="X675" s="3" t="n"/>
+      <c r="X675" s="4" t="n"/>
       <c r="Y675" s="4" t="n"/>
     </row>
     <row r="676">
@@ -18975,7 +18975,7 @@
       <c r="U676" s="2" t="n"/>
       <c r="V676" s="3" t="n"/>
       <c r="W676" s="2" t="n"/>
-      <c r="X676" s="3" t="n"/>
+      <c r="X676" s="2" t="n"/>
       <c r="Y676" s="2" t="n"/>
     </row>
     <row r="677">
@@ -19002,7 +19002,7 @@
       <c r="U677" s="4" t="n"/>
       <c r="V677" s="3" t="n"/>
       <c r="W677" s="4" t="n"/>
-      <c r="X677" s="3" t="n"/>
+      <c r="X677" s="4" t="n"/>
       <c r="Y677" s="4" t="n"/>
     </row>
     <row r="678">
@@ -19029,7 +19029,7 @@
       <c r="U678" s="2" t="n"/>
       <c r="V678" s="3" t="n"/>
       <c r="W678" s="2" t="n"/>
-      <c r="X678" s="3" t="n"/>
+      <c r="X678" s="2" t="n"/>
       <c r="Y678" s="2" t="n"/>
     </row>
     <row r="679">
@@ -19056,7 +19056,7 @@
       <c r="U679" s="4" t="n"/>
       <c r="V679" s="3" t="n"/>
       <c r="W679" s="4" t="n"/>
-      <c r="X679" s="3" t="n"/>
+      <c r="X679" s="4" t="n"/>
       <c r="Y679" s="4" t="n"/>
     </row>
     <row r="680">
@@ -19083,7 +19083,7 @@
       <c r="U680" s="2" t="n"/>
       <c r="V680" s="3" t="n"/>
       <c r="W680" s="2" t="n"/>
-      <c r="X680" s="3" t="n"/>
+      <c r="X680" s="2" t="n"/>
       <c r="Y680" s="2" t="n"/>
     </row>
     <row r="681">
@@ -19110,7 +19110,7 @@
       <c r="U681" s="4" t="n"/>
       <c r="V681" s="3" t="n"/>
       <c r="W681" s="4" t="n"/>
-      <c r="X681" s="3" t="n"/>
+      <c r="X681" s="4" t="n"/>
       <c r="Y681" s="4" t="n"/>
     </row>
     <row r="682">
@@ -19137,7 +19137,7 @@
       <c r="U682" s="2" t="n"/>
       <c r="V682" s="3" t="n"/>
       <c r="W682" s="2" t="n"/>
-      <c r="X682" s="3" t="n"/>
+      <c r="X682" s="2" t="n"/>
       <c r="Y682" s="2" t="n"/>
     </row>
     <row r="683">
@@ -19164,7 +19164,7 @@
       <c r="U683" s="4" t="n"/>
       <c r="V683" s="3" t="n"/>
       <c r="W683" s="4" t="n"/>
-      <c r="X683" s="3" t="n"/>
+      <c r="X683" s="4" t="n"/>
       <c r="Y683" s="4" t="n"/>
     </row>
     <row r="684">
@@ -19191,7 +19191,7 @@
       <c r="U684" s="2" t="n"/>
       <c r="V684" s="3" t="n"/>
       <c r="W684" s="2" t="n"/>
-      <c r="X684" s="3" t="n"/>
+      <c r="X684" s="2" t="n"/>
       <c r="Y684" s="2" t="n"/>
     </row>
     <row r="685">
@@ -19218,7 +19218,7 @@
       <c r="U685" s="4" t="n"/>
       <c r="V685" s="3" t="n"/>
       <c r="W685" s="4" t="n"/>
-      <c r="X685" s="3" t="n"/>
+      <c r="X685" s="4" t="n"/>
       <c r="Y685" s="4" t="n"/>
     </row>
     <row r="686">
@@ -19245,7 +19245,7 @@
       <c r="U686" s="2" t="n"/>
       <c r="V686" s="3" t="n"/>
       <c r="W686" s="2" t="n"/>
-      <c r="X686" s="3" t="n"/>
+      <c r="X686" s="2" t="n"/>
       <c r="Y686" s="2" t="n"/>
     </row>
     <row r="687">
@@ -19272,7 +19272,7 @@
       <c r="U687" s="4" t="n"/>
       <c r="V687" s="3" t="n"/>
       <c r="W687" s="4" t="n"/>
-      <c r="X687" s="3" t="n"/>
+      <c r="X687" s="4" t="n"/>
       <c r="Y687" s="4" t="n"/>
     </row>
     <row r="688">
@@ -19299,7 +19299,7 @@
       <c r="U688" s="2" t="n"/>
       <c r="V688" s="3" t="n"/>
       <c r="W688" s="2" t="n"/>
-      <c r="X688" s="3" t="n"/>
+      <c r="X688" s="2" t="n"/>
       <c r="Y688" s="2" t="n"/>
     </row>
     <row r="689">
@@ -19326,7 +19326,7 @@
       <c r="U689" s="4" t="n"/>
       <c r="V689" s="3" t="n"/>
       <c r="W689" s="4" t="n"/>
-      <c r="X689" s="3" t="n"/>
+      <c r="X689" s="4" t="n"/>
       <c r="Y689" s="4" t="n"/>
     </row>
     <row r="690">
@@ -19353,7 +19353,7 @@
       <c r="U690" s="2" t="n"/>
       <c r="V690" s="3" t="n"/>
       <c r="W690" s="2" t="n"/>
-      <c r="X690" s="3" t="n"/>
+      <c r="X690" s="2" t="n"/>
       <c r="Y690" s="2" t="n"/>
     </row>
     <row r="691">
@@ -19380,7 +19380,7 @@
       <c r="U691" s="4" t="n"/>
       <c r="V691" s="3" t="n"/>
       <c r="W691" s="4" t="n"/>
-      <c r="X691" s="3" t="n"/>
+      <c r="X691" s="4" t="n"/>
       <c r="Y691" s="4" t="n"/>
     </row>
     <row r="692">
@@ -19407,7 +19407,7 @@
       <c r="U692" s="2" t="n"/>
       <c r="V692" s="3" t="n"/>
       <c r="W692" s="2" t="n"/>
-      <c r="X692" s="3" t="n"/>
+      <c r="X692" s="2" t="n"/>
       <c r="Y692" s="2" t="n"/>
     </row>
     <row r="693">
@@ -19434,7 +19434,7 @@
       <c r="U693" s="4" t="n"/>
       <c r="V693" s="3" t="n"/>
       <c r="W693" s="4" t="n"/>
-      <c r="X693" s="3" t="n"/>
+      <c r="X693" s="4" t="n"/>
       <c r="Y693" s="4" t="n"/>
     </row>
     <row r="694">
@@ -19461,7 +19461,7 @@
       <c r="U694" s="2" t="n"/>
       <c r="V694" s="3" t="n"/>
       <c r="W694" s="2" t="n"/>
-      <c r="X694" s="3" t="n"/>
+      <c r="X694" s="2" t="n"/>
       <c r="Y694" s="2" t="n"/>
     </row>
     <row r="695">
@@ -19488,7 +19488,7 @@
       <c r="U695" s="4" t="n"/>
       <c r="V695" s="3" t="n"/>
       <c r="W695" s="4" t="n"/>
-      <c r="X695" s="3" t="n"/>
+      <c r="X695" s="4" t="n"/>
       <c r="Y695" s="4" t="n"/>
     </row>
     <row r="696">
@@ -19515,7 +19515,7 @@
       <c r="U696" s="2" t="n"/>
       <c r="V696" s="3" t="n"/>
       <c r="W696" s="2" t="n"/>
-      <c r="X696" s="3" t="n"/>
+      <c r="X696" s="2" t="n"/>
       <c r="Y696" s="2" t="n"/>
     </row>
     <row r="697">
@@ -19542,7 +19542,7 @@
       <c r="U697" s="4" t="n"/>
       <c r="V697" s="3" t="n"/>
       <c r="W697" s="4" t="n"/>
-      <c r="X697" s="3" t="n"/>
+      <c r="X697" s="4" t="n"/>
       <c r="Y697" s="4" t="n"/>
     </row>
     <row r="698">
@@ -19569,7 +19569,7 @@
       <c r="U698" s="2" t="n"/>
       <c r="V698" s="3" t="n"/>
       <c r="W698" s="2" t="n"/>
-      <c r="X698" s="3" t="n"/>
+      <c r="X698" s="2" t="n"/>
       <c r="Y698" s="2" t="n"/>
     </row>
     <row r="699">
@@ -19596,7 +19596,7 @@
       <c r="U699" s="4" t="n"/>
       <c r="V699" s="3" t="n"/>
       <c r="W699" s="4" t="n"/>
-      <c r="X699" s="3" t="n"/>
+      <c r="X699" s="4" t="n"/>
       <c r="Y699" s="4" t="n"/>
     </row>
     <row r="700">
@@ -19623,7 +19623,7 @@
       <c r="U700" s="2" t="n"/>
       <c r="V700" s="3" t="n"/>
       <c r="W700" s="2" t="n"/>
-      <c r="X700" s="3" t="n"/>
+      <c r="X700" s="2" t="n"/>
       <c r="Y700" s="2" t="n"/>
     </row>
     <row r="701">
@@ -19650,7 +19650,7 @@
       <c r="U701" s="4" t="n"/>
       <c r="V701" s="3" t="n"/>
       <c r="W701" s="4" t="n"/>
-      <c r="X701" s="3" t="n"/>
+      <c r="X701" s="4" t="n"/>
       <c r="Y701" s="4" t="n"/>
     </row>
     <row r="702">
@@ -19677,7 +19677,7 @@
       <c r="U702" s="2" t="n"/>
       <c r="V702" s="3" t="n"/>
       <c r="W702" s="2" t="n"/>
-      <c r="X702" s="3" t="n"/>
+      <c r="X702" s="2" t="n"/>
       <c r="Y702" s="2" t="n"/>
     </row>
     <row r="703">
@@ -19704,7 +19704,7 @@
       <c r="U703" s="4" t="n"/>
       <c r="V703" s="3" t="n"/>
       <c r="W703" s="4" t="n"/>
-      <c r="X703" s="3" t="n"/>
+      <c r="X703" s="4" t="n"/>
       <c r="Y703" s="4" t="n"/>
     </row>
     <row r="704">
@@ -19731,7 +19731,7 @@
       <c r="U704" s="2" t="n"/>
       <c r="V704" s="3" t="n"/>
       <c r="W704" s="2" t="n"/>
-      <c r="X704" s="3" t="n"/>
+      <c r="X704" s="2" t="n"/>
       <c r="Y704" s="2" t="n"/>
     </row>
     <row r="705">
@@ -19758,7 +19758,7 @@
       <c r="U705" s="4" t="n"/>
       <c r="V705" s="3" t="n"/>
       <c r="W705" s="4" t="n"/>
-      <c r="X705" s="3" t="n"/>
+      <c r="X705" s="4" t="n"/>
       <c r="Y705" s="4" t="n"/>
     </row>
     <row r="706">
@@ -19785,7 +19785,7 @@
       <c r="U706" s="2" t="n"/>
       <c r="V706" s="3" t="n"/>
       <c r="W706" s="2" t="n"/>
-      <c r="X706" s="3" t="n"/>
+      <c r="X706" s="2" t="n"/>
       <c r="Y706" s="2" t="n"/>
     </row>
     <row r="707">
@@ -19812,7 +19812,7 @@
       <c r="U707" s="4" t="n"/>
       <c r="V707" s="3" t="n"/>
       <c r="W707" s="4" t="n"/>
-      <c r="X707" s="3" t="n"/>
+      <c r="X707" s="4" t="n"/>
       <c r="Y707" s="4" t="n"/>
     </row>
     <row r="708">
@@ -19839,7 +19839,7 @@
       <c r="U708" s="2" t="n"/>
       <c r="V708" s="3" t="n"/>
       <c r="W708" s="2" t="n"/>
-      <c r="X708" s="3" t="n"/>
+      <c r="X708" s="2" t="n"/>
       <c r="Y708" s="2" t="n"/>
     </row>
     <row r="709">
@@ -19866,7 +19866,7 @@
       <c r="U709" s="4" t="n"/>
       <c r="V709" s="3" t="n"/>
       <c r="W709" s="4" t="n"/>
-      <c r="X709" s="3" t="n"/>
+      <c r="X709" s="4" t="n"/>
       <c r="Y709" s="4" t="n"/>
     </row>
     <row r="710">
@@ -19893,7 +19893,7 @@
       <c r="U710" s="2" t="n"/>
       <c r="V710" s="3" t="n"/>
       <c r="W710" s="2" t="n"/>
-      <c r="X710" s="3" t="n"/>
+      <c r="X710" s="2" t="n"/>
       <c r="Y710" s="2" t="n"/>
     </row>
     <row r="711">
@@ -19920,7 +19920,7 @@
       <c r="U711" s="4" t="n"/>
       <c r="V711" s="3" t="n"/>
       <c r="W711" s="4" t="n"/>
-      <c r="X711" s="3" t="n"/>
+      <c r="X711" s="4" t="n"/>
       <c r="Y711" s="4" t="n"/>
     </row>
     <row r="712">
@@ -19947,7 +19947,7 @@
       <c r="U712" s="2" t="n"/>
       <c r="V712" s="3" t="n"/>
       <c r="W712" s="2" t="n"/>
-      <c r="X712" s="3" t="n"/>
+      <c r="X712" s="2" t="n"/>
       <c r="Y712" s="2" t="n"/>
     </row>
     <row r="713">
@@ -19974,7 +19974,7 @@
       <c r="U713" s="4" t="n"/>
       <c r="V713" s="3" t="n"/>
       <c r="W713" s="4" t="n"/>
-      <c r="X713" s="3" t="n"/>
+      <c r="X713" s="4" t="n"/>
       <c r="Y713" s="4" t="n"/>
     </row>
     <row r="714">
@@ -20001,7 +20001,7 @@
       <c r="U714" s="2" t="n"/>
       <c r="V714" s="3" t="n"/>
       <c r="W714" s="2" t="n"/>
-      <c r="X714" s="3" t="n"/>
+      <c r="X714" s="2" t="n"/>
       <c r="Y714" s="2" t="n"/>
     </row>
     <row r="715">
@@ -20028,7 +20028,7 @@
       <c r="U715" s="4" t="n"/>
       <c r="V715" s="3" t="n"/>
       <c r="W715" s="4" t="n"/>
-      <c r="X715" s="3" t="n"/>
+      <c r="X715" s="4" t="n"/>
       <c r="Y715" s="4" t="n"/>
     </row>
     <row r="716">
@@ -20055,7 +20055,7 @@
       <c r="U716" s="2" t="n"/>
       <c r="V716" s="3" t="n"/>
       <c r="W716" s="2" t="n"/>
-      <c r="X716" s="3" t="n"/>
+      <c r="X716" s="2" t="n"/>
       <c r="Y716" s="2" t="n"/>
     </row>
     <row r="717">
@@ -20082,7 +20082,7 @@
       <c r="U717" s="4" t="n"/>
       <c r="V717" s="3" t="n"/>
       <c r="W717" s="4" t="n"/>
-      <c r="X717" s="3" t="n"/>
+      <c r="X717" s="4" t="n"/>
       <c r="Y717" s="4" t="n"/>
     </row>
     <row r="718">
@@ -20109,7 +20109,7 @@
       <c r="U718" s="2" t="n"/>
       <c r="V718" s="3" t="n"/>
       <c r="W718" s="2" t="n"/>
-      <c r="X718" s="3" t="n"/>
+      <c r="X718" s="2" t="n"/>
       <c r="Y718" s="2" t="n"/>
     </row>
     <row r="719">
@@ -20136,7 +20136,7 @@
       <c r="U719" s="4" t="n"/>
       <c r="V719" s="3" t="n"/>
       <c r="W719" s="4" t="n"/>
-      <c r="X719" s="3" t="n"/>
+      <c r="X719" s="4" t="n"/>
       <c r="Y719" s="4" t="n"/>
     </row>
     <row r="720">
@@ -20163,7 +20163,7 @@
       <c r="U720" s="2" t="n"/>
       <c r="V720" s="3" t="n"/>
       <c r="W720" s="2" t="n"/>
-      <c r="X720" s="3" t="n"/>
+      <c r="X720" s="2" t="n"/>
       <c r="Y720" s="2" t="n"/>
     </row>
     <row r="721">
@@ -20190,7 +20190,7 @@
       <c r="U721" s="4" t="n"/>
       <c r="V721" s="3" t="n"/>
       <c r="W721" s="4" t="n"/>
-      <c r="X721" s="3" t="n"/>
+      <c r="X721" s="4" t="n"/>
       <c r="Y721" s="4" t="n"/>
     </row>
     <row r="722">
@@ -20217,7 +20217,7 @@
       <c r="U722" s="2" t="n"/>
       <c r="V722" s="3" t="n"/>
       <c r="W722" s="2" t="n"/>
-      <c r="X722" s="3" t="n"/>
+      <c r="X722" s="2" t="n"/>
       <c r="Y722" s="2" t="n"/>
     </row>
     <row r="723">
@@ -20244,7 +20244,7 @@
       <c r="U723" s="4" t="n"/>
       <c r="V723" s="3" t="n"/>
       <c r="W723" s="4" t="n"/>
-      <c r="X723" s="3" t="n"/>
+      <c r="X723" s="4" t="n"/>
       <c r="Y723" s="4" t="n"/>
     </row>
     <row r="724">
@@ -20271,7 +20271,7 @@
       <c r="U724" s="2" t="n"/>
       <c r="V724" s="3" t="n"/>
       <c r="W724" s="2" t="n"/>
-      <c r="X724" s="3" t="n"/>
+      <c r="X724" s="2" t="n"/>
       <c r="Y724" s="2" t="n"/>
     </row>
     <row r="725">
@@ -20298,7 +20298,7 @@
       <c r="U725" s="4" t="n"/>
       <c r="V725" s="3" t="n"/>
       <c r="W725" s="4" t="n"/>
-      <c r="X725" s="3" t="n"/>
+      <c r="X725" s="4" t="n"/>
       <c r="Y725" s="4" t="n"/>
     </row>
     <row r="726">
@@ -20325,7 +20325,7 @@
       <c r="U726" s="2" t="n"/>
       <c r="V726" s="3" t="n"/>
       <c r="W726" s="2" t="n"/>
-      <c r="X726" s="3" t="n"/>
+      <c r="X726" s="2" t="n"/>
       <c r="Y726" s="2" t="n"/>
     </row>
     <row r="727">
@@ -20352,7 +20352,7 @@
       <c r="U727" s="4" t="n"/>
       <c r="V727" s="3" t="n"/>
       <c r="W727" s="4" t="n"/>
-      <c r="X727" s="3" t="n"/>
+      <c r="X727" s="4" t="n"/>
       <c r="Y727" s="4" t="n"/>
     </row>
     <row r="728">
@@ -20379,7 +20379,7 @@
       <c r="U728" s="2" t="n"/>
       <c r="V728" s="3" t="n"/>
       <c r="W728" s="2" t="n"/>
-      <c r="X728" s="3" t="n"/>
+      <c r="X728" s="2" t="n"/>
       <c r="Y728" s="2" t="n"/>
     </row>
     <row r="729">
@@ -20406,7 +20406,7 @@
       <c r="U729" s="4" t="n"/>
       <c r="V729" s="3" t="n"/>
       <c r="W729" s="4" t="n"/>
-      <c r="X729" s="3" t="n"/>
+      <c r="X729" s="4" t="n"/>
       <c r="Y729" s="4" t="n"/>
     </row>
     <row r="730">
@@ -20433,7 +20433,7 @@
       <c r="U730" s="2" t="n"/>
       <c r="V730" s="3" t="n"/>
       <c r="W730" s="2" t="n"/>
-      <c r="X730" s="3" t="n"/>
+      <c r="X730" s="2" t="n"/>
       <c r="Y730" s="2" t="n"/>
     </row>
     <row r="731">
@@ -20460,7 +20460,7 @@
       <c r="U731" s="4" t="n"/>
       <c r="V731" s="3" t="n"/>
       <c r="W731" s="4" t="n"/>
-      <c r="X731" s="3" t="n"/>
+      <c r="X731" s="4" t="n"/>
       <c r="Y731" s="4" t="n"/>
     </row>
     <row r="732">
@@ -20487,7 +20487,7 @@
       <c r="U732" s="2" t="n"/>
       <c r="V732" s="3" t="n"/>
       <c r="W732" s="2" t="n"/>
-      <c r="X732" s="3" t="n"/>
+      <c r="X732" s="2" t="n"/>
       <c r="Y732" s="2" t="n"/>
     </row>
     <row r="733">
@@ -20514,7 +20514,7 @@
       <c r="U733" s="4" t="n"/>
       <c r="V733" s="3" t="n"/>
       <c r="W733" s="4" t="n"/>
-      <c r="X733" s="3" t="n"/>
+      <c r="X733" s="4" t="n"/>
       <c r="Y733" s="4" t="n"/>
     </row>
     <row r="734">
@@ -20541,7 +20541,7 @@
       <c r="U734" s="2" t="n"/>
       <c r="V734" s="3" t="n"/>
       <c r="W734" s="2" t="n"/>
-      <c r="X734" s="3" t="n"/>
+      <c r="X734" s="2" t="n"/>
       <c r="Y734" s="2" t="n"/>
     </row>
     <row r="735">
@@ -20568,7 +20568,7 @@
       <c r="U735" s="4" t="n"/>
       <c r="V735" s="3" t="n"/>
       <c r="W735" s="4" t="n"/>
-      <c r="X735" s="3" t="n"/>
+      <c r="X735" s="4" t="n"/>
       <c r="Y735" s="4" t="n"/>
     </row>
     <row r="736">
@@ -20595,7 +20595,7 @@
       <c r="U736" s="2" t="n"/>
       <c r="V736" s="3" t="n"/>
       <c r="W736" s="2" t="n"/>
-      <c r="X736" s="3" t="n"/>
+      <c r="X736" s="2" t="n"/>
       <c r="Y736" s="2" t="n"/>
     </row>
     <row r="737">
@@ -20622,7 +20622,7 @@
       <c r="U737" s="4" t="n"/>
       <c r="V737" s="3" t="n"/>
       <c r="W737" s="4" t="n"/>
-      <c r="X737" s="3" t="n"/>
+      <c r="X737" s="4" t="n"/>
       <c r="Y737" s="4" t="n"/>
     </row>
     <row r="738">
@@ -20649,7 +20649,7 @@
       <c r="U738" s="2" t="n"/>
       <c r="V738" s="3" t="n"/>
       <c r="W738" s="2" t="n"/>
-      <c r="X738" s="3" t="n"/>
+      <c r="X738" s="2" t="n"/>
       <c r="Y738" s="2" t="n"/>
     </row>
     <row r="739">
@@ -20676,7 +20676,7 @@
       <c r="U739" s="4" t="n"/>
       <c r="V739" s="3" t="n"/>
       <c r="W739" s="4" t="n"/>
-      <c r="X739" s="3" t="n"/>
+      <c r="X739" s="4" t="n"/>
       <c r="Y739" s="4" t="n"/>
     </row>
     <row r="740">
@@ -20703,7 +20703,7 @@
       <c r="U740" s="2" t="n"/>
       <c r="V740" s="3" t="n"/>
       <c r="W740" s="2" t="n"/>
-      <c r="X740" s="3" t="n"/>
+      <c r="X740" s="2" t="n"/>
       <c r="Y740" s="2" t="n"/>
     </row>
     <row r="741">
@@ -20730,7 +20730,7 @@
       <c r="U741" s="4" t="n"/>
       <c r="V741" s="3" t="n"/>
       <c r="W741" s="4" t="n"/>
-      <c r="X741" s="3" t="n"/>
+      <c r="X741" s="4" t="n"/>
       <c r="Y741" s="4" t="n"/>
     </row>
     <row r="742">
@@ -20757,7 +20757,7 @@
       <c r="U742" s="2" t="n"/>
       <c r="V742" s="3" t="n"/>
       <c r="W742" s="2" t="n"/>
-      <c r="X742" s="3" t="n"/>
+      <c r="X742" s="2" t="n"/>
       <c r="Y742" s="2" t="n"/>
     </row>
     <row r="743">
@@ -20784,7 +20784,7 @@
       <c r="U743" s="4" t="n"/>
       <c r="V743" s="3" t="n"/>
       <c r="W743" s="4" t="n"/>
-      <c r="X743" s="3" t="n"/>
+      <c r="X743" s="4" t="n"/>
       <c r="Y743" s="4" t="n"/>
     </row>
     <row r="744">
@@ -20811,7 +20811,7 @@
       <c r="U744" s="2" t="n"/>
       <c r="V744" s="3" t="n"/>
       <c r="W744" s="2" t="n"/>
-      <c r="X744" s="3" t="n"/>
+      <c r="X744" s="2" t="n"/>
       <c r="Y744" s="2" t="n"/>
     </row>
     <row r="745">
@@ -20838,7 +20838,7 @@
       <c r="U745" s="4" t="n"/>
       <c r="V745" s="3" t="n"/>
       <c r="W745" s="4" t="n"/>
-      <c r="X745" s="3" t="n"/>
+      <c r="X745" s="4" t="n"/>
       <c r="Y745" s="4" t="n"/>
     </row>
     <row r="746">
@@ -20865,7 +20865,7 @@
       <c r="U746" s="2" t="n"/>
       <c r="V746" s="3" t="n"/>
       <c r="W746" s="2" t="n"/>
-      <c r="X746" s="3" t="n"/>
+      <c r="X746" s="2" t="n"/>
       <c r="Y746" s="2" t="n"/>
     </row>
     <row r="747">
@@ -20892,7 +20892,7 @@
       <c r="U747" s="4" t="n"/>
       <c r="V747" s="3" t="n"/>
       <c r="W747" s="4" t="n"/>
-      <c r="X747" s="3" t="n"/>
+      <c r="X747" s="4" t="n"/>
       <c r="Y747" s="4" t="n"/>
     </row>
     <row r="748">
@@ -20919,7 +20919,7 @@
       <c r="U748" s="2" t="n"/>
       <c r="V748" s="3" t="n"/>
       <c r="W748" s="2" t="n"/>
-      <c r="X748" s="3" t="n"/>
+      <c r="X748" s="2" t="n"/>
       <c r="Y748" s="2" t="n"/>
     </row>
     <row r="749">
@@ -20946,7 +20946,7 @@
       <c r="U749" s="4" t="n"/>
       <c r="V749" s="3" t="n"/>
       <c r="W749" s="4" t="n"/>
-      <c r="X749" s="3" t="n"/>
+      <c r="X749" s="4" t="n"/>
       <c r="Y749" s="4" t="n"/>
     </row>
     <row r="750">
@@ -20973,7 +20973,7 @@
       <c r="U750" s="2" t="n"/>
       <c r="V750" s="3" t="n"/>
       <c r="W750" s="2" t="n"/>
-      <c r="X750" s="3" t="n"/>
+      <c r="X750" s="2" t="n"/>
       <c r="Y750" s="2" t="n"/>
     </row>
     <row r="751">
@@ -21000,7 +21000,7 @@
       <c r="U751" s="4" t="n"/>
       <c r="V751" s="3" t="n"/>
       <c r="W751" s="4" t="n"/>
-      <c r="X751" s="3" t="n"/>
+      <c r="X751" s="4" t="n"/>
       <c r="Y751" s="4" t="n"/>
     </row>
     <row r="752">
@@ -21027,7 +21027,7 @@
       <c r="U752" s="2" t="n"/>
       <c r="V752" s="3" t="n"/>
       <c r="W752" s="2" t="n"/>
-      <c r="X752" s="3" t="n"/>
+      <c r="X752" s="2" t="n"/>
       <c r="Y752" s="2" t="n"/>
     </row>
     <row r="753">
@@ -21054,7 +21054,7 @@
       <c r="U753" s="4" t="n"/>
       <c r="V753" s="3" t="n"/>
       <c r="W753" s="4" t="n"/>
-      <c r="X753" s="3" t="n"/>
+      <c r="X753" s="4" t="n"/>
       <c r="Y753" s="4" t="n"/>
     </row>
     <row r="754">
@@ -21081,7 +21081,7 @@
       <c r="U754" s="2" t="n"/>
       <c r="V754" s="3" t="n"/>
       <c r="W754" s="2" t="n"/>
-      <c r="X754" s="3" t="n"/>
+      <c r="X754" s="2" t="n"/>
       <c r="Y754" s="2" t="n"/>
     </row>
     <row r="755">
@@ -21108,7 +21108,7 @@
       <c r="U755" s="4" t="n"/>
       <c r="V755" s="3" t="n"/>
       <c r="W755" s="4" t="n"/>
-      <c r="X755" s="3" t="n"/>
+      <c r="X755" s="4" t="n"/>
       <c r="Y755" s="4" t="n"/>
     </row>
     <row r="756">
@@ -21135,7 +21135,7 @@
       <c r="U756" s="2" t="n"/>
       <c r="V756" s="3" t="n"/>
       <c r="W756" s="2" t="n"/>
-      <c r="X756" s="3" t="n"/>
+      <c r="X756" s="2" t="n"/>
       <c r="Y756" s="2" t="n"/>
     </row>
     <row r="757">
@@ -21162,7 +21162,7 @@
       <c r="U757" s="4" t="n"/>
       <c r="V757" s="3" t="n"/>
       <c r="W757" s="4" t="n"/>
-      <c r="X757" s="3" t="n"/>
+      <c r="X757" s="4" t="n"/>
       <c r="Y757" s="4" t="n"/>
     </row>
     <row r="758">
@@ -21189,7 +21189,7 @@
       <c r="U758" s="2" t="n"/>
       <c r="V758" s="3" t="n"/>
       <c r="W758" s="2" t="n"/>
-      <c r="X758" s="3" t="n"/>
+      <c r="X758" s="2" t="n"/>
       <c r="Y758" s="2" t="n"/>
     </row>
     <row r="759">
@@ -21216,7 +21216,7 @@
       <c r="U759" s="4" t="n"/>
       <c r="V759" s="3" t="n"/>
       <c r="W759" s="4" t="n"/>
-      <c r="X759" s="3" t="n"/>
+      <c r="X759" s="4" t="n"/>
       <c r="Y759" s="4" t="n"/>
     </row>
     <row r="760">
@@ -21243,7 +21243,7 @@
       <c r="U760" s="2" t="n"/>
       <c r="V760" s="3" t="n"/>
       <c r="W760" s="2" t="n"/>
-      <c r="X760" s="3" t="n"/>
+      <c r="X760" s="2" t="n"/>
       <c r="Y760" s="2" t="n"/>
     </row>
     <row r="761">
@@ -21270,7 +21270,7 @@
       <c r="U761" s="4" t="n"/>
       <c r="V761" s="3" t="n"/>
       <c r="W761" s="4" t="n"/>
-      <c r="X761" s="3" t="n"/>
+      <c r="X761" s="4" t="n"/>
       <c r="Y761" s="4" t="n"/>
     </row>
     <row r="762">
@@ -21297,7 +21297,7 @@
       <c r="U762" s="2" t="n"/>
       <c r="V762" s="3" t="n"/>
       <c r="W762" s="2" t="n"/>
-      <c r="X762" s="3" t="n"/>
+      <c r="X762" s="2" t="n"/>
       <c r="Y762" s="2" t="n"/>
     </row>
     <row r="763">
@@ -21324,7 +21324,7 @@
       <c r="U763" s="4" t="n"/>
       <c r="V763" s="3" t="n"/>
       <c r="W763" s="4" t="n"/>
-      <c r="X763" s="3" t="n"/>
+      <c r="X763" s="4" t="n"/>
       <c r="Y763" s="4" t="n"/>
     </row>
     <row r="764">
@@ -21351,7 +21351,7 @@
       <c r="U764" s="2" t="n"/>
       <c r="V764" s="3" t="n"/>
       <c r="W764" s="2" t="n"/>
-      <c r="X764" s="3" t="n"/>
+      <c r="X764" s="2" t="n"/>
       <c r="Y764" s="2" t="n"/>
     </row>
     <row r="765">
@@ -21378,7 +21378,7 @@
       <c r="U765" s="4" t="n"/>
       <c r="V765" s="3" t="n"/>
       <c r="W765" s="4" t="n"/>
-      <c r="X765" s="3" t="n"/>
+      <c r="X765" s="4" t="n"/>
       <c r="Y765" s="4" t="n"/>
     </row>
     <row r="766">
@@ -21405,7 +21405,7 @@
       <c r="U766" s="2" t="n"/>
       <c r="V766" s="3" t="n"/>
       <c r="W766" s="2" t="n"/>
-      <c r="X766" s="3" t="n"/>
+      <c r="X766" s="2" t="n"/>
       <c r="Y766" s="2" t="n"/>
     </row>
     <row r="767">
@@ -21432,7 +21432,7 @@
       <c r="U767" s="4" t="n"/>
       <c r="V767" s="3" t="n"/>
       <c r="W767" s="4" t="n"/>
-      <c r="X767" s="3" t="n"/>
+      <c r="X767" s="4" t="n"/>
       <c r="Y767" s="4" t="n"/>
     </row>
     <row r="768">
@@ -21459,7 +21459,7 @@
       <c r="U768" s="2" t="n"/>
       <c r="V768" s="3" t="n"/>
       <c r="W768" s="2" t="n"/>
-      <c r="X768" s="3" t="n"/>
+      <c r="X768" s="2" t="n"/>
       <c r="Y768" s="2" t="n"/>
     </row>
     <row r="769">
@@ -21486,7 +21486,7 @@
       <c r="U769" s="4" t="n"/>
       <c r="V769" s="3" t="n"/>
       <c r="W769" s="4" t="n"/>
-      <c r="X769" s="3" t="n"/>
+      <c r="X769" s="4" t="n"/>
       <c r="Y769" s="4" t="n"/>
     </row>
     <row r="770">
@@ -21513,7 +21513,7 @@
       <c r="U770" s="2" t="n"/>
       <c r="V770" s="3" t="n"/>
       <c r="W770" s="2" t="n"/>
-      <c r="X770" s="3" t="n"/>
+      <c r="X770" s="2" t="n"/>
       <c r="Y770" s="2" t="n"/>
     </row>
     <row r="771">
@@ -21540,7 +21540,7 @@
       <c r="U771" s="4" t="n"/>
       <c r="V771" s="3" t="n"/>
       <c r="W771" s="4" t="n"/>
-      <c r="X771" s="3" t="n"/>
+      <c r="X771" s="4" t="n"/>
       <c r="Y771" s="4" t="n"/>
     </row>
     <row r="772">
@@ -21567,7 +21567,7 @@
       <c r="U772" s="2" t="n"/>
       <c r="V772" s="3" t="n"/>
       <c r="W772" s="2" t="n"/>
-      <c r="X772" s="3" t="n"/>
+      <c r="X772" s="2" t="n"/>
       <c r="Y772" s="2" t="n"/>
     </row>
     <row r="773">
@@ -21594,7 +21594,7 @@
       <c r="U773" s="4" t="n"/>
       <c r="V773" s="3" t="n"/>
       <c r="W773" s="4" t="n"/>
-      <c r="X773" s="3" t="n"/>
+      <c r="X773" s="4" t="n"/>
       <c r="Y773" s="4" t="n"/>
     </row>
     <row r="774">
@@ -21621,7 +21621,7 @@
       <c r="U774" s="2" t="n"/>
       <c r="V774" s="3" t="n"/>
       <c r="W774" s="2" t="n"/>
-      <c r="X774" s="3" t="n"/>
+      <c r="X774" s="2" t="n"/>
       <c r="Y774" s="2" t="n"/>
     </row>
     <row r="775">
@@ -21648,7 +21648,7 @@
       <c r="U775" s="4" t="n"/>
       <c r="V775" s="3" t="n"/>
       <c r="W775" s="4" t="n"/>
-      <c r="X775" s="3" t="n"/>
+      <c r="X775" s="4" t="n"/>
       <c r="Y775" s="4" t="n"/>
     </row>
     <row r="776">
@@ -21675,7 +21675,7 @@
       <c r="U776" s="2" t="n"/>
       <c r="V776" s="3" t="n"/>
       <c r="W776" s="2" t="n"/>
-      <c r="X776" s="3" t="n"/>
+      <c r="X776" s="2" t="n"/>
       <c r="Y776" s="2" t="n"/>
     </row>
     <row r="777">
@@ -21702,7 +21702,7 @@
       <c r="U777" s="4" t="n"/>
       <c r="V777" s="3" t="n"/>
       <c r="W777" s="4" t="n"/>
-      <c r="X777" s="3" t="n"/>
+      <c r="X777" s="4" t="n"/>
       <c r="Y777" s="4" t="n"/>
     </row>
     <row r="778">
@@ -21729,7 +21729,7 @@
       <c r="U778" s="2" t="n"/>
       <c r="V778" s="3" t="n"/>
       <c r="W778" s="2" t="n"/>
-      <c r="X778" s="3" t="n"/>
+      <c r="X778" s="2" t="n"/>
       <c r="Y778" s="2" t="n"/>
     </row>
     <row r="779">
@@ -21756,7 +21756,7 @@
       <c r="U779" s="4" t="n"/>
       <c r="V779" s="3" t="n"/>
       <c r="W779" s="4" t="n"/>
-      <c r="X779" s="3" t="n"/>
+      <c r="X779" s="4" t="n"/>
       <c r="Y779" s="4" t="n"/>
     </row>
     <row r="780">
@@ -21783,7 +21783,7 @@
       <c r="U780" s="2" t="n"/>
       <c r="V780" s="3" t="n"/>
       <c r="W780" s="2" t="n"/>
-      <c r="X780" s="3" t="n"/>
+      <c r="X780" s="2" t="n"/>
       <c r="Y780" s="2" t="n"/>
     </row>
     <row r="781">
@@ -21810,7 +21810,7 @@
       <c r="U781" s="4" t="n"/>
       <c r="V781" s="3" t="n"/>
       <c r="W781" s="4" t="n"/>
-      <c r="X781" s="3" t="n"/>
+      <c r="X781" s="4" t="n"/>
       <c r="Y781" s="4" t="n"/>
     </row>
     <row r="782">
@@ -21837,7 +21837,7 @@
       <c r="U782" s="2" t="n"/>
       <c r="V782" s="3" t="n"/>
       <c r="W782" s="2" t="n"/>
-      <c r="X782" s="3" t="n"/>
+      <c r="X782" s="2" t="n"/>
       <c r="Y782" s="2" t="n"/>
     </row>
     <row r="783">
@@ -21864,7 +21864,7 @@
       <c r="U783" s="4" t="n"/>
       <c r="V783" s="3" t="n"/>
       <c r="W783" s="4" t="n"/>
-      <c r="X783" s="3" t="n"/>
+      <c r="X783" s="4" t="n"/>
       <c r="Y783" s="4" t="n"/>
     </row>
     <row r="784">
@@ -21891,7 +21891,7 @@
       <c r="U784" s="2" t="n"/>
       <c r="V784" s="3" t="n"/>
       <c r="W784" s="2" t="n"/>
-      <c r="X784" s="3" t="n"/>
+      <c r="X784" s="2" t="n"/>
       <c r="Y784" s="2" t="n"/>
     </row>
     <row r="785">
@@ -21918,7 +21918,7 @@
       <c r="U785" s="4" t="n"/>
       <c r="V785" s="3" t="n"/>
       <c r="W785" s="4" t="n"/>
-      <c r="X785" s="3" t="n"/>
+      <c r="X785" s="4" t="n"/>
       <c r="Y785" s="4" t="n"/>
     </row>
     <row r="786">
@@ -21945,7 +21945,7 @@
       <c r="U786" s="2" t="n"/>
       <c r="V786" s="3" t="n"/>
       <c r="W786" s="2" t="n"/>
-      <c r="X786" s="3" t="n"/>
+      <c r="X786" s="2" t="n"/>
       <c r="Y786" s="2" t="n"/>
     </row>
     <row r="787">
@@ -21972,7 +21972,7 @@
       <c r="U787" s="4" t="n"/>
       <c r="V787" s="3" t="n"/>
       <c r="W787" s="4" t="n"/>
-      <c r="X787" s="3" t="n"/>
+      <c r="X787" s="4" t="n"/>
       <c r="Y787" s="4" t="n"/>
     </row>
     <row r="788">
@@ -21999,7 +21999,7 @@
       <c r="U788" s="2" t="n"/>
       <c r="V788" s="3" t="n"/>
       <c r="W788" s="2" t="n"/>
-      <c r="X788" s="3" t="n"/>
+      <c r="X788" s="2" t="n"/>
       <c r="Y788" s="2" t="n"/>
     </row>
     <row r="789">
@@ -22026,7 +22026,7 @@
       <c r="U789" s="4" t="n"/>
       <c r="V789" s="3" t="n"/>
       <c r="W789" s="4" t="n"/>
-      <c r="X789" s="3" t="n"/>
+      <c r="X789" s="4" t="n"/>
       <c r="Y789" s="4" t="n"/>
     </row>
     <row r="790">
@@ -22053,7 +22053,7 @@
       <c r="U790" s="2" t="n"/>
       <c r="V790" s="3" t="n"/>
       <c r="W790" s="2" t="n"/>
-      <c r="X790" s="3" t="n"/>
+      <c r="X790" s="2" t="n"/>
       <c r="Y790" s="2" t="n"/>
     </row>
     <row r="791">
@@ -22080,7 +22080,7 @@
       <c r="U791" s="4" t="n"/>
       <c r="V791" s="3" t="n"/>
       <c r="W791" s="4" t="n"/>
-      <c r="X791" s="3" t="n"/>
+      <c r="X791" s="4" t="n"/>
       <c r="Y791" s="4" t="n"/>
     </row>
     <row r="792">
@@ -22107,7 +22107,7 @@
       <c r="U792" s="2" t="n"/>
       <c r="V792" s="3" t="n"/>
       <c r="W792" s="2" t="n"/>
-      <c r="X792" s="3" t="n"/>
+      <c r="X792" s="2" t="n"/>
       <c r="Y792" s="2" t="n"/>
     </row>
     <row r="793">
@@ -22134,7 +22134,7 @@
       <c r="U793" s="4" t="n"/>
       <c r="V793" s="3" t="n"/>
       <c r="W793" s="4" t="n"/>
-      <c r="X793" s="3" t="n"/>
+      <c r="X793" s="4" t="n"/>
       <c r="Y793" s="4" t="n"/>
     </row>
     <row r="794">
@@ -22161,7 +22161,7 @@
       <c r="U794" s="2" t="n"/>
       <c r="V794" s="3" t="n"/>
       <c r="W794" s="2" t="n"/>
-      <c r="X794" s="3" t="n"/>
+      <c r="X794" s="2" t="n"/>
       <c r="Y794" s="2" t="n"/>
     </row>
     <row r="795">
@@ -22188,7 +22188,7 @@
       <c r="U795" s="4" t="n"/>
       <c r="V795" s="3" t="n"/>
       <c r="W795" s="4" t="n"/>
-      <c r="X795" s="3" t="n"/>
+      <c r="X795" s="4" t="n"/>
       <c r="Y795" s="4" t="n"/>
     </row>
     <row r="796">
@@ -22215,7 +22215,7 @@
       <c r="U796" s="2" t="n"/>
       <c r="V796" s="3" t="n"/>
       <c r="W796" s="2" t="n"/>
-      <c r="X796" s="3" t="n"/>
+      <c r="X796" s="2" t="n"/>
       <c r="Y796" s="2" t="n"/>
     </row>
     <row r="797">
@@ -22242,7 +22242,7 @@
       <c r="U797" s="4" t="n"/>
       <c r="V797" s="3" t="n"/>
       <c r="W797" s="4" t="n"/>
-      <c r="X797" s="3" t="n"/>
+      <c r="X797" s="4" t="n"/>
       <c r="Y797" s="4" t="n"/>
     </row>
     <row r="798">
@@ -22269,7 +22269,7 @@
       <c r="U798" s="2" t="n"/>
       <c r="V798" s="3" t="n"/>
       <c r="W798" s="2" t="n"/>
-      <c r="X798" s="3" t="n"/>
+      <c r="X798" s="2" t="n"/>
       <c r="Y798" s="2" t="n"/>
     </row>
     <row r="799">
@@ -22296,7 +22296,7 @@
       <c r="U799" s="4" t="n"/>
       <c r="V799" s="3" t="n"/>
       <c r="W799" s="4" t="n"/>
-      <c r="X799" s="3" t="n"/>
+      <c r="X799" s="4" t="n"/>
       <c r="Y799" s="4" t="n"/>
     </row>
     <row r="800">
@@ -22323,7 +22323,7 @@
       <c r="U800" s="2" t="n"/>
       <c r="V800" s="3" t="n"/>
       <c r="W800" s="2" t="n"/>
-      <c r="X800" s="3" t="n"/>
+      <c r="X800" s="2" t="n"/>
       <c r="Y800" s="2" t="n"/>
     </row>
     <row r="801">
@@ -22350,7 +22350,7 @@
       <c r="U801" s="4" t="n"/>
       <c r="V801" s="3" t="n"/>
       <c r="W801" s="4" t="n"/>
-      <c r="X801" s="3" t="n"/>
+      <c r="X801" s="4" t="n"/>
       <c r="Y801" s="4" t="n"/>
     </row>
     <row r="802">
@@ -22377,7 +22377,7 @@
       <c r="U802" s="2" t="n"/>
       <c r="V802" s="3" t="n"/>
       <c r="W802" s="2" t="n"/>
-      <c r="X802" s="3" t="n"/>
+      <c r="X802" s="2" t="n"/>
       <c r="Y802" s="2" t="n"/>
     </row>
     <row r="803">
@@ -22404,7 +22404,7 @@
       <c r="U803" s="4" t="n"/>
       <c r="V803" s="3" t="n"/>
       <c r="W803" s="4" t="n"/>
-      <c r="X803" s="3" t="n"/>
+      <c r="X803" s="4" t="n"/>
       <c r="Y803" s="4" t="n"/>
     </row>
     <row r="804">
@@ -22431,7 +22431,7 @@
       <c r="U804" s="2" t="n"/>
       <c r="V804" s="3" t="n"/>
       <c r="W804" s="2" t="n"/>
-      <c r="X804" s="3" t="n"/>
+      <c r="X804" s="2" t="n"/>
       <c r="Y804" s="2" t="n"/>
     </row>
     <row r="805">
@@ -22458,7 +22458,7 @@
       <c r="U805" s="4" t="n"/>
       <c r="V805" s="3" t="n"/>
       <c r="W805" s="4" t="n"/>
-      <c r="X805" s="3" t="n"/>
+      <c r="X805" s="4" t="n"/>
       <c r="Y805" s="4" t="n"/>
     </row>
     <row r="806">
@@ -22485,7 +22485,7 @@
       <c r="U806" s="2" t="n"/>
       <c r="V806" s="3" t="n"/>
       <c r="W806" s="2" t="n"/>
-      <c r="X806" s="3" t="n"/>
+      <c r="X806" s="2" t="n"/>
       <c r="Y806" s="2" t="n"/>
     </row>
     <row r="807">
@@ -22512,7 +22512,7 @@
       <c r="U807" s="4" t="n"/>
       <c r="V807" s="3" t="n"/>
       <c r="W807" s="4" t="n"/>
-      <c r="X807" s="3" t="n"/>
+      <c r="X807" s="4" t="n"/>
       <c r="Y807" s="4" t="n"/>
     </row>
     <row r="808">
@@ -22539,7 +22539,7 @@
       <c r="U808" s="2" t="n"/>
       <c r="V808" s="3" t="n"/>
       <c r="W808" s="2" t="n"/>
-      <c r="X808" s="3" t="n"/>
+      <c r="X808" s="2" t="n"/>
       <c r="Y808" s="2" t="n"/>
     </row>
     <row r="809">
@@ -22566,7 +22566,7 @@
       <c r="U809" s="4" t="n"/>
       <c r="V809" s="3" t="n"/>
       <c r="W809" s="4" t="n"/>
-      <c r="X809" s="3" t="n"/>
+      <c r="X809" s="4" t="n"/>
       <c r="Y809" s="4" t="n"/>
     </row>
     <row r="810">
@@ -22593,7 +22593,7 @@
       <c r="U810" s="2" t="n"/>
       <c r="V810" s="3" t="n"/>
       <c r="W810" s="2" t="n"/>
-      <c r="X810" s="3" t="n"/>
+      <c r="X810" s="2" t="n"/>
       <c r="Y810" s="2" t="n"/>
     </row>
     <row r="811">
@@ -22620,7 +22620,7 @@
       <c r="U811" s="4" t="n"/>
       <c r="V811" s="3" t="n"/>
       <c r="W811" s="4" t="n"/>
-      <c r="X811" s="3" t="n"/>
+      <c r="X811" s="4" t="n"/>
       <c r="Y811" s="4" t="n"/>
     </row>
     <row r="812">
@@ -22647,7 +22647,7 @@
       <c r="U812" s="2" t="n"/>
       <c r="V812" s="3" t="n"/>
       <c r="W812" s="2" t="n"/>
-      <c r="X812" s="3" t="n"/>
+      <c r="X812" s="2" t="n"/>
       <c r="Y812" s="2" t="n"/>
     </row>
     <row r="813">
@@ -22674,7 +22674,7 @@
       <c r="U813" s="4" t="n"/>
       <c r="V813" s="3" t="n"/>
       <c r="W813" s="4" t="n"/>
-      <c r="X813" s="3" t="n"/>
+      <c r="X813" s="4" t="n"/>
       <c r="Y813" s="4" t="n"/>
     </row>
     <row r="814">
@@ -22701,7 +22701,7 @@
       <c r="U814" s="2" t="n"/>
       <c r="V814" s="3" t="n"/>
       <c r="W814" s="2" t="n"/>
-      <c r="X814" s="3" t="n"/>
+      <c r="X814" s="2" t="n"/>
       <c r="Y814" s="2" t="n"/>
     </row>
     <row r="815">
@@ -22728,7 +22728,7 @@
       <c r="U815" s="4" t="n"/>
       <c r="V815" s="3" t="n"/>
       <c r="W815" s="4" t="n"/>
-      <c r="X815" s="3" t="n"/>
+      <c r="X815" s="4" t="n"/>
       <c r="Y815" s="4" t="n"/>
     </row>
     <row r="816">
@@ -22755,7 +22755,7 @@
       <c r="U816" s="2" t="n"/>
       <c r="V816" s="3" t="n"/>
       <c r="W816" s="2" t="n"/>
-      <c r="X816" s="3" t="n"/>
+      <c r="X816" s="2" t="n"/>
       <c r="Y816" s="2" t="n"/>
     </row>
     <row r="817">
@@ -22782,7 +22782,7 @@
       <c r="U817" s="4" t="n"/>
       <c r="V817" s="3" t="n"/>
       <c r="W817" s="4" t="n"/>
-      <c r="X817" s="3" t="n"/>
+      <c r="X817" s="4" t="n"/>
       <c r="Y817" s="4" t="n"/>
     </row>
     <row r="818">
@@ -22809,7 +22809,7 @@
       <c r="U818" s="2" t="n"/>
       <c r="V818" s="3" t="n"/>
       <c r="W818" s="2" t="n"/>
-      <c r="X818" s="3" t="n"/>
+      <c r="X818" s="2" t="n"/>
       <c r="Y818" s="2" t="n"/>
     </row>
     <row r="819">
@@ -22836,7 +22836,7 @@
       <c r="U819" s="4" t="n"/>
       <c r="V819" s="3" t="n"/>
       <c r="W819" s="4" t="n"/>
-      <c r="X819" s="3" t="n"/>
+      <c r="X819" s="4" t="n"/>
       <c r="Y819" s="4" t="n"/>
     </row>
     <row r="820">
@@ -22863,7 +22863,7 @@
       <c r="U820" s="2" t="n"/>
       <c r="V820" s="3" t="n"/>
       <c r="W820" s="2" t="n"/>
-      <c r="X820" s="3" t="n"/>
+      <c r="X820" s="2" t="n"/>
       <c r="Y820" s="2" t="n"/>
     </row>
     <row r="821">
@@ -22890,7 +22890,7 @@
       <c r="U821" s="4" t="n"/>
       <c r="V821" s="3" t="n"/>
       <c r="W821" s="4" t="n"/>
-      <c r="X821" s="3" t="n"/>
+      <c r="X821" s="4" t="n"/>
       <c r="Y821" s="4" t="n"/>
     </row>
     <row r="822">
@@ -22917,7 +22917,7 @@
       <c r="U822" s="2" t="n"/>
       <c r="V822" s="3" t="n"/>
       <c r="W822" s="2" t="n"/>
-      <c r="X822" s="3" t="n"/>
+      <c r="X822" s="2" t="n"/>
       <c r="Y822" s="2" t="n"/>
     </row>
     <row r="823">
@@ -22944,7 +22944,7 @@
       <c r="U823" s="4" t="n"/>
       <c r="V823" s="3" t="n"/>
       <c r="W823" s="4" t="n"/>
-      <c r="X823" s="3" t="n"/>
+      <c r="X823" s="4" t="n"/>
       <c r="Y823" s="4" t="n"/>
     </row>
     <row r="824">
@@ -22971,7 +22971,7 @@
       <c r="U824" s="2" t="n"/>
       <c r="V824" s="3" t="n"/>
       <c r="W824" s="2" t="n"/>
-      <c r="X824" s="3" t="n"/>
+      <c r="X824" s="2" t="n"/>
       <c r="Y824" s="2" t="n"/>
     </row>
     <row r="825">
@@ -22998,7 +22998,7 @@
       <c r="U825" s="4" t="n"/>
       <c r="V825" s="3" t="n"/>
       <c r="W825" s="4" t="n"/>
-      <c r="X825" s="3" t="n"/>
+      <c r="X825" s="4" t="n"/>
       <c r="Y825" s="4" t="n"/>
     </row>
     <row r="826">
@@ -23025,7 +23025,7 @@
       <c r="U826" s="2" t="n"/>
       <c r="V826" s="3" t="n"/>
       <c r="W826" s="2" t="n"/>
-      <c r="X826" s="3" t="n"/>
+      <c r="X826" s="2" t="n"/>
       <c r="Y826" s="2" t="n"/>
     </row>
     <row r="827">
@@ -23052,7 +23052,7 @@
       <c r="U827" s="4" t="n"/>
       <c r="V827" s="3" t="n"/>
       <c r="W827" s="4" t="n"/>
-      <c r="X827" s="3" t="n"/>
+      <c r="X827" s="4" t="n"/>
       <c r="Y827" s="4" t="n"/>
     </row>
     <row r="828">
@@ -23079,7 +23079,7 @@
       <c r="U828" s="2" t="n"/>
       <c r="V828" s="3" t="n"/>
       <c r="W828" s="2" t="n"/>
-      <c r="X828" s="3" t="n"/>
+      <c r="X828" s="2" t="n"/>
       <c r="Y828" s="2" t="n"/>
     </row>
     <row r="829">
@@ -23106,7 +23106,7 @@
       <c r="U829" s="4" t="n"/>
       <c r="V829" s="3" t="n"/>
       <c r="W829" s="4" t="n"/>
-      <c r="X829" s="3" t="n"/>
+      <c r="X829" s="4" t="n"/>
       <c r="Y829" s="4" t="n"/>
     </row>
     <row r="830">
@@ -23133,7 +23133,7 @@
       <c r="U830" s="2" t="n"/>
       <c r="V830" s="3" t="n"/>
       <c r="W830" s="2" t="n"/>
-      <c r="X830" s="3" t="n"/>
+      <c r="X830" s="2" t="n"/>
       <c r="Y830" s="2" t="n"/>
     </row>
     <row r="831">
@@ -23160,7 +23160,7 @@
       <c r="U831" s="4" t="n"/>
       <c r="V831" s="3" t="n"/>
       <c r="W831" s="4" t="n"/>
-      <c r="X831" s="3" t="n"/>
+      <c r="X831" s="4" t="n"/>
       <c r="Y831" s="4" t="n"/>
     </row>
     <row r="832">
@@ -23187,7 +23187,7 @@
       <c r="U832" s="2" t="n"/>
       <c r="V832" s="3" t="n"/>
       <c r="W832" s="2" t="n"/>
-      <c r="X832" s="3" t="n"/>
+      <c r="X832" s="2" t="n"/>
       <c r="Y832" s="2" t="n"/>
     </row>
     <row r="833">
@@ -23214,7 +23214,7 @@
       <c r="U833" s="4" t="n"/>
       <c r="V833" s="3" t="n"/>
       <c r="W833" s="4" t="n"/>
-      <c r="X833" s="3" t="n"/>
+      <c r="X833" s="4" t="n"/>
       <c r="Y833" s="4" t="n"/>
     </row>
     <row r="834">
@@ -23241,7 +23241,7 @@
       <c r="U834" s="2" t="n"/>
       <c r="V834" s="3" t="n"/>
       <c r="W834" s="2" t="n"/>
-      <c r="X834" s="3" t="n"/>
+      <c r="X834" s="2" t="n"/>
       <c r="Y834" s="2" t="n"/>
     </row>
     <row r="835">
@@ -23268,7 +23268,7 @@
       <c r="U835" s="4" t="n"/>
       <c r="V835" s="3" t="n"/>
       <c r="W835" s="4" t="n"/>
-      <c r="X835" s="3" t="n"/>
+      <c r="X835" s="4" t="n"/>
       <c r="Y835" s="4" t="n"/>
     </row>
     <row r="836">
@@ -23295,7 +23295,7 @@
       <c r="U836" s="2" t="n"/>
       <c r="V836" s="3" t="n"/>
       <c r="W836" s="2" t="n"/>
-      <c r="X836" s="3" t="n"/>
+      <c r="X836" s="2" t="n"/>
       <c r="Y836" s="2" t="n"/>
     </row>
     <row r="837">
@@ -23322,7 +23322,7 @@
       <c r="U837" s="4" t="n"/>
       <c r="V837" s="3" t="n"/>
       <c r="W837" s="4" t="n"/>
-      <c r="X837" s="3" t="n"/>
+      <c r="X837" s="4" t="n"/>
       <c r="Y837" s="4" t="n"/>
     </row>
     <row r="838">
@@ -23349,7 +23349,7 @@
       <c r="U838" s="2" t="n"/>
       <c r="V838" s="3" t="n"/>
       <c r="W838" s="2" t="n"/>
-      <c r="X838" s="3" t="n"/>
+      <c r="X838" s="2" t="n"/>
       <c r="Y838" s="2" t="n"/>
     </row>
     <row r="839">
@@ -23376,7 +23376,7 @@
       <c r="U839" s="4" t="n"/>
       <c r="V839" s="3" t="n"/>
       <c r="W839" s="4" t="n"/>
-      <c r="X839" s="3" t="n"/>
+      <c r="X839" s="4" t="n"/>
       <c r="Y839" s="4" t="n"/>
     </row>
     <row r="840">
@@ -23403,7 +23403,7 @@
       <c r="U840" s="2" t="n"/>
       <c r="V840" s="3" t="n"/>
       <c r="W840" s="2" t="n"/>
-      <c r="X840" s="3" t="n"/>
+      <c r="X840" s="2" t="n"/>
       <c r="Y840" s="2" t="n"/>
     </row>
     <row r="841">
@@ -23430,7 +23430,7 @@
       <c r="U841" s="4" t="n"/>
       <c r="V841" s="3" t="n"/>
       <c r="W841" s="4" t="n"/>
-      <c r="X841" s="3" t="n"/>
+      <c r="X841" s="4" t="n"/>
       <c r="Y841" s="4" t="n"/>
     </row>
     <row r="842">
@@ -23457,7 +23457,7 @@
       <c r="U842" s="2" t="n"/>
       <c r="V842" s="3" t="n"/>
       <c r="W842" s="2" t="n"/>
-      <c r="X842" s="3" t="n"/>
+      <c r="X842" s="2" t="n"/>
       <c r="Y842" s="2" t="n"/>
     </row>
     <row r="843">
@@ -23484,7 +23484,7 @@
       <c r="U843" s="4" t="n"/>
       <c r="V843" s="3" t="n"/>
       <c r="W843" s="4" t="n"/>
-      <c r="X843" s="3" t="n"/>
+      <c r="X843" s="4" t="n"/>
       <c r="Y843" s="4" t="n"/>
     </row>
     <row r="844">
@@ -23511,7 +23511,7 @@
       <c r="U844" s="2" t="n"/>
       <c r="V844" s="3" t="n"/>
       <c r="W844" s="2" t="n"/>
-      <c r="X844" s="3" t="n"/>
+      <c r="X844" s="2" t="n"/>
       <c r="Y844" s="2" t="n"/>
     </row>
     <row r="845">
@@ -23538,7 +23538,7 @@
       <c r="U845" s="4" t="n"/>
       <c r="V845" s="3" t="n"/>
       <c r="W845" s="4" t="n"/>
-      <c r="X845" s="3" t="n"/>
+      <c r="X845" s="4" t="n"/>
       <c r="Y845" s="4" t="n"/>
     </row>
     <row r="846">
@@ -23565,7 +23565,7 @@
       <c r="U846" s="2" t="n"/>
       <c r="V846" s="3" t="n"/>
       <c r="W846" s="2" t="n"/>
-      <c r="X846" s="3" t="n"/>
+      <c r="X846" s="2" t="n"/>
       <c r="Y846" s="2" t="n"/>
     </row>
     <row r="847">
@@ -23592,7 +23592,7 @@
       <c r="U847" s="4" t="n"/>
       <c r="V847" s="3" t="n"/>
       <c r="W847" s="4" t="n"/>
-      <c r="X847" s="3" t="n"/>
+      <c r="X847" s="4" t="n"/>
       <c r="Y847" s="4" t="n"/>
     </row>
     <row r="848">
@@ -23619,7 +23619,7 @@
       <c r="U848" s="2" t="n"/>
       <c r="V848" s="3" t="n"/>
       <c r="W848" s="2" t="n"/>
-      <c r="X848" s="3" t="n"/>
+      <c r="X848" s="2" t="n"/>
       <c r="Y848" s="2" t="n"/>
     </row>
     <row r="849">
@@ -23646,7 +23646,7 @@
       <c r="U849" s="4" t="n"/>
       <c r="V849" s="3" t="n"/>
       <c r="W849" s="4" t="n"/>
-      <c r="X849" s="3" t="n"/>
+      <c r="X849" s="4" t="n"/>
       <c r="Y849" s="4" t="n"/>
     </row>
     <row r="850">
@@ -23673,7 +23673,7 @@
       <c r="U850" s="2" t="n"/>
       <c r="V850" s="3" t="n"/>
       <c r="W850" s="2" t="n"/>
-      <c r="X850" s="3" t="n"/>
+      <c r="X850" s="2" t="n"/>
       <c r="Y850" s="2" t="n"/>
     </row>
     <row r="851">
@@ -23700,7 +23700,7 @@
       <c r="U851" s="4" t="n"/>
       <c r="V851" s="3" t="n"/>
       <c r="W851" s="4" t="n"/>
-      <c r="X851" s="3" t="n"/>
+      <c r="X851" s="4" t="n"/>
       <c r="Y851" s="4" t="n"/>
     </row>
     <row r="852">
@@ -23727,7 +23727,7 @@
       <c r="U852" s="2" t="n"/>
       <c r="V852" s="3" t="n"/>
       <c r="W852" s="2" t="n"/>
-      <c r="X852" s="3" t="n"/>
+      <c r="X852" s="2" t="n"/>
       <c r="Y852" s="2" t="n"/>
     </row>
     <row r="853">
@@ -23754,7 +23754,7 @@
       <c r="U853" s="4" t="n"/>
       <c r="V853" s="3" t="n"/>
       <c r="W853" s="4" t="n"/>
-      <c r="X853" s="3" t="n"/>
+      <c r="X853" s="4" t="n"/>
       <c r="Y853" s="4" t="n"/>
     </row>
     <row r="854">
@@ -23781,7 +23781,7 @@
       <c r="U854" s="2" t="n"/>
       <c r="V854" s="3" t="n"/>
       <c r="W854" s="2" t="n"/>
-      <c r="X854" s="3" t="n"/>
+      <c r="X854" s="2" t="n"/>
       <c r="Y854" s="2" t="n"/>
     </row>
     <row r="855">
@@ -23808,7 +23808,7 @@
       <c r="U855" s="4" t="n"/>
       <c r="V855" s="3" t="n"/>
       <c r="W855" s="4" t="n"/>
-      <c r="X855" s="3" t="n"/>
+      <c r="X855" s="4" t="n"/>
       <c r="Y855" s="4" t="n"/>
     </row>
     <row r="856">
@@ -23835,7 +23835,7 @@
       <c r="U856" s="2" t="n"/>
       <c r="V856" s="3" t="n"/>
       <c r="W856" s="2" t="n"/>
-      <c r="X856" s="3" t="n"/>
+      <c r="X856" s="2" t="n"/>
       <c r="Y856" s="2" t="n"/>
     </row>
     <row r="857">
@@ -23862,7 +23862,7 @@
       <c r="U857" s="4" t="n"/>
       <c r="V857" s="3" t="n"/>
       <c r="W857" s="4" t="n"/>
-      <c r="X857" s="3" t="n"/>
+      <c r="X857" s="4" t="n"/>
       <c r="Y857" s="4" t="n"/>
     </row>
     <row r="858">
@@ -23889,7 +23889,7 @@
       <c r="U858" s="2" t="n"/>
       <c r="V858" s="3" t="n"/>
       <c r="W858" s="2" t="n"/>
-      <c r="X858" s="3" t="n"/>
+      <c r="X858" s="2" t="n"/>
       <c r="Y858" s="2" t="n"/>
     </row>
     <row r="859">
@@ -23916,7 +23916,7 @@
       <c r="U859" s="4" t="n"/>
       <c r="V859" s="3" t="n"/>
       <c r="W859" s="4" t="n"/>
-      <c r="X859" s="3" t="n"/>
+      <c r="X859" s="4" t="n"/>
       <c r="Y859" s="4" t="n"/>
     </row>
     <row r="860">
@@ -23943,7 +23943,7 @@
       <c r="U860" s="2" t="n"/>
       <c r="V860" s="3" t="n"/>
       <c r="W860" s="2" t="n"/>
-      <c r="X860" s="3" t="n"/>
+      <c r="X860" s="2" t="n"/>
       <c r="Y860" s="2" t="n"/>
     </row>
     <row r="861">
@@ -23970,7 +23970,7 @@
       <c r="U861" s="4" t="n"/>
       <c r="V861" s="3" t="n"/>
       <c r="W861" s="4" t="n"/>
-      <c r="X861" s="3" t="n"/>
+      <c r="X861" s="4" t="n"/>
       <c r="Y861" s="4" t="n"/>
     </row>
     <row r="862">
@@ -23997,7 +23997,7 @@
       <c r="U862" s="2" t="n"/>
       <c r="V862" s="3" t="n"/>
       <c r="W862" s="2" t="n"/>
-      <c r="X862" s="3" t="n"/>
+      <c r="X862" s="2" t="n"/>
       <c r="Y862" s="2" t="n"/>
     </row>
     <row r="863">
@@ -24024,7 +24024,7 @@
       <c r="U863" s="4" t="n"/>
       <c r="V863" s="3" t="n"/>
       <c r="W863" s="4" t="n"/>
-      <c r="X863" s="3" t="n"/>
+      <c r="X863" s="4" t="n"/>
       <c r="Y863" s="4" t="n"/>
     </row>
     <row r="864">
@@ -24051,7 +24051,7 @@
       <c r="U864" s="2" t="n"/>
       <c r="V864" s="3" t="n"/>
       <c r="W864" s="2" t="n"/>
-      <c r="X864" s="3" t="n"/>
+      <c r="X864" s="2" t="n"/>
       <c r="Y864" s="2" t="n"/>
     </row>
     <row r="865">
@@ -24078,7 +24078,7 @@
       <c r="U865" s="4" t="n"/>
       <c r="V865" s="3" t="n"/>
       <c r="W865" s="4" t="n"/>
-      <c r="X865" s="3" t="n"/>
+      <c r="X865" s="4" t="n"/>
       <c r="Y865" s="4" t="n"/>
     </row>
     <row r="866">
@@ -24105,7 +24105,7 @@
       <c r="U866" s="2" t="n"/>
       <c r="V866" s="3" t="n"/>
       <c r="W866" s="2" t="n"/>
-      <c r="X866" s="3" t="n"/>
+      <c r="X866" s="2" t="n"/>
       <c r="Y866" s="2" t="n"/>
     </row>
     <row r="867">
@@ -24132,7 +24132,7 @@
       <c r="U867" s="4" t="n"/>
       <c r="V867" s="3" t="n"/>
       <c r="W867" s="4" t="n"/>
-      <c r="X867" s="3" t="n"/>
+      <c r="X867" s="4" t="n"/>
       <c r="Y867" s="4" t="n"/>
     </row>
     <row r="868">
@@ -24159,7 +24159,7 @@
       <c r="U868" s="2" t="n"/>
       <c r="V868" s="3" t="n"/>
       <c r="W868" s="2" t="n"/>
-      <c r="X868" s="3" t="n"/>
+      <c r="X868" s="2" t="n"/>
       <c r="Y868" s="2" t="n"/>
     </row>
     <row r="869">
@@ -24186,7 +24186,7 @@
       <c r="U869" s="4" t="n"/>
       <c r="V869" s="3" t="n"/>
       <c r="W869" s="4" t="n"/>
-      <c r="X869" s="3" t="n"/>
+      <c r="X869" s="4" t="n"/>
       <c r="Y869" s="4" t="n"/>
     </row>
     <row r="870">
@@ -24213,7 +24213,7 @@
       <c r="U870" s="2" t="n"/>
       <c r="V870" s="3" t="n"/>
       <c r="W870" s="2" t="n"/>
-      <c r="X870" s="3" t="n"/>
+      <c r="X870" s="2" t="n"/>
       <c r="Y870" s="2" t="n"/>
     </row>
     <row r="871">
@@ -24240,7 +24240,7 @@
       <c r="U871" s="4" t="n"/>
       <c r="V871" s="3" t="n"/>
       <c r="W871" s="4" t="n"/>
-      <c r="X871" s="3" t="n"/>
+      <c r="X871" s="4" t="n"/>
       <c r="Y871" s="4" t="n"/>
     </row>
     <row r="872">
@@ -24267,7 +24267,7 @@
       <c r="U872" s="2" t="n"/>
       <c r="V872" s="3" t="n"/>
       <c r="W872" s="2" t="n"/>
-      <c r="X872" s="3" t="n"/>
+      <c r="X872" s="2" t="n"/>
       <c r="Y872" s="2" t="n"/>
     </row>
     <row r="873">
@@ -24294,7 +24294,7 @@
       <c r="U873" s="4" t="n"/>
       <c r="V873" s="3" t="n"/>
       <c r="W873" s="4" t="n"/>
-      <c r="X873" s="3" t="n"/>
+      <c r="X873" s="4" t="n"/>
       <c r="Y873" s="4" t="n"/>
     </row>
     <row r="874">
@@ -24321,7 +24321,7 @@
       <c r="U874" s="2" t="n"/>
       <c r="V874" s="3" t="n"/>
       <c r="W874" s="2" t="n"/>
-      <c r="X874" s="3" t="n"/>
+      <c r="X874" s="2" t="n"/>
       <c r="Y874" s="2" t="n"/>
     </row>
     <row r="875">
@@ -24348,7 +24348,7 @@
       <c r="U875" s="4" t="n"/>
       <c r="V875" s="3" t="n"/>
       <c r="W875" s="4" t="n"/>
-      <c r="X875" s="3" t="n"/>
+      <c r="X875" s="4" t="n"/>
       <c r="Y875" s="4" t="n"/>
     </row>
     <row r="876">
@@ -24375,7 +24375,7 @@
       <c r="U876" s="2" t="n"/>
       <c r="V876" s="3" t="n"/>
       <c r="W876" s="2" t="n"/>
-      <c r="X876" s="3" t="n"/>
+      <c r="X876" s="2" t="n"/>
       <c r="Y876" s="2" t="n"/>
     </row>
     <row r="877">
@@ -24402,7 +24402,7 @@
       <c r="U877" s="4" t="n"/>
       <c r="V877" s="3" t="n"/>
       <c r="W877" s="4" t="n"/>
-      <c r="X877" s="3" t="n"/>
+      <c r="X877" s="4" t="n"/>
       <c r="Y877" s="4" t="n"/>
     </row>
     <row r="878">
@@ -24429,7 +24429,7 @@
       <c r="U878" s="2" t="n"/>
       <c r="V878" s="3" t="n"/>
       <c r="W878" s="2" t="n"/>
-      <c r="X878" s="3" t="n"/>
+      <c r="X878" s="2" t="n"/>
       <c r="Y878" s="2" t="n"/>
     </row>
     <row r="879">
@@ -24456,7 +24456,7 @@
       <c r="U879" s="4" t="n"/>
       <c r="V879" s="3" t="n"/>
       <c r="W879" s="4" t="n"/>
-      <c r="X879" s="3" t="n"/>
+      <c r="X879" s="4" t="n"/>
       <c r="Y879" s="4" t="n"/>
     </row>
     <row r="880">
@@ -24483,7 +24483,7 @@
       <c r="U880" s="2" t="n"/>
       <c r="V880" s="3" t="n"/>
       <c r="W880" s="2" t="n"/>
-      <c r="X880" s="3" t="n"/>
+      <c r="X880" s="2" t="n"/>
       <c r="Y880" s="2" t="n"/>
     </row>
     <row r="881">
@@ -24510,7 +24510,7 @@
       <c r="U881" s="4" t="n"/>
       <c r="V881" s="3" t="n"/>
       <c r="W881" s="4" t="n"/>
-      <c r="X881" s="3" t="n"/>
+      <c r="X881" s="4" t="n"/>
       <c r="Y881" s="4" t="n"/>
     </row>
     <row r="882">
@@ -24537,7 +24537,7 @@
       <c r="U882" s="2" t="n"/>
       <c r="V882" s="3" t="n"/>
       <c r="W882" s="2" t="n"/>
-      <c r="X882" s="3" t="n"/>
+      <c r="X882" s="2" t="n"/>
       <c r="Y882" s="2" t="n"/>
     </row>
     <row r="883">
@@ -24564,7 +24564,7 @@
       <c r="U883" s="4" t="n"/>
       <c r="V883" s="3" t="n"/>
       <c r="W883" s="4" t="n"/>
-      <c r="X883" s="3" t="n"/>
+      <c r="X883" s="4" t="n"/>
       <c r="Y883" s="4" t="n"/>
     </row>
     <row r="884">
@@ -24591,7 +24591,7 @@
       <c r="U884" s="2" t="n"/>
       <c r="V884" s="3" t="n"/>
       <c r="W884" s="2" t="n"/>
-      <c r="X884" s="3" t="n"/>
+      <c r="X884" s="2" t="n"/>
       <c r="Y884" s="2" t="n"/>
     </row>
     <row r="885">
@@ -24618,7 +24618,7 @@
       <c r="U885" s="4" t="n"/>
       <c r="V885" s="3" t="n"/>
       <c r="W885" s="4" t="n"/>
-      <c r="X885" s="3" t="n"/>
+      <c r="X885" s="4" t="n"/>
       <c r="Y885" s="4" t="n"/>
     </row>
     <row r="886">
@@ -24645,7 +24645,7 @@
       <c r="U886" s="2" t="n"/>
       <c r="V886" s="3" t="n"/>
       <c r="W886" s="2" t="n"/>
-      <c r="X886" s="3" t="n"/>
+      <c r="X886" s="2" t="n"/>
       <c r="Y886" s="2" t="n"/>
     </row>
     <row r="887">
@@ -24672,7 +24672,7 @@
       <c r="U887" s="4" t="n"/>
       <c r="V887" s="3" t="n"/>
       <c r="W887" s="4" t="n"/>
-      <c r="X887" s="3" t="n"/>
+      <c r="X887" s="4" t="n"/>
       <c r="Y887" s="4" t="n"/>
     </row>
     <row r="888">
@@ -24699,7 +24699,7 @@
       <c r="U888" s="2" t="n"/>
       <c r="V888" s="3" t="n"/>
       <c r="W888" s="2" t="n"/>
-      <c r="X888" s="3" t="n"/>
+      <c r="X888" s="2" t="n"/>
       <c r="Y888" s="2" t="n"/>
     </row>
     <row r="889">
@@ -24726,7 +24726,7 @@
       <c r="U889" s="4" t="n"/>
       <c r="V889" s="3" t="n"/>
       <c r="W889" s="4" t="n"/>
-      <c r="X889" s="3" t="n"/>
+      <c r="X889" s="4" t="n"/>
       <c r="Y889" s="4" t="n"/>
     </row>
     <row r="890">
@@ -24753,7 +24753,7 @@
       <c r="U890" s="2" t="n"/>
       <c r="V890" s="3" t="n"/>
       <c r="W890" s="2" t="n"/>
-      <c r="X890" s="3" t="n"/>
+      <c r="X890" s="2" t="n"/>
       <c r="Y890" s="2" t="n"/>
     </row>
     <row r="891">
@@ -24780,7 +24780,7 @@
       <c r="U891" s="4" t="n"/>
       <c r="V891" s="3" t="n"/>
       <c r="W891" s="4" t="n"/>
-      <c r="X891" s="3" t="n"/>
+      <c r="X891" s="4" t="n"/>
       <c r="Y891" s="4" t="n"/>
     </row>
     <row r="892">
@@ -24807,7 +24807,7 @@
       <c r="U892" s="2" t="n"/>
       <c r="V892" s="3" t="n"/>
       <c r="W892" s="2" t="n"/>
-      <c r="X892" s="3" t="n"/>
+      <c r="X892" s="2" t="n"/>
       <c r="Y892" s="2" t="n"/>
     </row>
     <row r="893">
@@ -24834,7 +24834,7 @@
       <c r="U893" s="4" t="n"/>
       <c r="V893" s="3" t="n"/>
       <c r="W893" s="4" t="n"/>
-      <c r="X893" s="3" t="n"/>
+      <c r="X893" s="4" t="n"/>
       <c r="Y893" s="4" t="n"/>
     </row>
     <row r="894">
@@ -24861,7 +24861,7 @@
       <c r="U894" s="2" t="n"/>
       <c r="V894" s="3" t="n"/>
       <c r="W894" s="2" t="n"/>
-      <c r="X894" s="3" t="n"/>
+      <c r="X894" s="2" t="n"/>
       <c r="Y894" s="2" t="n"/>
     </row>
     <row r="895">
@@ -24888,7 +24888,7 @@
       <c r="U895" s="4" t="n"/>
       <c r="V895" s="3" t="n"/>
       <c r="W895" s="4" t="n"/>
-      <c r="X895" s="3" t="n"/>
+      <c r="X895" s="4" t="n"/>
       <c r="Y895" s="4" t="n"/>
     </row>
     <row r="896">
@@ -24915,7 +24915,7 @@
       <c r="U896" s="2" t="n"/>
       <c r="V896" s="3" t="n"/>
       <c r="W896" s="2" t="n"/>
-      <c r="X896" s="3" t="n"/>
+      <c r="X896" s="2" t="n"/>
       <c r="Y896" s="2" t="n"/>
     </row>
     <row r="897">
@@ -24942,7 +24942,7 @@
       <c r="U897" s="4" t="n"/>
       <c r="V897" s="3" t="n"/>
       <c r="W897" s="4" t="n"/>
-      <c r="X897" s="3" t="n"/>
+      <c r="X897" s="4" t="n"/>
       <c r="Y897" s="4" t="n"/>
     </row>
     <row r="898">
@@ -24969,7 +24969,7 @@
       <c r="U898" s="2" t="n"/>
       <c r="V898" s="3" t="n"/>
       <c r="W898" s="2" t="n"/>
-      <c r="X898" s="3" t="n"/>
+      <c r="X898" s="2" t="n"/>
       <c r="Y898" s="2" t="n"/>
     </row>
     <row r="899">
@@ -24996,7 +24996,7 @@
       <c r="U899" s="4" t="n"/>
       <c r="V899" s="3" t="n"/>
       <c r="W899" s="4" t="n"/>
-      <c r="X899" s="3" t="n"/>
+      <c r="X899" s="4" t="n"/>
       <c r="Y899" s="4" t="n"/>
     </row>
     <row r="900">
@@ -25023,7 +25023,7 @@
       <c r="U900" s="2" t="n"/>
       <c r="V900" s="3" t="n"/>
       <c r="W900" s="2" t="n"/>
-      <c r="X900" s="3" t="n"/>
+      <c r="X900" s="2" t="n"/>
       <c r="Y900" s="2" t="n"/>
     </row>
     <row r="901">
@@ -25050,7 +25050,7 @@
       <c r="U901" s="4" t="n"/>
       <c r="V901" s="3" t="n"/>
       <c r="W901" s="4" t="n"/>
-      <c r="X901" s="3" t="n"/>
+      <c r="X901" s="4" t="n"/>
       <c r="Y901" s="4" t="n"/>
     </row>
     <row r="902">
@@ -25077,7 +25077,7 @@
       <c r="U902" s="2" t="n"/>
       <c r="V902" s="3" t="n"/>
       <c r="W902" s="2" t="n"/>
-      <c r="X902" s="3" t="n"/>
+      <c r="X902" s="2" t="n"/>
       <c r="Y902" s="2" t="n"/>
     </row>
     <row r="903">
@@ -25104,7 +25104,7 @@
       <c r="U903" s="4" t="n"/>
       <c r="V903" s="3" t="n"/>
       <c r="W903" s="4" t="n"/>
-      <c r="X903" s="3" t="n"/>
+      <c r="X903" s="4" t="n"/>
       <c r="Y903" s="4" t="n"/>
     </row>
     <row r="904">
@@ -25131,7 +25131,7 @@
       <c r="U904" s="2" t="n"/>
       <c r="V904" s="3" t="n"/>
       <c r="W904" s="2" t="n"/>
-      <c r="X904" s="3" t="n"/>
+      <c r="X904" s="2" t="n"/>
       <c r="Y904" s="2" t="n"/>
     </row>
     <row r="905">
@@ -25158,7 +25158,7 @@
       <c r="U905" s="4" t="n"/>
       <c r="V905" s="3" t="n"/>
       <c r="W905" s="4" t="n"/>
-      <c r="X905" s="3" t="n"/>
+      <c r="X905" s="4" t="n"/>
       <c r="Y905" s="4" t="n"/>
     </row>
     <row r="906">
@@ -25185,7 +25185,7 @@
       <c r="U906" s="2" t="n"/>
       <c r="V906" s="3" t="n"/>
       <c r="W906" s="2" t="n"/>
-      <c r="X906" s="3" t="n"/>
+      <c r="X906" s="2" t="n"/>
       <c r="Y906" s="2" t="n"/>
     </row>
     <row r="907">
@@ -25212,7 +25212,7 @@
       <c r="U907" s="4" t="n"/>
       <c r="V907" s="3" t="n"/>
       <c r="W907" s="4" t="n"/>
-      <c r="X907" s="3" t="n"/>
+      <c r="X907" s="4" t="n"/>
       <c r="Y907" s="4" t="n"/>
     </row>
     <row r="908">
@@ -25239,7 +25239,7 @@
       <c r="U908" s="2" t="n"/>
       <c r="V908" s="3" t="n"/>
       <c r="W908" s="2" t="n"/>
-      <c r="X908" s="3" t="n"/>
+      <c r="X908" s="2" t="n"/>
       <c r="Y908" s="2" t="n"/>
     </row>
     <row r="909">
@@ -25266,7 +25266,7 @@
       <c r="U909" s="4" t="n"/>
       <c r="V909" s="3" t="n"/>
       <c r="W909" s="4" t="n"/>
-      <c r="X909" s="3" t="n"/>
+      <c r="X909" s="4" t="n"/>
       <c r="Y909" s="4" t="n"/>
     </row>
     <row r="910">
@@ -25293,7 +25293,7 @@
       <c r="U910" s="2" t="n"/>
       <c r="V910" s="3" t="n"/>
       <c r="W910" s="2" t="n"/>
-      <c r="X910" s="3" t="n"/>
+      <c r="X910" s="2" t="n"/>
       <c r="Y910" s="2" t="n"/>
     </row>
     <row r="911">
@@ -25320,7 +25320,7 @@
       <c r="U911" s="4" t="n"/>
       <c r="V911" s="3" t="n"/>
       <c r="W911" s="4" t="n"/>
-      <c r="X911" s="3" t="n"/>
+      <c r="X911" s="4" t="n"/>
       <c r="Y911" s="4" t="n"/>
     </row>
     <row r="912">
@@ -25347,7 +25347,7 @@
       <c r="U912" s="2" t="n"/>
       <c r="V912" s="3" t="n"/>
       <c r="W912" s="2" t="n"/>
-      <c r="X912" s="3" t="n"/>
+      <c r="X912" s="2" t="n"/>
       <c r="Y912" s="2" t="n"/>
     </row>
     <row r="913">
@@ -25374,7 +25374,7 @@
       <c r="U913" s="4" t="n"/>
       <c r="V913" s="3" t="n"/>
       <c r="W913" s="4" t="n"/>
-      <c r="X913" s="3" t="n"/>
+      <c r="X913" s="4" t="n"/>
       <c r="Y913" s="4" t="n"/>
     </row>
     <row r="914">
@@ -25401,7 +25401,7 @@
       <c r="U914" s="2" t="n"/>
       <c r="V914" s="3" t="n"/>
       <c r="W914" s="2" t="n"/>
-      <c r="X914" s="3" t="n"/>
+      <c r="X914" s="2" t="n"/>
       <c r="Y914" s="2" t="n"/>
     </row>
     <row r="915">
@@ -25428,7 +25428,7 @@
       <c r="U915" s="4" t="n"/>
       <c r="V915" s="3" t="n"/>
       <c r="W915" s="4" t="n"/>
-      <c r="X915" s="3" t="n"/>
+      <c r="X915" s="4" t="n"/>
       <c r="Y915" s="4" t="n"/>
     </row>
     <row r="916">
@@ -25455,7 +25455,7 @@
       <c r="U916" s="2" t="n"/>
       <c r="V916" s="3" t="n"/>
       <c r="W916" s="2" t="n"/>
-      <c r="X916" s="3" t="n"/>
+      <c r="X916" s="2" t="n"/>
       <c r="Y916" s="2" t="n"/>
     </row>
     <row r="917">
@@ -25482,7 +25482,7 @@
       <c r="U917" s="4" t="n"/>
       <c r="V917" s="3" t="n"/>
       <c r="W917" s="4" t="n"/>
-      <c r="X917" s="3" t="n"/>
+      <c r="X917" s="4" t="n"/>
       <c r="Y917" s="4" t="n"/>
     </row>
     <row r="918">
@@ -25509,7 +25509,7 @@
       <c r="U918" s="2" t="n"/>
       <c r="V918" s="3" t="n"/>
       <c r="W918" s="2" t="n"/>
-      <c r="X918" s="3" t="n"/>
+      <c r="X918" s="2" t="n"/>
       <c r="Y918" s="2" t="n"/>
     </row>
     <row r="919">
@@ -25536,7 +25536,7 @@
       <c r="U919" s="4" t="n"/>
       <c r="V919" s="3" t="n"/>
       <c r="W919" s="4" t="n"/>
-      <c r="X919" s="3" t="n"/>
+      <c r="X919" s="4" t="n"/>
       <c r="Y919" s="4" t="n"/>
     </row>
     <row r="920">
@@ -25563,7 +25563,7 @@
       <c r="U920" s="2" t="n"/>
       <c r="V920" s="3" t="n"/>
       <c r="W920" s="2" t="n"/>
-      <c r="X920" s="3" t="n"/>
+      <c r="X920" s="2" t="n"/>
       <c r="Y920" s="2" t="n"/>
     </row>
     <row r="921">
@@ -25590,7 +25590,7 @@
       <c r="U921" s="4" t="n"/>
       <c r="V921" s="3" t="n"/>
       <c r="W921" s="4" t="n"/>
-      <c r="X921" s="3" t="n"/>
+      <c r="X921" s="4" t="n"/>
       <c r="Y921" s="4" t="n"/>
     </row>
     <row r="922">
@@ -25617,7 +25617,7 @@
       <c r="U922" s="2" t="n"/>
       <c r="V922" s="3" t="n"/>
       <c r="W922" s="2" t="n"/>
-      <c r="X922" s="3" t="n"/>
+      <c r="X922" s="2" t="n"/>
       <c r="Y922" s="2" t="n"/>
     </row>
     <row r="923">
@@ -25644,7 +25644,7 @@
       <c r="U923" s="4" t="n"/>
       <c r="V923" s="3" t="n"/>
       <c r="W923" s="4" t="n"/>
-      <c r="X923" s="3" t="n"/>
+      <c r="X923" s="4" t="n"/>
       <c r="Y923" s="4" t="n"/>
     </row>
     <row r="924">
@@ -25671,7 +25671,7 @@
       <c r="U924" s="2" t="n"/>
       <c r="V924" s="3" t="n"/>
       <c r="W924" s="2" t="n"/>
-      <c r="X924" s="3" t="n"/>
+      <c r="X924" s="2" t="n"/>
       <c r="Y924" s="2" t="n"/>
     </row>
     <row r="925">
@@ -25698,7 +25698,7 @@
       <c r="U925" s="4" t="n"/>
       <c r="V925" s="3" t="n"/>
       <c r="W925" s="4" t="n"/>
-      <c r="X925" s="3" t="n"/>
+      <c r="X925" s="4" t="n"/>
       <c r="Y925" s="4" t="n"/>
     </row>
     <row r="926">
@@ -25725,7 +25725,7 @@
       <c r="U926" s="2" t="n"/>
       <c r="V926" s="3" t="n"/>
       <c r="W926" s="2" t="n"/>
-      <c r="X926" s="3" t="n"/>
+      <c r="X926" s="2" t="n"/>
       <c r="Y926" s="2" t="n"/>
     </row>
     <row r="927">
@@ -25752,7 +25752,7 @@
       <c r="U927" s="4" t="n"/>
       <c r="V927" s="3" t="n"/>
       <c r="W927" s="4" t="n"/>
-      <c r="X927" s="3" t="n"/>
+      <c r="X927" s="4" t="n"/>
       <c r="Y927" s="4" t="n"/>
     </row>
     <row r="928">
@@ -25779,7 +25779,7 @@
       <c r="U928" s="2" t="n"/>
       <c r="V928" s="3" t="n"/>
       <c r="W928" s="2" t="n"/>
-      <c r="X928" s="3" t="n"/>
+      <c r="X928" s="2" t="n"/>
       <c r="Y928" s="2" t="n"/>
     </row>
     <row r="929">
@@ -25806,7 +25806,7 @@
       <c r="U929" s="4" t="n"/>
       <c r="V929" s="3" t="n"/>
       <c r="W929" s="4" t="n"/>
-      <c r="X929" s="3" t="n"/>
+      <c r="X929" s="4" t="n"/>
       <c r="Y929" s="4" t="n"/>
     </row>
     <row r="930">
@@ -25833,7 +25833,7 @@
       <c r="U930" s="2" t="n"/>
       <c r="V930" s="3" t="n"/>
       <c r="W930" s="2" t="n"/>
-      <c r="X930" s="3" t="n"/>
+      <c r="X930" s="2" t="n"/>
       <c r="Y930" s="2" t="n"/>
     </row>
     <row r="931">
@@ -25860,7 +25860,7 @@
       <c r="U931" s="4" t="n"/>
       <c r="V931" s="3" t="n"/>
       <c r="W931" s="4" t="n"/>
-      <c r="X931" s="3" t="n"/>
+      <c r="X931" s="4" t="n"/>
       <c r="Y931" s="4" t="n"/>
     </row>
     <row r="932">
@@ -25887,7 +25887,7 @@
       <c r="U932" s="2" t="n"/>
       <c r="V932" s="3" t="n"/>
       <c r="W932" s="2" t="n"/>
-      <c r="X932" s="3" t="n"/>
+      <c r="X932" s="2" t="n"/>
       <c r="Y932" s="2" t="n"/>
     </row>
     <row r="933">
@@ -25914,7 +25914,7 @@
       <c r="U933" s="4" t="n"/>
       <c r="V933" s="3" t="n"/>
       <c r="W933" s="4" t="n"/>
-      <c r="X933" s="3" t="n"/>
+      <c r="X933" s="4" t="n"/>
       <c r="Y933" s="4" t="n"/>
     </row>
     <row r="934">
@@ -25941,7 +25941,7 @@
       <c r="U934" s="2" t="n"/>
       <c r="V934" s="3" t="n"/>
       <c r="W934" s="2" t="n"/>
-      <c r="X934" s="3" t="n"/>
+      <c r="X934" s="2" t="n"/>
       <c r="Y934" s="2" t="n"/>
     </row>
     <row r="935">
@@ -25968,7 +25968,7 @@
       <c r="U935" s="4" t="n"/>
       <c r="V935" s="3" t="n"/>
       <c r="W935" s="4" t="n"/>
-      <c r="X935" s="3" t="n"/>
+      <c r="X935" s="4" t="n"/>
       <c r="Y935" s="4" t="n"/>
     </row>
     <row r="936">
@@ -25995,7 +25995,7 @@
       <c r="U936" s="2" t="n"/>
       <c r="V936" s="3" t="n"/>
       <c r="W936" s="2" t="n"/>
-      <c r="X936" s="3" t="n"/>
+      <c r="X936" s="2" t="n"/>
       <c r="Y936" s="2" t="n"/>
     </row>
     <row r="937">
@@ -26022,7 +26022,7 @@
       <c r="U937" s="4" t="n"/>
       <c r="V937" s="3" t="n"/>
       <c r="W937" s="4" t="n"/>
-      <c r="X937" s="3" t="n"/>
+      <c r="X937" s="4" t="n"/>
       <c r="Y937" s="4" t="n"/>
     </row>
     <row r="938">
@@ -26049,7 +26049,7 @@
       <c r="U938" s="2" t="n"/>
       <c r="V938" s="3" t="n"/>
       <c r="W938" s="2" t="n"/>
-      <c r="X938" s="3" t="n"/>
+      <c r="X938" s="2" t="n"/>
       <c r="Y938" s="2" t="n"/>
     </row>
     <row r="939">
@@ -26076,7 +26076,7 @@
       <c r="U939" s="4" t="n"/>
       <c r="V939" s="3" t="n"/>
       <c r="W939" s="4" t="n"/>
-      <c r="X939" s="3" t="n"/>
+      <c r="X939" s="4" t="n"/>
       <c r="Y939" s="4" t="n"/>
     </row>
     <row r="940">
@@ -26103,7 +26103,7 @@
       <c r="U940" s="2" t="n"/>
       <c r="V940" s="3" t="n"/>
       <c r="W940" s="2" t="n"/>
-      <c r="X940" s="3" t="n"/>
+      <c r="X940" s="2" t="n"/>
       <c r="Y940" s="2" t="n"/>
     </row>
     <row r="941">
@@ -26130,7 +26130,7 @@
       <c r="U941" s="4" t="n"/>
       <c r="V941" s="3" t="n"/>
       <c r="W941" s="4" t="n"/>
-      <c r="X941" s="3" t="n"/>
+      <c r="X941" s="4" t="n"/>
       <c r="Y941" s="4" t="n"/>
     </row>
     <row r="942">
@@ -26157,7 +26157,7 @@
       <c r="U942" s="2" t="n"/>
       <c r="V942" s="3" t="n"/>
       <c r="W942" s="2" t="n"/>
-      <c r="X942" s="3" t="n"/>
+      <c r="X942" s="2" t="n"/>
       <c r="Y942" s="2" t="n"/>
     </row>
     <row r="943">
@@ -26184,7 +26184,7 @@
       <c r="U943" s="4" t="n"/>
       <c r="V943" s="3" t="n"/>
       <c r="W943" s="4" t="n"/>
-      <c r="X943" s="3" t="n"/>
+      <c r="X943" s="4" t="n"/>
       <c r="Y943" s="4" t="n"/>
     </row>
     <row r="944">
@@ -26211,7 +26211,7 @@
       <c r="U944" s="2" t="n"/>
       <c r="V944" s="3" t="n"/>
       <c r="W944" s="2" t="n"/>
-      <c r="X944" s="3" t="n"/>
+      <c r="X944" s="2" t="n"/>
       <c r="Y944" s="2" t="n"/>
     </row>
     <row r="945">
@@ -26238,7 +26238,7 @@
       <c r="U945" s="4" t="n"/>
       <c r="V945" s="3" t="n"/>
       <c r="W945" s="4" t="n"/>
-      <c r="X945" s="3" t="n"/>
+      <c r="X945" s="4" t="n"/>
       <c r="Y945" s="4" t="n"/>
     </row>
     <row r="946">
@@ -26265,7 +26265,7 @@
       <c r="U946" s="2" t="n"/>
       <c r="V946" s="3" t="n"/>
       <c r="W946" s="2" t="n"/>
-      <c r="X946" s="3" t="n"/>
+      <c r="X946" s="2" t="n"/>
       <c r="Y946" s="2" t="n"/>
     </row>
     <row r="947">
@@ -26292,7 +26292,7 @@
       <c r="U947" s="4" t="n"/>
       <c r="V947" s="3" t="n"/>
       <c r="W947" s="4" t="n"/>
-      <c r="X947" s="3" t="n"/>
+      <c r="X947" s="4" t="n"/>
       <c r="Y947" s="4" t="n"/>
     </row>
     <row r="948">
@@ -26319,7 +26319,7 @@
       <c r="U948" s="2" t="n"/>
       <c r="V948" s="3" t="n"/>
       <c r="W948" s="2" t="n"/>
-      <c r="X948" s="3" t="n"/>
+      <c r="X948" s="2" t="n"/>
       <c r="Y948" s="2" t="n"/>
     </row>
     <row r="949">
@@ -26346,7 +26346,7 @@
       <c r="U949" s="4" t="n"/>
       <c r="V949" s="3" t="n"/>
       <c r="W949" s="4" t="n"/>
-      <c r="X949" s="3" t="n"/>
+      <c r="X949" s="4" t="n"/>
       <c r="Y949" s="4" t="n"/>
     </row>
     <row r="950">
@@ -26373,7 +26373,7 @@
       <c r="U950" s="2" t="n"/>
       <c r="V950" s="3" t="n"/>
       <c r="W950" s="2" t="n"/>
-      <c r="X950" s="3" t="n"/>
+      <c r="X950" s="2" t="n"/>
       <c r="Y950" s="2" t="n"/>
     </row>
     <row r="951">
@@ -26400,7 +26400,7 @@
       <c r="U951" s="4" t="n"/>
       <c r="V951" s="3" t="n"/>
       <c r="W951" s="4" t="n"/>
-      <c r="X951" s="3" t="n"/>
+      <c r="X951" s="4" t="n"/>
       <c r="Y951" s="4" t="n"/>
     </row>
     <row r="952">
@@ -26427,7 +26427,7 @@
       <c r="U952" s="2" t="n"/>
       <c r="V952" s="3" t="n"/>
       <c r="W952" s="2" t="n"/>
-      <c r="X952" s="3" t="n"/>
+      <c r="X952" s="2" t="n"/>
       <c r="Y952" s="2" t="n"/>
     </row>
     <row r="953">
@@ -26454,7 +26454,7 @@
       <c r="U953" s="4" t="n"/>
       <c r="V953" s="3" t="n"/>
       <c r="W953" s="4" t="n"/>
-      <c r="X953" s="3" t="n"/>
+      <c r="X953" s="4" t="n"/>
       <c r="Y953" s="4" t="n"/>
     </row>
     <row r="954">
@@ -26481,7 +26481,7 @@
       <c r="U954" s="2" t="n"/>
       <c r="V954" s="3" t="n"/>
       <c r="W954" s="2" t="n"/>
-      <c r="X954" s="3" t="n"/>
+      <c r="X954" s="2" t="n"/>
       <c r="Y954" s="2" t="n"/>
     </row>
     <row r="955">
@@ -26508,7 +26508,7 @@
       <c r="U955" s="4" t="n"/>
       <c r="V955" s="3" t="n"/>
       <c r="W955" s="4" t="n"/>
-      <c r="X955" s="3" t="n"/>
+      <c r="X955" s="4" t="n"/>
       <c r="Y955" s="4" t="n"/>
     </row>
     <row r="956">
@@ -26535,7 +26535,7 @@
       <c r="U956" s="2" t="n"/>
       <c r="V956" s="3" t="n"/>
       <c r="W956" s="2" t="n"/>
-      <c r="X956" s="3" t="n"/>
+      <c r="X956" s="2" t="n"/>
       <c r="Y956" s="2" t="n"/>
     </row>
     <row r="957">
@@ -26562,7 +26562,7 @@
       <c r="U957" s="4" t="n"/>
       <c r="V957" s="3" t="n"/>
       <c r="W957" s="4" t="n"/>
-      <c r="X957" s="3" t="n"/>
+      <c r="X957" s="4" t="n"/>
       <c r="Y957" s="4" t="n"/>
     </row>
     <row r="958">
@@ -26589,7 +26589,7 @@
       <c r="U958" s="2" t="n"/>
       <c r="V958" s="3" t="n"/>
       <c r="W958" s="2" t="n"/>
-      <c r="X958" s="3" t="n"/>
+      <c r="X958" s="2" t="n"/>
       <c r="Y958" s="2" t="n"/>
     </row>
     <row r="959">
@@ -26616,7 +26616,7 @@
       <c r="U959" s="4" t="n"/>
       <c r="V959" s="3" t="n"/>
       <c r="W959" s="4" t="n"/>
-      <c r="X959" s="3" t="n"/>
+      <c r="X959" s="4" t="n"/>
       <c r="Y959" s="4" t="n"/>
     </row>
     <row r="960">
@@ -26643,7 +26643,7 @@
       <c r="U960" s="2" t="n"/>
       <c r="V960" s="3" t="n"/>
       <c r="W960" s="2" t="n"/>
-      <c r="X960" s="3" t="n"/>
+      <c r="X960" s="2" t="n"/>
       <c r="Y960" s="2" t="n"/>
     </row>
     <row r="961">
@@ -26670,7 +26670,7 @@
       <c r="U961" s="4" t="n"/>
       <c r="V961" s="3" t="n"/>
       <c r="W961" s="4" t="n"/>
-      <c r="X961" s="3" t="n"/>
+      <c r="X961" s="4" t="n"/>
       <c r="Y961" s="4" t="n"/>
     </row>
     <row r="962">
@@ -26697,7 +26697,7 @@
       <c r="U962" s="2" t="n"/>
       <c r="V962" s="3" t="n"/>
       <c r="W962" s="2" t="n"/>
-      <c r="X962" s="3" t="n"/>
+      <c r="X962" s="2" t="n"/>
       <c r="Y962" s="2" t="n"/>
     </row>
     <row r="963">
@@ -26724,7 +26724,7 @@
       <c r="U963" s="4" t="n"/>
       <c r="V963" s="3" t="n"/>
       <c r="W963" s="4" t="n"/>
-      <c r="X963" s="3" t="n"/>
+      <c r="X963" s="4" t="n"/>
       <c r="Y963" s="4" t="n"/>
     </row>
     <row r="964">
@@ -26751,7 +26751,7 @@
       <c r="U964" s="2" t="n"/>
       <c r="V964" s="3" t="n"/>
       <c r="W964" s="2" t="n"/>
-      <c r="X964" s="3" t="n"/>
+      <c r="X964" s="2" t="n"/>
       <c r="Y964" s="2" t="n"/>
     </row>
     <row r="965">
@@ -26778,7 +26778,7 @@
       <c r="U965" s="4" t="n"/>
       <c r="V965" s="3" t="n"/>
       <c r="W965" s="4" t="n"/>
-      <c r="X965" s="3" t="n"/>
+      <c r="X965" s="4" t="n"/>
       <c r="Y965" s="4" t="n"/>
     </row>
     <row r="966">
@@ -26805,7 +26805,7 @@
       <c r="U966" s="2" t="n"/>
       <c r="V966" s="3" t="n"/>
       <c r="W966" s="2" t="n"/>
-      <c r="X966" s="3" t="n"/>
+      <c r="X966" s="2" t="n"/>
       <c r="Y966" s="2" t="n"/>
     </row>
     <row r="967">
@@ -26832,7 +26832,7 @@
       <c r="U967" s="4" t="n"/>
       <c r="V967" s="3" t="n"/>
       <c r="W967" s="4" t="n"/>
-      <c r="X967" s="3" t="n"/>
+      <c r="X967" s="4" t="n"/>
       <c r="Y967" s="4" t="n"/>
     </row>
     <row r="968">
@@ -26859,7 +26859,7 @@
       <c r="U968" s="2" t="n"/>
       <c r="V968" s="3" t="n"/>
       <c r="W968" s="2" t="n"/>
-      <c r="X968" s="3" t="n"/>
+      <c r="X968" s="2" t="n"/>
       <c r="Y968" s="2" t="n"/>
     </row>
     <row r="969">
@@ -26886,7 +26886,7 @@
       <c r="U969" s="4" t="n"/>
       <c r="V969" s="3" t="n"/>
       <c r="W969" s="4" t="n"/>
-      <c r="X969" s="3" t="n"/>
+      <c r="X969" s="4" t="n"/>
       <c r="Y969" s="4" t="n"/>
     </row>
     <row r="970">
@@ -26913,7 +26913,7 @@
       <c r="U970" s="2" t="n"/>
       <c r="V970" s="3" t="n"/>
       <c r="W970" s="2" t="n"/>
-      <c r="X970" s="3" t="n"/>
+      <c r="X970" s="2" t="n"/>
       <c r="Y970" s="2" t="n"/>
     </row>
     <row r="971">
@@ -26940,7 +26940,7 @@
       <c r="U971" s="4" t="n"/>
       <c r="V971" s="3" t="n"/>
       <c r="W971" s="4" t="n"/>
-      <c r="X971" s="3" t="n"/>
+      <c r="X971" s="4" t="n"/>
       <c r="Y971" s="4" t="n"/>
     </row>
     <row r="972">
@@ -26967,7 +26967,7 @@
       <c r="U972" s="2" t="n"/>
       <c r="V972" s="3" t="n"/>
       <c r="W972" s="2" t="n"/>
-      <c r="X972" s="3" t="n"/>
+      <c r="X972" s="2" t="n"/>
       <c r="Y972" s="2" t="n"/>
     </row>
     <row r="973">
@@ -26994,7 +26994,7 @@
       <c r="U973" s="4" t="n"/>
       <c r="V973" s="3" t="n"/>
       <c r="W973" s="4" t="n"/>
-      <c r="X973" s="3" t="n"/>
+      <c r="X973" s="4" t="n"/>
       <c r="Y973" s="4" t="n"/>
     </row>
     <row r="974">
@@ -27021,7 +27021,7 @@
       <c r="U974" s="2" t="n"/>
       <c r="V974" s="3" t="n"/>
       <c r="W974" s="2" t="n"/>
-      <c r="X974" s="3" t="n"/>
+      <c r="X974" s="2" t="n"/>
       <c r="Y974" s="2" t="n"/>
     </row>
     <row r="975">
@@ -27048,7 +27048,7 @@
       <c r="U975" s="4" t="n"/>
       <c r="V975" s="3" t="n"/>
       <c r="W975" s="4" t="n"/>
-      <c r="X975" s="3" t="n"/>
+      <c r="X975" s="4" t="n"/>
       <c r="Y975" s="4" t="n"/>
     </row>
     <row r="976">
@@ -27075,7 +27075,7 @@
       <c r="U976" s="2" t="n"/>
       <c r="V976" s="3" t="n"/>
       <c r="W976" s="2" t="n"/>
-      <c r="X976" s="3" t="n"/>
+      <c r="X976" s="2" t="n"/>
       <c r="Y976" s="2" t="n"/>
     </row>
     <row r="977">
@@ -27102,7 +27102,7 @@
       <c r="U977" s="4" t="n"/>
       <c r="V977" s="3" t="n"/>
       <c r="W977" s="4" t="n"/>
-      <c r="X977" s="3" t="n"/>
+      <c r="X977" s="4" t="n"/>
       <c r="Y977" s="4" t="n"/>
     </row>
     <row r="978">
@@ -27129,7 +27129,7 @@
       <c r="U978" s="2" t="n"/>
       <c r="V978" s="3" t="n"/>
       <c r="W978" s="2" t="n"/>
-      <c r="X978" s="3" t="n"/>
+      <c r="X978" s="2" t="n"/>
       <c r="Y978" s="2" t="n"/>
     </row>
     <row r="979">
@@ -27156,7 +27156,7 @@
       <c r="U979" s="4" t="n"/>
       <c r="V979" s="3" t="n"/>
       <c r="W979" s="4" t="n"/>
-      <c r="X979" s="3" t="n"/>
+      <c r="X979" s="4" t="n"/>
       <c r="Y979" s="4" t="n"/>
     </row>
     <row r="980">
@@ -27183,7 +27183,7 @@
       <c r="U980" s="2" t="n"/>
       <c r="V980" s="3" t="n"/>
       <c r="W980" s="2" t="n"/>
-      <c r="X980" s="3" t="n"/>
+      <c r="X980" s="2" t="n"/>
       <c r="Y980" s="2" t="n"/>
     </row>
     <row r="981">
@@ -27210,7 +27210,7 @@
       <c r="U981" s="4" t="n"/>
       <c r="V981" s="3" t="n"/>
       <c r="W981" s="4" t="n"/>
-      <c r="X981" s="3" t="n"/>
+      <c r="X981" s="4" t="n"/>
       <c r="Y981" s="4" t="n"/>
     </row>
     <row r="982">
@@ -27237,7 +27237,7 @@
       <c r="U982" s="2" t="n"/>
       <c r="V982" s="3" t="n"/>
       <c r="W982" s="2" t="n"/>
-      <c r="X982" s="3" t="n"/>
+      <c r="X982" s="2" t="n"/>
       <c r="Y982" s="2" t="n"/>
     </row>
     <row r="983">
@@ -27264,7 +27264,7 @@
       <c r="U983" s="4" t="n"/>
       <c r="V983" s="3" t="n"/>
       <c r="W983" s="4" t="n"/>
-      <c r="X983" s="3" t="n"/>
+      <c r="X983" s="4" t="n"/>
       <c r="Y983" s="4" t="n"/>
     </row>
     <row r="984">
@@ -27291,7 +27291,7 @@
       <c r="U984" s="2" t="n"/>
       <c r="V984" s="3" t="n"/>
       <c r="W984" s="2" t="n"/>
-      <c r="X984" s="3" t="n"/>
+      <c r="X984" s="2" t="n"/>
       <c r="Y984" s="2" t="n"/>
     </row>
     <row r="985">
@@ -27318,7 +27318,7 @@
       <c r="U985" s="4" t="n"/>
       <c r="V985" s="3" t="n"/>
       <c r="W985" s="4" t="n"/>
-      <c r="X985" s="3" t="n"/>
+      <c r="X985" s="4" t="n"/>
       <c r="Y985" s="4" t="n"/>
     </row>
     <row r="986">
@@ -27345,7 +27345,7 @@
       <c r="U986" s="2" t="n"/>
       <c r="V986" s="3" t="n"/>
       <c r="W986" s="2" t="n"/>
-      <c r="X986" s="3" t="n"/>
+      <c r="X986" s="2" t="n"/>
       <c r="Y986" s="2" t="n"/>
     </row>
     <row r="987">
@@ -27372,7 +27372,7 @@
       <c r="U987" s="4" t="n"/>
       <c r="V987" s="3" t="n"/>
       <c r="W987" s="4" t="n"/>
-      <c r="X987" s="3" t="n"/>
+      <c r="X987" s="4" t="n"/>
       <c r="Y987" s="4" t="n"/>
     </row>
     <row r="988">
@@ -27399,7 +27399,7 @@
       <c r="U988" s="2" t="n"/>
       <c r="V988" s="3" t="n"/>
       <c r="W988" s="2" t="n"/>
-      <c r="X988" s="3" t="n"/>
+      <c r="X988" s="2" t="n"/>
       <c r="Y988" s="2" t="n"/>
     </row>
     <row r="989">
@@ -27426,7 +27426,7 @@
       <c r="U989" s="4" t="n"/>
       <c r="V989" s="3" t="n"/>
       <c r="W989" s="4" t="n"/>
-      <c r="X989" s="3" t="n"/>
+      <c r="X989" s="4" t="n"/>
       <c r="Y989" s="4" t="n"/>
     </row>
     <row r="990">
@@ -27453,7 +27453,7 @@
       <c r="U990" s="2" t="n"/>
       <c r="V990" s="3" t="n"/>
       <c r="W990" s="2" t="n"/>
-      <c r="X990" s="3" t="n"/>
+      <c r="X990" s="2" t="n"/>
       <c r="Y990" s="2" t="n"/>
     </row>
     <row r="991">
@@ -27480,7 +27480,7 @@
       <c r="U991" s="4" t="n"/>
       <c r="V991" s="3" t="n"/>
       <c r="W991" s="4" t="n"/>
-      <c r="X991" s="3" t="n"/>
+      <c r="X991" s="4" t="n"/>
       <c r="Y991" s="4" t="n"/>
     </row>
     <row r="992">
@@ -27507,7 +27507,7 @@
       <c r="U992" s="2" t="n"/>
       <c r="V992" s="3" t="n"/>
       <c r="W992" s="2" t="n"/>
-      <c r="X992" s="3" t="n"/>
+      <c r="X992" s="2" t="n"/>
       <c r="Y992" s="2" t="n"/>
     </row>
     <row r="993">
@@ -27534,7 +27534,7 @@
       <c r="U993" s="4" t="n"/>
       <c r="V993" s="3" t="n"/>
       <c r="W993" s="4" t="n"/>
-      <c r="X993" s="3" t="n"/>
+      <c r="X993" s="4" t="n"/>
       <c r="Y993" s="4" t="n"/>
     </row>
     <row r="994">
@@ -27561,7 +27561,7 @@
       <c r="U994" s="2" t="n"/>
       <c r="V994" s="3" t="n"/>
       <c r="W994" s="2" t="n"/>
-      <c r="X994" s="3" t="n"/>
+      <c r="X994" s="2" t="n"/>
       <c r="Y994" s="2" t="n"/>
     </row>
     <row r="995">
@@ -27588,7 +27588,7 @@
       <c r="U995" s="4" t="n"/>
       <c r="V995" s="3" t="n"/>
       <c r="W995" s="4" t="n"/>
-      <c r="X995" s="3" t="n"/>
+      <c r="X995" s="4" t="n"/>
       <c r="Y995" s="4" t="n"/>
     </row>
     <row r="996">
@@ -27615,7 +27615,7 @@
       <c r="U996" s="2" t="n"/>
       <c r="V996" s="3" t="n"/>
       <c r="W996" s="2" t="n"/>
-      <c r="X996" s="3" t="n"/>
+      <c r="X996" s="2" t="n"/>
       <c r="Y996" s="2" t="n"/>
     </row>
     <row r="997">
@@ -27642,7 +27642,7 @@
       <c r="U997" s="4" t="n"/>
       <c r="V997" s="3" t="n"/>
       <c r="W997" s="4" t="n"/>
-      <c r="X997" s="3" t="n"/>
+      <c r="X997" s="4" t="n"/>
       <c r="Y997" s="4" t="n"/>
     </row>
     <row r="998">
@@ -27669,7 +27669,7 @@
       <c r="U998" s="2" t="n"/>
       <c r="V998" s="3" t="n"/>
       <c r="W998" s="2" t="n"/>
-      <c r="X998" s="3" t="n"/>
+      <c r="X998" s="2" t="n"/>
       <c r="Y998" s="2" t="n"/>
     </row>
     <row r="999">
@@ -27696,7 +27696,7 @@
       <c r="U999" s="4" t="n"/>
       <c r="V999" s="3" t="n"/>
       <c r="W999" s="4" t="n"/>
-      <c r="X999" s="3" t="n"/>
+      <c r="X999" s="4" t="n"/>
       <c r="Y999" s="4" t="n"/>
     </row>
     <row r="1000">
@@ -27723,7 +27723,7 @@
       <c r="U1000" s="2" t="n"/>
       <c r="V1000" s="3" t="n"/>
       <c r="W1000" s="2" t="n"/>
-      <c r="X1000" s="3" t="n"/>
+      <c r="X1000" s="2" t="n"/>
       <c r="Y1000" s="2" t="n"/>
     </row>
     <row r="1001">
@@ -27750,7 +27750,7 @@
       <c r="U1001" s="4" t="n"/>
       <c r="V1001" s="3" t="n"/>
       <c r="W1001" s="4" t="n"/>
-      <c r="X1001" s="3" t="n"/>
+      <c r="X1001" s="4" t="n"/>
       <c r="Y1001" s="4" t="n"/>
     </row>
   </sheetData>
@@ -28563,19 +28563,19 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="10" t="inlineStr">
+      <c r="A56" s="12" t="inlineStr">
         <is>
           <t>Dia chi</t>
         </is>
       </c>
       <c r="B56" s="13" t="inlineStr">
         <is>
-          <t>Địa chỉ chi tiết của trạm – bắt buộc</t>
-        </is>
-      </c>
-      <c r="C56" s="15" t="inlineStr">
-        <is>
-          <t>✔ Bắt buộc</t>
+          <t>Địa chỉ chi tiết của trạm – không bắt buộc</t>
+        </is>
+      </c>
+      <c r="C56" s="14" t="inlineStr">
+        <is>
+          <t>Tùy chọn</t>
         </is>
       </c>
     </row>
